--- a/docs/classifiche/classifica2025.xlsx
+++ b/docs/classifiche/classifica2025.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="127">
   <si>
     <t>STAGIONE 2025: MOTO 2</t>
   </si>
@@ -292,6 +292,12 @@
     <t>1:48,664, Aldeguer</t>
   </si>
   <si>
+    <t>1:49.780, Garcia</t>
+  </si>
+  <si>
+    <t>1:35.314</t>
+  </si>
+  <si>
     <t>1:33.839, pole</t>
   </si>
   <si>
@@ -334,6 +340,12 @@
     <t>1:49.364, 10</t>
   </si>
   <si>
+    <t>1:50.378, 9</t>
+  </si>
+  <si>
+    <t>1:35.314, pole</t>
+  </si>
+  <si>
     <t>1:34.373, 2</t>
   </si>
   <si>
@@ -374,6 +386,12 @@
   </si>
   <si>
     <t>1:50.301, 14esimo</t>
+  </si>
+  <si>
+    <t>1:49.829, 3</t>
+  </si>
+  <si>
+    <t>1:36.115, 7</t>
   </si>
 </sst>
 </file>
@@ -463,14 +481,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF999999"/>
-        <bgColor rgb="FF999999"/>
+        <fgColor rgb="FFB45F06"/>
+        <bgColor rgb="FFB45F06"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB45F06"/>
-        <bgColor rgb="FFB45F06"/>
+        <fgColor rgb="FF999999"/>
+        <bgColor rgb="FF999999"/>
       </patternFill>
     </fill>
   </fills>
@@ -595,22 +613,22 @@
     <xf borderId="0" fillId="5" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
+    <xf borderId="0" fillId="6" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
     <xf borderId="6" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="0" fillId="6" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="7" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="6" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="7" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="7" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="6" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="3" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -619,10 +637,10 @@
     <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="6" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="7" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="7" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="6" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="4" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -893,6 +911,7 @@
     <col customWidth="1" min="10" max="10" width="15.75"/>
     <col customWidth="1" min="13" max="13" width="14.25"/>
     <col customWidth="1" min="15" max="15" width="14.75"/>
+    <col customWidth="1" min="16" max="16" width="13.5"/>
     <col customWidth="1" min="26" max="27" width="14.63"/>
   </cols>
   <sheetData>
@@ -1055,8 +1074,8 @@
         <v>25</v>
       </c>
       <c r="B5" s="12">
-        <f>Z13 +Z11 +Z7 +Z10 +Z5 +Z9 +Z6 + Z8 + Z7 +Z4</f>
-        <v>81</v>
+        <f>Z13 +Z11 +Z7 +Z10 +Z5 +Z9 +Z6 + Z8 + Z7 +Z4 +Z3</f>
+        <v>97</v>
       </c>
       <c r="C5" s="12" t="s">
         <v>26</v>
@@ -1103,51 +1122,55 @@
       <c r="Q5" s="13">
         <v>4.0</v>
       </c>
-      <c r="R5" s="15"/>
-      <c r="S5" s="15"/>
-      <c r="T5" s="15"/>
-      <c r="U5" s="15"/>
-      <c r="V5" s="15"/>
-      <c r="W5" s="15"/>
-      <c r="X5" s="15"/>
-      <c r="Y5" s="15"/>
+      <c r="R5" s="15">
+        <v>3.0</v>
+      </c>
+      <c r="S5" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="T5" s="16"/>
+      <c r="U5" s="16"/>
+      <c r="V5" s="16"/>
+      <c r="W5" s="16"/>
+      <c r="X5" s="16"/>
+      <c r="Y5" s="16"/>
       <c r="Z5" s="3">
         <v>11.0</v>
       </c>
-      <c r="AA5" s="16">
+      <c r="AA5" s="17">
         <v>2.0</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="15"/>
-      <c r="B6" s="15"/>
-      <c r="C6" s="15"/>
-      <c r="D6" s="15"/>
-      <c r="E6" s="15"/>
-      <c r="F6" s="15"/>
-      <c r="G6" s="15"/>
-      <c r="H6" s="15"/>
-      <c r="I6" s="15"/>
-      <c r="J6" s="15"/>
-      <c r="K6" s="15"/>
-      <c r="L6" s="15"/>
-      <c r="M6" s="15"/>
-      <c r="N6" s="15"/>
-      <c r="O6" s="15"/>
-      <c r="P6" s="15"/>
-      <c r="Q6" s="15"/>
-      <c r="R6" s="15"/>
-      <c r="S6" s="15"/>
-      <c r="T6" s="15"/>
-      <c r="U6" s="15"/>
-      <c r="V6" s="15"/>
-      <c r="W6" s="15"/>
-      <c r="X6" s="15"/>
-      <c r="Y6" s="15"/>
+      <c r="A6" s="16"/>
+      <c r="B6" s="16"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="16"/>
+      <c r="H6" s="16"/>
+      <c r="I6" s="16"/>
+      <c r="J6" s="16"/>
+      <c r="K6" s="16"/>
+      <c r="L6" s="16"/>
+      <c r="M6" s="16"/>
+      <c r="N6" s="16"/>
+      <c r="O6" s="16"/>
+      <c r="P6" s="16"/>
+      <c r="Q6" s="16"/>
+      <c r="R6" s="16"/>
+      <c r="S6" s="16"/>
+      <c r="T6" s="16"/>
+      <c r="U6" s="16"/>
+      <c r="V6" s="16"/>
+      <c r="W6" s="16"/>
+      <c r="X6" s="16"/>
+      <c r="Y6" s="16"/>
       <c r="Z6" s="3">
         <v>10.0</v>
       </c>
-      <c r="AA6" s="17">
+      <c r="AA6" s="15">
         <v>3.0</v>
       </c>
     </row>
@@ -1204,14 +1227,18 @@
       <c r="Q7" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="R7" s="15"/>
-      <c r="S7" s="15"/>
-      <c r="T7" s="15"/>
-      <c r="U7" s="15"/>
-      <c r="V7" s="15"/>
-      <c r="W7" s="15"/>
-      <c r="X7" s="15"/>
-      <c r="Y7" s="15"/>
+      <c r="R7" s="12">
+        <v>17.0</v>
+      </c>
+      <c r="S7" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="T7" s="16"/>
+      <c r="U7" s="16"/>
+      <c r="V7" s="16"/>
+      <c r="W7" s="16"/>
+      <c r="X7" s="16"/>
+      <c r="Y7" s="16"/>
       <c r="Z7" s="3">
         <v>9.0</v>
       </c>
@@ -1220,31 +1247,31 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="15"/>
-      <c r="B8" s="15"/>
-      <c r="C8" s="15"/>
-      <c r="D8" s="15"/>
-      <c r="E8" s="15"/>
-      <c r="F8" s="15"/>
-      <c r="G8" s="15"/>
-      <c r="H8" s="15"/>
-      <c r="I8" s="15"/>
-      <c r="J8" s="15"/>
-      <c r="K8" s="15"/>
-      <c r="L8" s="15"/>
-      <c r="M8" s="15"/>
-      <c r="N8" s="15"/>
-      <c r="O8" s="15"/>
-      <c r="P8" s="15"/>
-      <c r="Q8" s="15"/>
-      <c r="R8" s="15"/>
-      <c r="S8" s="15"/>
-      <c r="T8" s="15"/>
-      <c r="U8" s="15"/>
-      <c r="V8" s="15"/>
-      <c r="W8" s="15"/>
-      <c r="X8" s="15"/>
-      <c r="Y8" s="15"/>
+      <c r="A8" s="16"/>
+      <c r="B8" s="16"/>
+      <c r="C8" s="16"/>
+      <c r="D8" s="16"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="16"/>
+      <c r="I8" s="16"/>
+      <c r="J8" s="16"/>
+      <c r="K8" s="16"/>
+      <c r="L8" s="16"/>
+      <c r="M8" s="16"/>
+      <c r="N8" s="16"/>
+      <c r="O8" s="16"/>
+      <c r="P8" s="16"/>
+      <c r="Q8" s="16"/>
+      <c r="R8" s="16"/>
+      <c r="S8" s="16"/>
+      <c r="T8" s="16"/>
+      <c r="U8" s="16"/>
+      <c r="V8" s="16"/>
+      <c r="W8" s="16"/>
+      <c r="X8" s="16"/>
+      <c r="Y8" s="16"/>
       <c r="Z8" s="3">
         <v>8.0</v>
       </c>
@@ -1257,8 +1284,8 @@
         <v>29</v>
       </c>
       <c r="B9" s="12">
-        <f> Z4 +Z10 +Z14 +Z2 +Z4 +Z11 +Z13 +Z3 + Z2 + Z2</f>
-        <v>118</v>
+        <f> Z4 +Z10 +Z14 +Z2 +Z4 +Z11 +Z13 +Z3 + Z2 + Z2 +Z10 +Z6</f>
+        <v>134</v>
       </c>
       <c r="C9" s="12" t="s">
         <v>30</v>
@@ -1275,7 +1302,7 @@
       <c r="G9" s="13">
         <v>14.0</v>
       </c>
-      <c r="H9" s="16">
+      <c r="H9" s="17">
         <v>2.0</v>
       </c>
       <c r="I9" s="13">
@@ -1287,7 +1314,7 @@
       <c r="K9" s="13">
         <v>13.0</v>
       </c>
-      <c r="L9" s="17">
+      <c r="L9" s="15">
         <v>3.0</v>
       </c>
       <c r="M9" s="18">
@@ -1305,14 +1332,18 @@
       <c r="Q9" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="R9" s="15"/>
-      <c r="S9" s="15"/>
-      <c r="T9" s="15"/>
-      <c r="U9" s="15"/>
-      <c r="V9" s="15"/>
-      <c r="W9" s="15"/>
-      <c r="X9" s="15"/>
-      <c r="Y9" s="15"/>
+      <c r="R9" s="13">
+        <v>10.0</v>
+      </c>
+      <c r="S9" s="13">
+        <v>6.0</v>
+      </c>
+      <c r="T9" s="16"/>
+      <c r="U9" s="16"/>
+      <c r="V9" s="16"/>
+      <c r="W9" s="16"/>
+      <c r="X9" s="16"/>
+      <c r="Y9" s="16"/>
       <c r="Z9" s="3">
         <v>7.0</v>
       </c>
@@ -1321,31 +1352,31 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="15"/>
-      <c r="B10" s="15"/>
-      <c r="C10" s="15"/>
-      <c r="D10" s="15"/>
-      <c r="E10" s="15"/>
-      <c r="F10" s="15"/>
-      <c r="G10" s="15"/>
-      <c r="H10" s="15"/>
-      <c r="I10" s="15"/>
-      <c r="J10" s="15"/>
-      <c r="K10" s="15"/>
-      <c r="L10" s="15"/>
-      <c r="M10" s="15"/>
-      <c r="N10" s="15"/>
-      <c r="O10" s="15"/>
-      <c r="P10" s="15"/>
-      <c r="Q10" s="15"/>
-      <c r="R10" s="15"/>
-      <c r="S10" s="15"/>
-      <c r="T10" s="15"/>
-      <c r="U10" s="15"/>
-      <c r="V10" s="15"/>
-      <c r="W10" s="15"/>
-      <c r="X10" s="15"/>
-      <c r="Y10" s="15"/>
+      <c r="A10" s="16"/>
+      <c r="B10" s="16"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="16"/>
+      <c r="E10" s="16"/>
+      <c r="F10" s="16"/>
+      <c r="G10" s="16"/>
+      <c r="H10" s="16"/>
+      <c r="I10" s="16"/>
+      <c r="J10" s="16"/>
+      <c r="K10" s="16"/>
+      <c r="L10" s="16"/>
+      <c r="M10" s="16"/>
+      <c r="N10" s="16"/>
+      <c r="O10" s="16"/>
+      <c r="P10" s="16"/>
+      <c r="Q10" s="16"/>
+      <c r="R10" s="16"/>
+      <c r="S10" s="16"/>
+      <c r="T10" s="16"/>
+      <c r="U10" s="16"/>
+      <c r="V10" s="16"/>
+      <c r="W10" s="16"/>
+      <c r="X10" s="16"/>
+      <c r="Y10" s="16"/>
       <c r="Z10" s="3">
         <v>6.0</v>
       </c>
@@ -1358,8 +1389,8 @@
         <v>31</v>
       </c>
       <c r="B11" s="12">
-        <f>Z13 +Z9 +Z13 +Z11 +Z11 +Z14 +Z10 +Z12 + Z15 + Z11 + Z12 +Z10 +Z9</f>
-        <v>58</v>
+        <f>Z13 +Z9 +Z13 +Z11 +Z11 +Z14 +Z10 +Z12 + Z15 + Z11 + Z12 +Z10 +Z9 +Z9</f>
+        <v>65</v>
       </c>
       <c r="C11" s="12" t="s">
         <v>30</v>
@@ -1406,14 +1437,18 @@
       <c r="Q11" s="13">
         <v>9.0</v>
       </c>
-      <c r="R11" s="15"/>
-      <c r="S11" s="15"/>
-      <c r="T11" s="15"/>
-      <c r="U11" s="15"/>
-      <c r="V11" s="15"/>
-      <c r="W11" s="15"/>
-      <c r="X11" s="15"/>
-      <c r="Y11" s="15"/>
+      <c r="R11" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="S11" s="13">
+        <v>9.0</v>
+      </c>
+      <c r="T11" s="16"/>
+      <c r="U11" s="16"/>
+      <c r="V11" s="16"/>
+      <c r="W11" s="16"/>
+      <c r="X11" s="16"/>
+      <c r="Y11" s="16"/>
       <c r="Z11" s="3">
         <v>5.0</v>
       </c>
@@ -1422,31 +1457,31 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="15"/>
-      <c r="B12" s="15"/>
-      <c r="C12" s="15"/>
-      <c r="D12" s="15"/>
-      <c r="E12" s="15"/>
-      <c r="F12" s="15"/>
-      <c r="G12" s="15"/>
-      <c r="H12" s="15"/>
-      <c r="I12" s="15"/>
-      <c r="J12" s="15"/>
-      <c r="K12" s="15"/>
-      <c r="L12" s="15"/>
-      <c r="M12" s="15"/>
-      <c r="N12" s="15"/>
-      <c r="O12" s="15"/>
-      <c r="P12" s="15"/>
-      <c r="Q12" s="15"/>
-      <c r="R12" s="15"/>
-      <c r="S12" s="15"/>
-      <c r="T12" s="15"/>
-      <c r="U12" s="15"/>
-      <c r="V12" s="15"/>
-      <c r="W12" s="15"/>
-      <c r="X12" s="15"/>
-      <c r="Y12" s="15"/>
+      <c r="A12" s="16"/>
+      <c r="B12" s="16"/>
+      <c r="C12" s="16"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="16"/>
+      <c r="G12" s="16"/>
+      <c r="H12" s="16"/>
+      <c r="I12" s="16"/>
+      <c r="J12" s="16"/>
+      <c r="K12" s="16"/>
+      <c r="L12" s="16"/>
+      <c r="M12" s="16"/>
+      <c r="N12" s="16"/>
+      <c r="O12" s="16"/>
+      <c r="P12" s="16"/>
+      <c r="Q12" s="16"/>
+      <c r="R12" s="16"/>
+      <c r="S12" s="16"/>
+      <c r="T12" s="16"/>
+      <c r="U12" s="16"/>
+      <c r="V12" s="16"/>
+      <c r="W12" s="16"/>
+      <c r="X12" s="16"/>
+      <c r="Y12" s="16"/>
       <c r="Z12" s="3">
         <v>4.0</v>
       </c>
@@ -1459,8 +1494,8 @@
         <v>32</v>
       </c>
       <c r="B13" s="12">
-        <f>Z14 +Z8 +Z11 +Z9 +Z15 +Z13 + Z11 +Z11 +Z8</f>
-        <v>44</v>
+        <f>Z14 +Z8 +Z11 +Z9 +Z15 +Z13 + Z11 +Z11 +Z8 +Z15 +Z15</f>
+        <v>46</v>
       </c>
       <c r="C13" s="12" t="s">
         <v>33</v>
@@ -1507,14 +1542,18 @@
       <c r="Q13" s="13">
         <v>8.0</v>
       </c>
-      <c r="R13" s="15"/>
-      <c r="S13" s="15"/>
-      <c r="T13" s="15"/>
-      <c r="U13" s="15"/>
-      <c r="V13" s="15"/>
-      <c r="W13" s="15"/>
-      <c r="X13" s="15"/>
-      <c r="Y13" s="15"/>
+      <c r="R13" s="13">
+        <v>15.0</v>
+      </c>
+      <c r="S13" s="13">
+        <v>15.0</v>
+      </c>
+      <c r="T13" s="16"/>
+      <c r="U13" s="16"/>
+      <c r="V13" s="16"/>
+      <c r="W13" s="16"/>
+      <c r="X13" s="16"/>
+      <c r="Y13" s="16"/>
       <c r="Z13" s="3">
         <v>3.0</v>
       </c>
@@ -1523,31 +1562,31 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="15"/>
-      <c r="B14" s="15"/>
-      <c r="C14" s="15"/>
-      <c r="D14" s="15"/>
-      <c r="E14" s="15"/>
-      <c r="F14" s="15"/>
-      <c r="G14" s="15"/>
-      <c r="H14" s="15"/>
-      <c r="I14" s="15"/>
-      <c r="J14" s="15"/>
-      <c r="K14" s="15"/>
-      <c r="L14" s="15"/>
-      <c r="M14" s="15"/>
-      <c r="N14" s="15"/>
-      <c r="O14" s="15"/>
-      <c r="P14" s="15"/>
-      <c r="Q14" s="15"/>
-      <c r="R14" s="15"/>
-      <c r="S14" s="15"/>
-      <c r="T14" s="15"/>
-      <c r="U14" s="15"/>
-      <c r="V14" s="15"/>
-      <c r="W14" s="15"/>
-      <c r="X14" s="15"/>
-      <c r="Y14" s="15"/>
+      <c r="A14" s="16"/>
+      <c r="B14" s="16"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="16"/>
+      <c r="E14" s="16"/>
+      <c r="F14" s="16"/>
+      <c r="G14" s="16"/>
+      <c r="H14" s="16"/>
+      <c r="I14" s="16"/>
+      <c r="J14" s="16"/>
+      <c r="K14" s="16"/>
+      <c r="L14" s="16"/>
+      <c r="M14" s="16"/>
+      <c r="N14" s="16"/>
+      <c r="O14" s="16"/>
+      <c r="P14" s="16"/>
+      <c r="Q14" s="16"/>
+      <c r="R14" s="16"/>
+      <c r="S14" s="16"/>
+      <c r="T14" s="16"/>
+      <c r="U14" s="16"/>
+      <c r="V14" s="16"/>
+      <c r="W14" s="16"/>
+      <c r="X14" s="16"/>
+      <c r="Y14" s="16"/>
       <c r="Z14" s="3">
         <v>2.0</v>
       </c>
@@ -1560,8 +1599,8 @@
         <v>34</v>
       </c>
       <c r="B15" s="12">
-        <f> Z6 +Z5 +Z8 +Z7 +Z4 +Z11 + Z6 +Z6 +Z7</f>
-        <v>85</v>
+        <f> Z6 +Z5 +Z8 +Z7 +Z4 +Z11 + Z6 +Z6 +Z7 +Z7</f>
+        <v>94</v>
       </c>
       <c r="C15" s="12" t="s">
         <v>33</v>
@@ -1608,14 +1647,18 @@
       <c r="Q15" s="13">
         <v>7.0</v>
       </c>
-      <c r="R15" s="15"/>
-      <c r="S15" s="15"/>
-      <c r="T15" s="15"/>
-      <c r="U15" s="15"/>
-      <c r="V15" s="15"/>
-      <c r="W15" s="15"/>
-      <c r="X15" s="15"/>
-      <c r="Y15" s="15"/>
+      <c r="R15" s="12">
+        <v>16.0</v>
+      </c>
+      <c r="S15" s="13">
+        <v>7.0</v>
+      </c>
+      <c r="T15" s="16"/>
+      <c r="U15" s="16"/>
+      <c r="V15" s="16"/>
+      <c r="W15" s="16"/>
+      <c r="X15" s="16"/>
+      <c r="Y15" s="16"/>
       <c r="Z15" s="3">
         <v>1.0</v>
       </c>
@@ -1624,31 +1667,31 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="15"/>
-      <c r="B16" s="15"/>
-      <c r="C16" s="15"/>
-      <c r="D16" s="15"/>
-      <c r="E16" s="15"/>
-      <c r="F16" s="15"/>
-      <c r="G16" s="15"/>
-      <c r="H16" s="15"/>
-      <c r="I16" s="15"/>
-      <c r="J16" s="15"/>
-      <c r="K16" s="15"/>
-      <c r="L16" s="15"/>
-      <c r="M16" s="15"/>
-      <c r="N16" s="15"/>
-      <c r="O16" s="15"/>
-      <c r="P16" s="15"/>
-      <c r="Q16" s="15"/>
-      <c r="R16" s="15"/>
-      <c r="S16" s="15"/>
-      <c r="T16" s="15"/>
-      <c r="U16" s="15"/>
-      <c r="V16" s="15"/>
-      <c r="W16" s="15"/>
-      <c r="X16" s="15"/>
-      <c r="Y16" s="15"/>
+      <c r="A16" s="16"/>
+      <c r="B16" s="16"/>
+      <c r="C16" s="16"/>
+      <c r="D16" s="16"/>
+      <c r="E16" s="16"/>
+      <c r="F16" s="16"/>
+      <c r="G16" s="16"/>
+      <c r="H16" s="16"/>
+      <c r="I16" s="16"/>
+      <c r="J16" s="16"/>
+      <c r="K16" s="16"/>
+      <c r="L16" s="16"/>
+      <c r="M16" s="16"/>
+      <c r="N16" s="16"/>
+      <c r="O16" s="16"/>
+      <c r="P16" s="16"/>
+      <c r="Q16" s="16"/>
+      <c r="R16" s="16"/>
+      <c r="S16" s="16"/>
+      <c r="T16" s="16"/>
+      <c r="U16" s="16"/>
+      <c r="V16" s="16"/>
+      <c r="W16" s="16"/>
+      <c r="X16" s="16"/>
+      <c r="Y16" s="16"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="13">
         <v>13.0</v>
@@ -1659,8 +1702,8 @@
         <v>35</v>
       </c>
       <c r="B17" s="12">
-        <f>Z12 +Z4 +Z3 +Z6 +Z12 +Z8 + Z7 + Z5 +Z7</f>
-        <v>84</v>
+        <f>Z12 +Z4 +Z3 +Z6 +Z12 +Z8 + Z7 + Z5 +Z7 +Z9 +Z4</f>
+        <v>104</v>
       </c>
       <c r="C17" s="12" t="s">
         <v>36</v>
@@ -1677,7 +1720,7 @@
       <c r="G17" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="H17" s="17">
+      <c r="H17" s="15">
         <v>3.0</v>
       </c>
       <c r="I17" s="13">
@@ -1707,45 +1750,49 @@
       <c r="Q17" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="R17" s="15"/>
-      <c r="S17" s="15"/>
-      <c r="T17" s="15"/>
-      <c r="U17" s="15"/>
-      <c r="V17" s="15"/>
-      <c r="W17" s="15"/>
-      <c r="X17" s="15"/>
-      <c r="Y17" s="15"/>
+      <c r="R17" s="13">
+        <v>9.0</v>
+      </c>
+      <c r="S17" s="13">
+        <v>4.0</v>
+      </c>
+      <c r="T17" s="16"/>
+      <c r="U17" s="16"/>
+      <c r="V17" s="16"/>
+      <c r="W17" s="16"/>
+      <c r="X17" s="16"/>
+      <c r="Y17" s="16"/>
       <c r="Z17" s="3"/>
       <c r="AA17" s="13">
         <v>14.0</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="15"/>
-      <c r="B18" s="15"/>
-      <c r="C18" s="15"/>
-      <c r="D18" s="15"/>
-      <c r="E18" s="15"/>
-      <c r="F18" s="15"/>
-      <c r="G18" s="15"/>
-      <c r="H18" s="15"/>
-      <c r="I18" s="15"/>
-      <c r="J18" s="15"/>
-      <c r="K18" s="15"/>
-      <c r="L18" s="15"/>
-      <c r="M18" s="15"/>
-      <c r="N18" s="15"/>
-      <c r="O18" s="15"/>
-      <c r="P18" s="15"/>
-      <c r="Q18" s="15"/>
-      <c r="R18" s="15"/>
-      <c r="S18" s="15"/>
-      <c r="T18" s="15"/>
-      <c r="U18" s="15"/>
-      <c r="V18" s="15"/>
-      <c r="W18" s="15"/>
-      <c r="X18" s="15"/>
-      <c r="Y18" s="15"/>
+      <c r="A18" s="16"/>
+      <c r="B18" s="16"/>
+      <c r="C18" s="16"/>
+      <c r="D18" s="16"/>
+      <c r="E18" s="16"/>
+      <c r="F18" s="16"/>
+      <c r="G18" s="16"/>
+      <c r="H18" s="16"/>
+      <c r="I18" s="16"/>
+      <c r="J18" s="16"/>
+      <c r="K18" s="16"/>
+      <c r="L18" s="16"/>
+      <c r="M18" s="16"/>
+      <c r="N18" s="16"/>
+      <c r="O18" s="16"/>
+      <c r="P18" s="16"/>
+      <c r="Q18" s="16"/>
+      <c r="R18" s="16"/>
+      <c r="S18" s="16"/>
+      <c r="T18" s="16"/>
+      <c r="U18" s="16"/>
+      <c r="V18" s="16"/>
+      <c r="W18" s="16"/>
+      <c r="X18" s="16"/>
+      <c r="Y18" s="16"/>
       <c r="Z18" s="3"/>
       <c r="AA18" s="13">
         <v>15.0</v>
@@ -1756,8 +1803,8 @@
         <v>37</v>
       </c>
       <c r="B19" s="12">
-        <f> Z8 + Z2 +Z5 +Z4 +Z4 +Z4 +Z2 +Z7 + Z12 + Z13 +Z12</f>
-        <v>118</v>
+        <f> Z8 + Z2 +Z5 +Z4 +Z4 +Z4 +Z2 +Z7 + Z12 + Z13 +Z12 +Z11</f>
+        <v>123</v>
       </c>
       <c r="C19" s="12" t="s">
         <v>36</v>
@@ -1765,7 +1812,7 @@
       <c r="D19" s="13">
         <v>8.0</v>
       </c>
-      <c r="E19" s="16">
+      <c r="E19" s="17">
         <v>2.0</v>
       </c>
       <c r="F19" s="13">
@@ -1804,52 +1851,56 @@
       <c r="Q19" s="13">
         <v>12.0</v>
       </c>
-      <c r="R19" s="15"/>
-      <c r="S19" s="15"/>
-      <c r="T19" s="15"/>
-      <c r="U19" s="15"/>
-      <c r="V19" s="15"/>
-      <c r="W19" s="15"/>
-      <c r="X19" s="15"/>
-      <c r="Y19" s="15"/>
+      <c r="R19" s="13">
+        <v>11.0</v>
+      </c>
+      <c r="S19" s="12">
+        <v>16.0</v>
+      </c>
+      <c r="T19" s="16"/>
+      <c r="U19" s="16"/>
+      <c r="V19" s="16"/>
+      <c r="W19" s="16"/>
+      <c r="X19" s="16"/>
+      <c r="Y19" s="16"/>
       <c r="AA19" s="14" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="15"/>
-      <c r="B20" s="15"/>
-      <c r="C20" s="15"/>
-      <c r="D20" s="15"/>
-      <c r="E20" s="15"/>
-      <c r="F20" s="15"/>
-      <c r="G20" s="15"/>
-      <c r="H20" s="15"/>
-      <c r="I20" s="15"/>
-      <c r="J20" s="15"/>
-      <c r="K20" s="15"/>
-      <c r="L20" s="15"/>
-      <c r="M20" s="15"/>
-      <c r="N20" s="15"/>
-      <c r="O20" s="15"/>
-      <c r="P20" s="15"/>
-      <c r="Q20" s="15"/>
-      <c r="R20" s="15"/>
-      <c r="S20" s="15"/>
-      <c r="T20" s="15"/>
-      <c r="U20" s="15"/>
-      <c r="V20" s="15"/>
-      <c r="W20" s="15"/>
-      <c r="X20" s="15"/>
-      <c r="Y20" s="15"/>
+      <c r="A20" s="16"/>
+      <c r="B20" s="16"/>
+      <c r="C20" s="16"/>
+      <c r="D20" s="16"/>
+      <c r="E20" s="16"/>
+      <c r="F20" s="16"/>
+      <c r="G20" s="16"/>
+      <c r="H20" s="16"/>
+      <c r="I20" s="16"/>
+      <c r="J20" s="16"/>
+      <c r="K20" s="16"/>
+      <c r="L20" s="16"/>
+      <c r="M20" s="16"/>
+      <c r="N20" s="16"/>
+      <c r="O20" s="16"/>
+      <c r="P20" s="16"/>
+      <c r="Q20" s="16"/>
+      <c r="R20" s="16"/>
+      <c r="S20" s="16"/>
+      <c r="T20" s="16"/>
+      <c r="U20" s="16"/>
+      <c r="V20" s="16"/>
+      <c r="W20" s="16"/>
+      <c r="X20" s="16"/>
+      <c r="Y20" s="16"/>
     </row>
     <row r="21">
       <c r="A21" s="12" t="s">
         <v>38</v>
       </c>
       <c r="B21" s="12">
-        <f>Z2 +Z2 +Z1 +Z1 +Z5+Z2 + Z14 + Z15 +Z4</f>
-        <v>137</v>
+        <f>Z2 +Z2 +Z1 +Z1 +Z5+Z2 + Z14 + Z15 +Z4 +Z8 +Z5</f>
+        <v>156</v>
       </c>
       <c r="C21" s="12" t="s">
         <v>39</v>
@@ -1860,10 +1911,10 @@
       <c r="E21" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="F21" s="16">
+      <c r="F21" s="17">
         <v>2.0</v>
       </c>
-      <c r="G21" s="16">
+      <c r="G21" s="17">
         <v>2.0</v>
       </c>
       <c r="H21" s="14" t="s">
@@ -1896,41 +1947,45 @@
       <c r="Q21" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="R21" s="15"/>
-      <c r="S21" s="15"/>
-      <c r="T21" s="15"/>
-      <c r="U21" s="15"/>
-      <c r="V21" s="15"/>
-      <c r="W21" s="15"/>
-      <c r="X21" s="15"/>
-      <c r="Y21" s="15"/>
+      <c r="R21" s="13">
+        <v>8.0</v>
+      </c>
+      <c r="S21" s="13">
+        <v>5.0</v>
+      </c>
+      <c r="T21" s="16"/>
+      <c r="U21" s="16"/>
+      <c r="V21" s="16"/>
+      <c r="W21" s="16"/>
+      <c r="X21" s="16"/>
+      <c r="Y21" s="16"/>
     </row>
     <row r="22">
-      <c r="A22" s="15"/>
-      <c r="B22" s="15"/>
-      <c r="C22" s="15"/>
-      <c r="D22" s="15"/>
-      <c r="E22" s="15"/>
-      <c r="F22" s="15"/>
-      <c r="G22" s="15"/>
-      <c r="H22" s="15"/>
-      <c r="I22" s="15"/>
-      <c r="J22" s="15"/>
-      <c r="K22" s="15"/>
-      <c r="L22" s="15"/>
-      <c r="M22" s="15"/>
-      <c r="N22" s="15"/>
-      <c r="O22" s="15"/>
-      <c r="P22" s="15"/>
-      <c r="Q22" s="15"/>
-      <c r="R22" s="15"/>
-      <c r="S22" s="15"/>
-      <c r="T22" s="15"/>
-      <c r="U22" s="15"/>
-      <c r="V22" s="15"/>
-      <c r="W22" s="15"/>
-      <c r="X22" s="15"/>
-      <c r="Y22" s="15"/>
+      <c r="A22" s="16"/>
+      <c r="B22" s="16"/>
+      <c r="C22" s="16"/>
+      <c r="D22" s="16"/>
+      <c r="E22" s="16"/>
+      <c r="F22" s="16"/>
+      <c r="G22" s="16"/>
+      <c r="H22" s="16"/>
+      <c r="I22" s="16"/>
+      <c r="J22" s="16"/>
+      <c r="K22" s="16"/>
+      <c r="L22" s="16"/>
+      <c r="M22" s="16"/>
+      <c r="N22" s="16"/>
+      <c r="O22" s="16"/>
+      <c r="P22" s="16"/>
+      <c r="Q22" s="16"/>
+      <c r="R22" s="16"/>
+      <c r="S22" s="16"/>
+      <c r="T22" s="16"/>
+      <c r="U22" s="16"/>
+      <c r="V22" s="16"/>
+      <c r="W22" s="16"/>
+      <c r="X22" s="16"/>
+      <c r="Y22" s="16"/>
       <c r="Z22" s="19"/>
     </row>
     <row r="23">
@@ -1938,8 +1993,8 @@
         <v>40</v>
       </c>
       <c r="B23" s="12">
-        <f>Z9 +Z1 +Z10 +Z1 + Z4 + Z4 +Z8 +Z5</f>
-        <v>108</v>
+        <f>Z9 +Z1 +Z10 +Z1 + Z4 + Z4 +Z8 +Z5 +Z2 +Z10</f>
+        <v>134</v>
       </c>
       <c r="C23" s="12" t="s">
         <v>39</v>
@@ -1986,42 +2041,46 @@
       <c r="Q23" s="13">
         <v>5.0</v>
       </c>
-      <c r="R23" s="15"/>
-      <c r="S23" s="15"/>
-      <c r="T23" s="15"/>
-      <c r="U23" s="15"/>
-      <c r="V23" s="15"/>
-      <c r="W23" s="15"/>
-      <c r="X23" s="15"/>
-      <c r="Y23" s="15"/>
+      <c r="R23" s="18">
+        <v>2.0</v>
+      </c>
+      <c r="S23" s="13">
+        <v>10.0</v>
+      </c>
+      <c r="T23" s="16"/>
+      <c r="U23" s="16"/>
+      <c r="V23" s="16"/>
+      <c r="W23" s="16"/>
+      <c r="X23" s="16"/>
+      <c r="Y23" s="16"/>
       <c r="Z23" s="19"/>
     </row>
     <row r="24">
-      <c r="A24" s="15"/>
-      <c r="B24" s="15"/>
-      <c r="C24" s="15"/>
-      <c r="D24" s="15"/>
-      <c r="E24" s="15"/>
-      <c r="F24" s="15"/>
-      <c r="G24" s="15"/>
-      <c r="H24" s="15"/>
-      <c r="I24" s="15"/>
-      <c r="J24" s="15"/>
-      <c r="K24" s="15"/>
-      <c r="L24" s="15"/>
-      <c r="M24" s="15"/>
-      <c r="N24" s="15"/>
-      <c r="O24" s="15"/>
-      <c r="P24" s="15"/>
-      <c r="Q24" s="15"/>
-      <c r="R24" s="15"/>
-      <c r="S24" s="15"/>
-      <c r="T24" s="15"/>
-      <c r="U24" s="15"/>
-      <c r="V24" s="15"/>
-      <c r="W24" s="15"/>
-      <c r="X24" s="15"/>
-      <c r="Y24" s="15"/>
+      <c r="A24" s="16"/>
+      <c r="B24" s="16"/>
+      <c r="C24" s="16"/>
+      <c r="D24" s="16"/>
+      <c r="E24" s="16"/>
+      <c r="F24" s="16"/>
+      <c r="G24" s="16"/>
+      <c r="H24" s="16"/>
+      <c r="I24" s="16"/>
+      <c r="J24" s="16"/>
+      <c r="K24" s="16"/>
+      <c r="L24" s="16"/>
+      <c r="M24" s="16"/>
+      <c r="N24" s="16"/>
+      <c r="O24" s="16"/>
+      <c r="P24" s="16"/>
+      <c r="Q24" s="16"/>
+      <c r="R24" s="16"/>
+      <c r="S24" s="16"/>
+      <c r="T24" s="16"/>
+      <c r="U24" s="16"/>
+      <c r="V24" s="16"/>
+      <c r="W24" s="16"/>
+      <c r="X24" s="16"/>
+      <c r="Y24" s="16"/>
       <c r="Z24" s="19"/>
     </row>
     <row r="25">
@@ -2029,8 +2088,8 @@
         <v>41</v>
       </c>
       <c r="B25" s="12">
-        <f> Z9 + Z1 +Z8 +Z3 +Z3 +Z8 +Z5 + Z11 + Z1 + Z13</f>
-        <v>124</v>
+        <f> Z9 + Z1 +Z8 +Z3 +Z3 +Z8 +Z5 + Z11 + Z1 + Z13 +Z7</f>
+        <v>133</v>
       </c>
       <c r="C25" s="12" t="s">
         <v>42</v>
@@ -2044,7 +2103,7 @@
       <c r="F25" s="13">
         <v>8.0</v>
       </c>
-      <c r="G25" s="17">
+      <c r="G25" s="15">
         <v>3.0</v>
       </c>
       <c r="H25" s="14" t="s">
@@ -2077,42 +2136,46 @@
       <c r="Q25" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="R25" s="15"/>
-      <c r="S25" s="15"/>
-      <c r="T25" s="15"/>
-      <c r="U25" s="15"/>
-      <c r="V25" s="15"/>
-      <c r="W25" s="15"/>
-      <c r="X25" s="15"/>
-      <c r="Y25" s="15"/>
+      <c r="R25" s="13">
+        <v>7.0</v>
+      </c>
+      <c r="S25" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="T25" s="16"/>
+      <c r="U25" s="16"/>
+      <c r="V25" s="16"/>
+      <c r="W25" s="16"/>
+      <c r="X25" s="16"/>
+      <c r="Y25" s="16"/>
       <c r="Z25" s="19"/>
     </row>
     <row r="26">
-      <c r="A26" s="15"/>
-      <c r="B26" s="15"/>
-      <c r="C26" s="15"/>
-      <c r="D26" s="15"/>
-      <c r="E26" s="15"/>
-      <c r="F26" s="15"/>
-      <c r="G26" s="15"/>
-      <c r="H26" s="15"/>
-      <c r="I26" s="15"/>
-      <c r="J26" s="15"/>
-      <c r="K26" s="15"/>
-      <c r="L26" s="15"/>
-      <c r="M26" s="15"/>
-      <c r="N26" s="15"/>
-      <c r="O26" s="15"/>
-      <c r="P26" s="15"/>
-      <c r="Q26" s="15"/>
-      <c r="R26" s="15"/>
-      <c r="S26" s="15"/>
-      <c r="T26" s="15"/>
-      <c r="U26" s="15"/>
-      <c r="V26" s="15"/>
-      <c r="W26" s="15"/>
-      <c r="X26" s="15"/>
-      <c r="Y26" s="15"/>
+      <c r="A26" s="16"/>
+      <c r="B26" s="16"/>
+      <c r="C26" s="16"/>
+      <c r="D26" s="16"/>
+      <c r="E26" s="16"/>
+      <c r="F26" s="16"/>
+      <c r="G26" s="16"/>
+      <c r="H26" s="16"/>
+      <c r="I26" s="16"/>
+      <c r="J26" s="16"/>
+      <c r="K26" s="16"/>
+      <c r="L26" s="16"/>
+      <c r="M26" s="16"/>
+      <c r="N26" s="16"/>
+      <c r="O26" s="16"/>
+      <c r="P26" s="16"/>
+      <c r="Q26" s="16"/>
+      <c r="R26" s="16"/>
+      <c r="S26" s="16"/>
+      <c r="T26" s="16"/>
+      <c r="U26" s="16"/>
+      <c r="V26" s="16"/>
+      <c r="W26" s="16"/>
+      <c r="X26" s="16"/>
+      <c r="Y26" s="16"/>
       <c r="Z26" s="19"/>
     </row>
     <row r="27">
@@ -2120,8 +2183,8 @@
         <v>43</v>
       </c>
       <c r="B27" s="12">
-        <f>Z11 +Z6 +Z6 +Z5 +Z9 +Z2 +Z3 + Z10 + Z10 +Z13</f>
-        <v>94</v>
+        <f>Z11 +Z6 +Z6 +Z5 +Z9 +Z2 +Z3 + Z10 + Z10 +Z13 +Z6 +Z8</f>
+        <v>112</v>
       </c>
       <c r="C27" s="12" t="s">
         <v>42</v>
@@ -2147,7 +2210,7 @@
       <c r="J27" s="18">
         <v>2.0</v>
       </c>
-      <c r="K27" s="17">
+      <c r="K27" s="15">
         <v>3.0</v>
       </c>
       <c r="L27" s="14" t="s">
@@ -2168,42 +2231,46 @@
       <c r="Q27" s="13">
         <v>13.0</v>
       </c>
-      <c r="R27" s="15"/>
-      <c r="S27" s="15"/>
-      <c r="T27" s="15"/>
-      <c r="U27" s="15"/>
-      <c r="V27" s="15"/>
-      <c r="W27" s="15"/>
-      <c r="X27" s="15"/>
-      <c r="Y27" s="15"/>
+      <c r="R27" s="13">
+        <v>6.0</v>
+      </c>
+      <c r="S27" s="13">
+        <v>8.0</v>
+      </c>
+      <c r="T27" s="16"/>
+      <c r="U27" s="16"/>
+      <c r="V27" s="16"/>
+      <c r="W27" s="16"/>
+      <c r="X27" s="16"/>
+      <c r="Y27" s="16"/>
       <c r="Z27" s="19"/>
     </row>
     <row r="28">
-      <c r="A28" s="15"/>
-      <c r="B28" s="15"/>
-      <c r="C28" s="15"/>
-      <c r="D28" s="15"/>
-      <c r="E28" s="15"/>
-      <c r="F28" s="15"/>
-      <c r="G28" s="15"/>
-      <c r="H28" s="15"/>
-      <c r="I28" s="15"/>
-      <c r="J28" s="15"/>
-      <c r="K28" s="15"/>
-      <c r="L28" s="15"/>
-      <c r="M28" s="15"/>
-      <c r="N28" s="15"/>
-      <c r="O28" s="15"/>
-      <c r="P28" s="15"/>
-      <c r="Q28" s="15"/>
-      <c r="R28" s="15"/>
-      <c r="S28" s="15"/>
-      <c r="T28" s="15"/>
-      <c r="U28" s="15"/>
-      <c r="V28" s="15"/>
-      <c r="W28" s="15"/>
-      <c r="X28" s="15"/>
-      <c r="Y28" s="15"/>
+      <c r="A28" s="16"/>
+      <c r="B28" s="16"/>
+      <c r="C28" s="16"/>
+      <c r="D28" s="16"/>
+      <c r="E28" s="16"/>
+      <c r="F28" s="16"/>
+      <c r="G28" s="16"/>
+      <c r="H28" s="16"/>
+      <c r="I28" s="16"/>
+      <c r="J28" s="16"/>
+      <c r="K28" s="16"/>
+      <c r="L28" s="16"/>
+      <c r="M28" s="16"/>
+      <c r="N28" s="16"/>
+      <c r="O28" s="16"/>
+      <c r="P28" s="16"/>
+      <c r="Q28" s="16"/>
+      <c r="R28" s="16"/>
+      <c r="S28" s="16"/>
+      <c r="T28" s="16"/>
+      <c r="U28" s="16"/>
+      <c r="V28" s="16"/>
+      <c r="W28" s="16"/>
+      <c r="X28" s="16"/>
+      <c r="Y28" s="16"/>
       <c r="Z28" s="19"/>
     </row>
     <row r="29">
@@ -2211,8 +2278,8 @@
         <v>44</v>
       </c>
       <c r="B29" s="12">
-        <f>Z15 +Z13</f>
-        <v>4</v>
+        <f>Z15 +Z13 +Z14</f>
+        <v>6</v>
       </c>
       <c r="C29" s="12" t="s">
         <v>45</v>
@@ -2259,42 +2326,46 @@
       <c r="Q29" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="R29" s="15"/>
-      <c r="S29" s="15"/>
-      <c r="T29" s="15"/>
-      <c r="U29" s="15"/>
-      <c r="V29" s="15"/>
-      <c r="W29" s="15"/>
-      <c r="X29" s="15"/>
-      <c r="Y29" s="15"/>
+      <c r="R29" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="S29" s="13">
+        <v>14.0</v>
+      </c>
+      <c r="T29" s="16"/>
+      <c r="U29" s="16"/>
+      <c r="V29" s="16"/>
+      <c r="W29" s="16"/>
+      <c r="X29" s="16"/>
+      <c r="Y29" s="16"/>
       <c r="Z29" s="19"/>
     </row>
     <row r="30">
-      <c r="A30" s="15"/>
-      <c r="B30" s="15"/>
-      <c r="C30" s="15"/>
-      <c r="D30" s="15"/>
-      <c r="E30" s="15"/>
-      <c r="F30" s="15"/>
-      <c r="G30" s="15"/>
-      <c r="H30" s="15"/>
-      <c r="I30" s="15"/>
-      <c r="J30" s="15"/>
-      <c r="K30" s="15"/>
-      <c r="L30" s="15"/>
-      <c r="M30" s="15"/>
-      <c r="N30" s="15"/>
-      <c r="O30" s="15"/>
-      <c r="P30" s="15"/>
-      <c r="Q30" s="15"/>
-      <c r="R30" s="15"/>
-      <c r="S30" s="15"/>
-      <c r="T30" s="15"/>
-      <c r="U30" s="15"/>
-      <c r="V30" s="15"/>
-      <c r="W30" s="15"/>
-      <c r="X30" s="15"/>
-      <c r="Y30" s="15"/>
+      <c r="A30" s="16"/>
+      <c r="B30" s="16"/>
+      <c r="C30" s="16"/>
+      <c r="D30" s="16"/>
+      <c r="E30" s="16"/>
+      <c r="F30" s="16"/>
+      <c r="G30" s="16"/>
+      <c r="H30" s="16"/>
+      <c r="I30" s="16"/>
+      <c r="J30" s="16"/>
+      <c r="K30" s="16"/>
+      <c r="L30" s="16"/>
+      <c r="M30" s="16"/>
+      <c r="N30" s="16"/>
+      <c r="O30" s="16"/>
+      <c r="P30" s="16"/>
+      <c r="Q30" s="16"/>
+      <c r="R30" s="16"/>
+      <c r="S30" s="16"/>
+      <c r="T30" s="16"/>
+      <c r="U30" s="16"/>
+      <c r="V30" s="16"/>
+      <c r="W30" s="16"/>
+      <c r="X30" s="16"/>
+      <c r="Y30" s="16"/>
       <c r="Z30" s="19"/>
     </row>
     <row r="31">
@@ -2350,42 +2421,46 @@
       <c r="Q31" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="R31" s="15"/>
-      <c r="S31" s="15"/>
-      <c r="T31" s="15"/>
-      <c r="U31" s="15"/>
-      <c r="V31" s="15"/>
-      <c r="W31" s="15"/>
-      <c r="X31" s="15"/>
-      <c r="Y31" s="15"/>
+      <c r="R31" s="12">
+        <v>20.0</v>
+      </c>
+      <c r="S31" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="T31" s="16"/>
+      <c r="U31" s="16"/>
+      <c r="V31" s="16"/>
+      <c r="W31" s="16"/>
+      <c r="X31" s="16"/>
+      <c r="Y31" s="16"/>
       <c r="Z31" s="19"/>
     </row>
     <row r="32">
-      <c r="A32" s="15"/>
-      <c r="B32" s="15"/>
-      <c r="C32" s="15"/>
-      <c r="D32" s="15"/>
-      <c r="E32" s="15"/>
-      <c r="F32" s="15"/>
-      <c r="G32" s="15"/>
-      <c r="H32" s="15"/>
-      <c r="I32" s="15"/>
-      <c r="J32" s="15"/>
-      <c r="K32" s="15"/>
-      <c r="L32" s="15"/>
-      <c r="M32" s="15"/>
-      <c r="N32" s="15"/>
-      <c r="O32" s="15"/>
-      <c r="P32" s="15"/>
-      <c r="Q32" s="15"/>
-      <c r="R32" s="15"/>
-      <c r="S32" s="15"/>
-      <c r="T32" s="15"/>
-      <c r="U32" s="15"/>
-      <c r="V32" s="15"/>
-      <c r="W32" s="15"/>
-      <c r="X32" s="15"/>
-      <c r="Y32" s="15"/>
+      <c r="A32" s="16"/>
+      <c r="B32" s="16"/>
+      <c r="C32" s="16"/>
+      <c r="D32" s="16"/>
+      <c r="E32" s="16"/>
+      <c r="F32" s="16"/>
+      <c r="G32" s="16"/>
+      <c r="H32" s="16"/>
+      <c r="I32" s="16"/>
+      <c r="J32" s="16"/>
+      <c r="K32" s="16"/>
+      <c r="L32" s="16"/>
+      <c r="M32" s="16"/>
+      <c r="N32" s="16"/>
+      <c r="O32" s="16"/>
+      <c r="P32" s="16"/>
+      <c r="Q32" s="16"/>
+      <c r="R32" s="16"/>
+      <c r="S32" s="16"/>
+      <c r="T32" s="16"/>
+      <c r="U32" s="16"/>
+      <c r="V32" s="16"/>
+      <c r="W32" s="16"/>
+      <c r="X32" s="16"/>
+      <c r="Y32" s="16"/>
       <c r="Z32" s="19"/>
     </row>
     <row r="33">
@@ -2393,8 +2468,8 @@
         <v>47</v>
       </c>
       <c r="B33" s="12">
-        <f> Z1 +Z4 +Z7 +Z12 +Z1 +Z2 +Z11 +Z1 +Z1 + Z5 + Z1 +Z1 +Z3</f>
-        <v>228</v>
+        <f> Z1 +Z4 +Z7 +Z12 +Z1 +Z2 +Z11 +Z1 +Z1 + Z5 + Z1 +Z1 +Z3 +Z1</f>
+        <v>253</v>
       </c>
       <c r="C33" s="12" t="s">
         <v>48</v>
@@ -2438,45 +2513,49 @@
       <c r="P33" s="11">
         <v>1.0</v>
       </c>
-      <c r="Q33" s="17">
+      <c r="Q33" s="15">
         <v>3.0</v>
       </c>
-      <c r="R33" s="15"/>
-      <c r="S33" s="15"/>
-      <c r="T33" s="15"/>
-      <c r="U33" s="15"/>
-      <c r="V33" s="15"/>
-      <c r="W33" s="15"/>
-      <c r="X33" s="15"/>
-      <c r="Y33" s="15"/>
+      <c r="R33" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="S33" s="11">
+        <v>1.0</v>
+      </c>
+      <c r="T33" s="16"/>
+      <c r="U33" s="16"/>
+      <c r="V33" s="16"/>
+      <c r="W33" s="16"/>
+      <c r="X33" s="16"/>
+      <c r="Y33" s="16"/>
       <c r="Z33" s="19"/>
     </row>
     <row r="34">
-      <c r="A34" s="15"/>
-      <c r="B34" s="15"/>
-      <c r="C34" s="15"/>
-      <c r="D34" s="15"/>
-      <c r="E34" s="15"/>
-      <c r="F34" s="15"/>
-      <c r="G34" s="15"/>
-      <c r="H34" s="15"/>
-      <c r="I34" s="15"/>
-      <c r="J34" s="15"/>
-      <c r="K34" s="15"/>
-      <c r="L34" s="15"/>
-      <c r="M34" s="15"/>
-      <c r="N34" s="15"/>
-      <c r="O34" s="15"/>
-      <c r="P34" s="15"/>
-      <c r="Q34" s="15"/>
-      <c r="R34" s="15"/>
-      <c r="S34" s="15"/>
-      <c r="T34" s="15"/>
-      <c r="U34" s="15"/>
-      <c r="V34" s="15"/>
-      <c r="W34" s="15"/>
-      <c r="X34" s="15"/>
-      <c r="Y34" s="15"/>
+      <c r="A34" s="16"/>
+      <c r="B34" s="16"/>
+      <c r="C34" s="16"/>
+      <c r="D34" s="16"/>
+      <c r="E34" s="16"/>
+      <c r="F34" s="16"/>
+      <c r="G34" s="16"/>
+      <c r="H34" s="16"/>
+      <c r="I34" s="16"/>
+      <c r="J34" s="16"/>
+      <c r="K34" s="16"/>
+      <c r="L34" s="16"/>
+      <c r="M34" s="16"/>
+      <c r="N34" s="16"/>
+      <c r="O34" s="16"/>
+      <c r="P34" s="16"/>
+      <c r="Q34" s="16"/>
+      <c r="R34" s="16"/>
+      <c r="S34" s="16"/>
+      <c r="T34" s="16"/>
+      <c r="U34" s="16"/>
+      <c r="V34" s="16"/>
+      <c r="W34" s="16"/>
+      <c r="X34" s="16"/>
+      <c r="Y34" s="16"/>
       <c r="Z34" s="19"/>
     </row>
     <row r="35">
@@ -2490,7 +2569,7 @@
       <c r="C35" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="D35" s="16">
+      <c r="D35" s="17">
         <v>2.0</v>
       </c>
       <c r="E35" s="14" t="s">
@@ -2532,42 +2611,46 @@
       <c r="Q35" s="18">
         <v>2.0</v>
       </c>
-      <c r="R35" s="15"/>
-      <c r="S35" s="15"/>
-      <c r="T35" s="15"/>
-      <c r="U35" s="15"/>
-      <c r="V35" s="15"/>
-      <c r="W35" s="15"/>
-      <c r="X35" s="15"/>
-      <c r="Y35" s="15"/>
+      <c r="R35" s="12">
+        <v>19.0</v>
+      </c>
+      <c r="S35" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="T35" s="16"/>
+      <c r="U35" s="16"/>
+      <c r="V35" s="16"/>
+      <c r="W35" s="16"/>
+      <c r="X35" s="16"/>
+      <c r="Y35" s="16"/>
       <c r="Z35" s="19"/>
     </row>
     <row r="36">
-      <c r="A36" s="15"/>
-      <c r="B36" s="15"/>
-      <c r="C36" s="15"/>
-      <c r="D36" s="15"/>
-      <c r="E36" s="15"/>
-      <c r="F36" s="15"/>
-      <c r="G36" s="15"/>
-      <c r="H36" s="15"/>
-      <c r="I36" s="15"/>
-      <c r="J36" s="15"/>
-      <c r="K36" s="15"/>
-      <c r="L36" s="15"/>
-      <c r="M36" s="15"/>
-      <c r="N36" s="15"/>
-      <c r="O36" s="15"/>
-      <c r="P36" s="15"/>
-      <c r="Q36" s="15"/>
-      <c r="R36" s="15"/>
-      <c r="S36" s="15"/>
-      <c r="T36" s="15"/>
-      <c r="U36" s="15"/>
-      <c r="V36" s="15"/>
-      <c r="W36" s="15"/>
-      <c r="X36" s="15"/>
-      <c r="Y36" s="15"/>
+      <c r="A36" s="16"/>
+      <c r="B36" s="16"/>
+      <c r="C36" s="16"/>
+      <c r="D36" s="16"/>
+      <c r="E36" s="16"/>
+      <c r="F36" s="16"/>
+      <c r="G36" s="16"/>
+      <c r="H36" s="16"/>
+      <c r="I36" s="16"/>
+      <c r="J36" s="16"/>
+      <c r="K36" s="16"/>
+      <c r="L36" s="16"/>
+      <c r="M36" s="16"/>
+      <c r="N36" s="16"/>
+      <c r="O36" s="16"/>
+      <c r="P36" s="16"/>
+      <c r="Q36" s="16"/>
+      <c r="R36" s="16"/>
+      <c r="S36" s="16"/>
+      <c r="T36" s="16"/>
+      <c r="U36" s="16"/>
+      <c r="V36" s="16"/>
+      <c r="W36" s="16"/>
+      <c r="X36" s="16"/>
+      <c r="Y36" s="16"/>
       <c r="Z36" s="19"/>
     </row>
     <row r="37">
@@ -2623,50 +2706,54 @@
       <c r="Q37" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="R37" s="15"/>
-      <c r="S37" s="15"/>
-      <c r="T37" s="15"/>
-      <c r="U37" s="15"/>
-      <c r="V37" s="15"/>
-      <c r="W37" s="15"/>
-      <c r="X37" s="15"/>
-      <c r="Y37" s="15"/>
+      <c r="R37" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="S37" s="12">
+        <v>17.0</v>
+      </c>
+      <c r="T37" s="16"/>
+      <c r="U37" s="16"/>
+      <c r="V37" s="16"/>
+      <c r="W37" s="16"/>
+      <c r="X37" s="16"/>
+      <c r="Y37" s="16"/>
       <c r="Z37" s="19"/>
     </row>
     <row r="38">
-      <c r="A38" s="15"/>
-      <c r="B38" s="15"/>
-      <c r="C38" s="15"/>
-      <c r="D38" s="15"/>
-      <c r="E38" s="15"/>
-      <c r="F38" s="15"/>
-      <c r="G38" s="15"/>
-      <c r="H38" s="15"/>
-      <c r="I38" s="15"/>
-      <c r="J38" s="15"/>
-      <c r="K38" s="15"/>
-      <c r="L38" s="15"/>
-      <c r="M38" s="15"/>
-      <c r="N38" s="15"/>
-      <c r="O38" s="15"/>
-      <c r="P38" s="15"/>
-      <c r="Q38" s="15"/>
-      <c r="R38" s="15"/>
-      <c r="S38" s="15"/>
-      <c r="T38" s="15"/>
-      <c r="U38" s="15"/>
-      <c r="V38" s="15"/>
-      <c r="W38" s="15"/>
-      <c r="X38" s="15"/>
-      <c r="Y38" s="15"/>
+      <c r="A38" s="16"/>
+      <c r="B38" s="16"/>
+      <c r="C38" s="16"/>
+      <c r="D38" s="16"/>
+      <c r="E38" s="16"/>
+      <c r="F38" s="16"/>
+      <c r="G38" s="16"/>
+      <c r="H38" s="16"/>
+      <c r="I38" s="16"/>
+      <c r="J38" s="16"/>
+      <c r="K38" s="16"/>
+      <c r="L38" s="16"/>
+      <c r="M38" s="16"/>
+      <c r="N38" s="16"/>
+      <c r="O38" s="16"/>
+      <c r="P38" s="16"/>
+      <c r="Q38" s="16"/>
+      <c r="R38" s="16"/>
+      <c r="S38" s="16"/>
+      <c r="T38" s="16"/>
+      <c r="U38" s="16"/>
+      <c r="V38" s="16"/>
+      <c r="W38" s="16"/>
+      <c r="X38" s="16"/>
+      <c r="Y38" s="16"/>
     </row>
     <row r="39">
       <c r="A39" s="12" t="s">
         <v>52</v>
       </c>
       <c r="B39" s="12">
-        <f> Z10 +Z5 +Z8 +Z10 + Z5 + Z4 + Z10 +Z1</f>
-        <v>86</v>
+        <f> Z10 +Z5 +Z8 +Z10 + Z5 + Z4 + Z10 +Z1 +Z1</f>
+        <v>111</v>
       </c>
       <c r="C39" s="12" t="s">
         <v>51</v>
@@ -2713,41 +2800,45 @@
       <c r="Q39" s="11">
         <v>1.0</v>
       </c>
-      <c r="R39" s="15"/>
-      <c r="S39" s="15"/>
-      <c r="T39" s="15"/>
-      <c r="U39" s="15"/>
-      <c r="V39" s="15"/>
-      <c r="W39" s="15"/>
-      <c r="X39" s="15"/>
-      <c r="Y39" s="15"/>
+      <c r="R39" s="11">
+        <v>1.0</v>
+      </c>
+      <c r="S39" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="T39" s="16"/>
+      <c r="U39" s="16"/>
+      <c r="V39" s="16"/>
+      <c r="W39" s="16"/>
+      <c r="X39" s="16"/>
+      <c r="Y39" s="16"/>
     </row>
     <row r="40">
-      <c r="A40" s="15"/>
-      <c r="B40" s="15"/>
-      <c r="C40" s="15"/>
-      <c r="D40" s="15"/>
-      <c r="E40" s="15"/>
-      <c r="F40" s="15"/>
-      <c r="G40" s="15"/>
-      <c r="H40" s="15"/>
-      <c r="I40" s="15"/>
-      <c r="J40" s="15"/>
-      <c r="K40" s="15"/>
-      <c r="L40" s="15"/>
-      <c r="M40" s="15"/>
-      <c r="N40" s="15"/>
-      <c r="O40" s="15"/>
-      <c r="P40" s="15"/>
-      <c r="Q40" s="15"/>
-      <c r="R40" s="15"/>
-      <c r="S40" s="15"/>
-      <c r="T40" s="15"/>
-      <c r="U40" s="15"/>
-      <c r="V40" s="15"/>
-      <c r="W40" s="15"/>
-      <c r="X40" s="15"/>
-      <c r="Y40" s="15"/>
+      <c r="A40" s="16"/>
+      <c r="B40" s="16"/>
+      <c r="C40" s="16"/>
+      <c r="D40" s="16"/>
+      <c r="E40" s="16"/>
+      <c r="F40" s="16"/>
+      <c r="G40" s="16"/>
+      <c r="H40" s="16"/>
+      <c r="I40" s="16"/>
+      <c r="J40" s="16"/>
+      <c r="K40" s="16"/>
+      <c r="L40" s="16"/>
+      <c r="M40" s="16"/>
+      <c r="N40" s="16"/>
+      <c r="O40" s="16"/>
+      <c r="P40" s="16"/>
+      <c r="Q40" s="16"/>
+      <c r="R40" s="16"/>
+      <c r="S40" s="16"/>
+      <c r="T40" s="16"/>
+      <c r="U40" s="16"/>
+      <c r="V40" s="16"/>
+      <c r="W40" s="16"/>
+      <c r="X40" s="16"/>
+      <c r="Y40" s="16"/>
     </row>
     <row r="41">
       <c r="A41" s="12" t="s">
@@ -2802,41 +2893,45 @@
       <c r="Q41" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="R41" s="15"/>
-      <c r="S41" s="15"/>
-      <c r="T41" s="15"/>
-      <c r="U41" s="15"/>
-      <c r="V41" s="15"/>
-      <c r="W41" s="15"/>
-      <c r="X41" s="15"/>
-      <c r="Y41" s="15"/>
+      <c r="R41" s="12">
+        <v>18.0</v>
+      </c>
+      <c r="S41" s="12">
+        <v>18.0</v>
+      </c>
+      <c r="T41" s="16"/>
+      <c r="U41" s="16"/>
+      <c r="V41" s="16"/>
+      <c r="W41" s="16"/>
+      <c r="X41" s="16"/>
+      <c r="Y41" s="16"/>
     </row>
     <row r="42">
-      <c r="A42" s="15"/>
-      <c r="B42" s="15"/>
-      <c r="C42" s="15"/>
-      <c r="D42" s="15"/>
-      <c r="E42" s="15"/>
-      <c r="F42" s="15"/>
-      <c r="G42" s="15"/>
-      <c r="H42" s="15"/>
-      <c r="I42" s="15"/>
-      <c r="J42" s="15"/>
-      <c r="K42" s="15"/>
-      <c r="L42" s="15"/>
-      <c r="M42" s="15"/>
-      <c r="N42" s="15"/>
-      <c r="O42" s="15"/>
-      <c r="P42" s="15"/>
-      <c r="Q42" s="15"/>
-      <c r="R42" s="15"/>
-      <c r="S42" s="15"/>
-      <c r="T42" s="15"/>
-      <c r="U42" s="15"/>
-      <c r="V42" s="15"/>
-      <c r="W42" s="15"/>
-      <c r="X42" s="15"/>
-      <c r="Y42" s="15"/>
+      <c r="A42" s="16"/>
+      <c r="B42" s="16"/>
+      <c r="C42" s="16"/>
+      <c r="D42" s="16"/>
+      <c r="E42" s="16"/>
+      <c r="F42" s="16"/>
+      <c r="G42" s="16"/>
+      <c r="H42" s="16"/>
+      <c r="I42" s="16"/>
+      <c r="J42" s="16"/>
+      <c r="K42" s="16"/>
+      <c r="L42" s="16"/>
+      <c r="M42" s="16"/>
+      <c r="N42" s="16"/>
+      <c r="O42" s="16"/>
+      <c r="P42" s="16"/>
+      <c r="Q42" s="16"/>
+      <c r="R42" s="16"/>
+      <c r="S42" s="16"/>
+      <c r="T42" s="16"/>
+      <c r="U42" s="16"/>
+      <c r="V42" s="16"/>
+      <c r="W42" s="16"/>
+      <c r="X42" s="16"/>
+      <c r="Y42" s="16"/>
     </row>
     <row r="43">
       <c r="A43" s="12" t="s">
@@ -2890,41 +2985,45 @@
       <c r="Q43" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="R43" s="15"/>
-      <c r="S43" s="15"/>
-      <c r="T43" s="15"/>
-      <c r="U43" s="15"/>
-      <c r="V43" s="15"/>
-      <c r="W43" s="15"/>
-      <c r="X43" s="15"/>
-      <c r="Y43" s="15"/>
+      <c r="R43" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="S43" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="T43" s="16"/>
+      <c r="U43" s="16"/>
+      <c r="V43" s="16"/>
+      <c r="W43" s="16"/>
+      <c r="X43" s="16"/>
+      <c r="Y43" s="16"/>
     </row>
     <row r="44">
-      <c r="A44" s="15"/>
-      <c r="B44" s="15"/>
-      <c r="C44" s="15"/>
-      <c r="D44" s="15"/>
-      <c r="E44" s="15"/>
-      <c r="F44" s="15"/>
-      <c r="G44" s="15"/>
-      <c r="H44" s="15"/>
-      <c r="I44" s="15"/>
-      <c r="J44" s="15"/>
-      <c r="K44" s="15"/>
-      <c r="L44" s="15"/>
-      <c r="M44" s="15"/>
-      <c r="N44" s="15"/>
-      <c r="O44" s="15"/>
-      <c r="P44" s="15"/>
-      <c r="Q44" s="15"/>
-      <c r="R44" s="15"/>
-      <c r="S44" s="15"/>
-      <c r="T44" s="15"/>
-      <c r="U44" s="15"/>
-      <c r="V44" s="15"/>
-      <c r="W44" s="15"/>
-      <c r="X44" s="15"/>
-      <c r="Y44" s="15"/>
+      <c r="A44" s="16"/>
+      <c r="B44" s="16"/>
+      <c r="C44" s="16"/>
+      <c r="D44" s="16"/>
+      <c r="E44" s="16"/>
+      <c r="F44" s="16"/>
+      <c r="G44" s="16"/>
+      <c r="H44" s="16"/>
+      <c r="I44" s="16"/>
+      <c r="J44" s="16"/>
+      <c r="K44" s="16"/>
+      <c r="L44" s="16"/>
+      <c r="M44" s="16"/>
+      <c r="N44" s="16"/>
+      <c r="O44" s="16"/>
+      <c r="P44" s="16"/>
+      <c r="Q44" s="16"/>
+      <c r="R44" s="16"/>
+      <c r="S44" s="16"/>
+      <c r="T44" s="16"/>
+      <c r="U44" s="16"/>
+      <c r="V44" s="16"/>
+      <c r="W44" s="16"/>
+      <c r="X44" s="16"/>
+      <c r="Y44" s="16"/>
     </row>
     <row r="45">
       <c r="A45" s="12" t="s">
@@ -2979,41 +3078,45 @@
       <c r="Q45" s="13">
         <v>14.0</v>
       </c>
-      <c r="R45" s="15"/>
-      <c r="S45" s="15"/>
-      <c r="T45" s="15"/>
-      <c r="U45" s="15"/>
-      <c r="V45" s="15"/>
-      <c r="W45" s="15"/>
-      <c r="X45" s="15"/>
-      <c r="Y45" s="15"/>
+      <c r="R45" s="12">
+        <v>21.0</v>
+      </c>
+      <c r="S45" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="T45" s="16"/>
+      <c r="U45" s="16"/>
+      <c r="V45" s="16"/>
+      <c r="W45" s="16"/>
+      <c r="X45" s="16"/>
+      <c r="Y45" s="16"/>
     </row>
     <row r="46">
-      <c r="A46" s="15"/>
-      <c r="B46" s="15"/>
-      <c r="C46" s="15"/>
-      <c r="D46" s="15"/>
-      <c r="E46" s="15"/>
-      <c r="F46" s="15"/>
-      <c r="G46" s="15"/>
-      <c r="H46" s="15"/>
-      <c r="I46" s="15"/>
-      <c r="J46" s="15"/>
-      <c r="K46" s="15"/>
-      <c r="L46" s="15"/>
-      <c r="M46" s="15"/>
-      <c r="N46" s="15"/>
-      <c r="O46" s="15"/>
-      <c r="P46" s="15"/>
-      <c r="Q46" s="15"/>
-      <c r="R46" s="15"/>
-      <c r="S46" s="15"/>
-      <c r="T46" s="15"/>
-      <c r="U46" s="15"/>
-      <c r="V46" s="15"/>
-      <c r="W46" s="15"/>
-      <c r="X46" s="15"/>
-      <c r="Y46" s="15"/>
+      <c r="A46" s="16"/>
+      <c r="B46" s="16"/>
+      <c r="C46" s="16"/>
+      <c r="D46" s="16"/>
+      <c r="E46" s="16"/>
+      <c r="F46" s="16"/>
+      <c r="G46" s="16"/>
+      <c r="H46" s="16"/>
+      <c r="I46" s="16"/>
+      <c r="J46" s="16"/>
+      <c r="K46" s="16"/>
+      <c r="L46" s="16"/>
+      <c r="M46" s="16"/>
+      <c r="N46" s="16"/>
+      <c r="O46" s="16"/>
+      <c r="P46" s="16"/>
+      <c r="Q46" s="16"/>
+      <c r="R46" s="16"/>
+      <c r="S46" s="16"/>
+      <c r="T46" s="16"/>
+      <c r="U46" s="16"/>
+      <c r="V46" s="16"/>
+      <c r="W46" s="16"/>
+      <c r="X46" s="16"/>
+      <c r="Y46" s="16"/>
     </row>
     <row r="47">
       <c r="A47" s="12" t="s">
@@ -3068,49 +3171,53 @@
       <c r="Q47" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="R47" s="15"/>
-      <c r="S47" s="15"/>
-      <c r="T47" s="15"/>
-      <c r="U47" s="15"/>
-      <c r="V47" s="15"/>
-      <c r="W47" s="15"/>
-      <c r="X47" s="15"/>
-      <c r="Y47" s="15"/>
+      <c r="R47" s="12">
+        <v>22.0</v>
+      </c>
+      <c r="S47" s="12">
+        <v>20.0</v>
+      </c>
+      <c r="T47" s="16"/>
+      <c r="U47" s="16"/>
+      <c r="V47" s="16"/>
+      <c r="W47" s="16"/>
+      <c r="X47" s="16"/>
+      <c r="Y47" s="16"/>
     </row>
     <row r="48">
-      <c r="A48" s="15"/>
-      <c r="B48" s="15"/>
-      <c r="C48" s="15"/>
-      <c r="D48" s="15"/>
-      <c r="E48" s="15"/>
-      <c r="F48" s="15"/>
-      <c r="G48" s="15"/>
-      <c r="H48" s="15"/>
-      <c r="I48" s="15"/>
-      <c r="J48" s="15"/>
-      <c r="K48" s="15"/>
-      <c r="L48" s="15"/>
-      <c r="M48" s="15"/>
-      <c r="N48" s="15"/>
-      <c r="O48" s="15"/>
-      <c r="P48" s="15"/>
-      <c r="Q48" s="15"/>
-      <c r="R48" s="15"/>
-      <c r="S48" s="15"/>
-      <c r="T48" s="15"/>
-      <c r="U48" s="15"/>
-      <c r="V48" s="15"/>
-      <c r="W48" s="15"/>
-      <c r="X48" s="15"/>
-      <c r="Y48" s="15"/>
+      <c r="A48" s="16"/>
+      <c r="B48" s="16"/>
+      <c r="C48" s="16"/>
+      <c r="D48" s="16"/>
+      <c r="E48" s="16"/>
+      <c r="F48" s="16"/>
+      <c r="G48" s="16"/>
+      <c r="H48" s="16"/>
+      <c r="I48" s="16"/>
+      <c r="J48" s="16"/>
+      <c r="K48" s="16"/>
+      <c r="L48" s="16"/>
+      <c r="M48" s="16"/>
+      <c r="N48" s="16"/>
+      <c r="O48" s="16"/>
+      <c r="P48" s="16"/>
+      <c r="Q48" s="16"/>
+      <c r="R48" s="16"/>
+      <c r="S48" s="16"/>
+      <c r="T48" s="16"/>
+      <c r="U48" s="16"/>
+      <c r="V48" s="16"/>
+      <c r="W48" s="16"/>
+      <c r="X48" s="16"/>
+      <c r="Y48" s="16"/>
     </row>
     <row r="49">
       <c r="A49" s="12" t="s">
         <v>59</v>
       </c>
       <c r="B49" s="12">
-        <f> Z7 +Z3 +Z12 +Z14 +Z7 +Z6 +Z12 +Z9 + Z6 + Z9 + Z14</f>
-        <v>80</v>
+        <f> Z7 +Z3 +Z12 +Z14 +Z7 +Z6 +Z12 +Z9 + Z6 + Z9 + Z14 +Z4 +Z11</f>
+        <v>98</v>
       </c>
       <c r="C49" s="12" t="s">
         <v>60</v>
@@ -3118,7 +3225,7 @@
       <c r="D49" s="13">
         <v>7.0</v>
       </c>
-      <c r="E49" s="17">
+      <c r="E49" s="15">
         <v>3.0</v>
       </c>
       <c r="F49" s="13">
@@ -3157,49 +3264,53 @@
       <c r="Q49" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="R49" s="15"/>
-      <c r="S49" s="15"/>
-      <c r="T49" s="15"/>
-      <c r="U49" s="15"/>
-      <c r="V49" s="15"/>
-      <c r="W49" s="15"/>
-      <c r="X49" s="15"/>
-      <c r="Y49" s="15"/>
+      <c r="R49" s="13">
+        <v>4.0</v>
+      </c>
+      <c r="S49" s="13">
+        <v>11.0</v>
+      </c>
+      <c r="T49" s="16"/>
+      <c r="U49" s="16"/>
+      <c r="V49" s="16"/>
+      <c r="W49" s="16"/>
+      <c r="X49" s="16"/>
+      <c r="Y49" s="16"/>
     </row>
     <row r="50">
-      <c r="A50" s="15"/>
-      <c r="B50" s="15"/>
-      <c r="C50" s="15"/>
-      <c r="D50" s="15"/>
-      <c r="E50" s="15"/>
-      <c r="F50" s="15"/>
-      <c r="G50" s="15"/>
-      <c r="H50" s="15"/>
-      <c r="I50" s="15"/>
-      <c r="J50" s="15"/>
-      <c r="K50" s="15"/>
-      <c r="L50" s="15"/>
-      <c r="M50" s="15"/>
-      <c r="N50" s="15"/>
-      <c r="O50" s="15"/>
-      <c r="P50" s="15"/>
-      <c r="Q50" s="15"/>
-      <c r="R50" s="15"/>
-      <c r="S50" s="15"/>
-      <c r="T50" s="15"/>
-      <c r="U50" s="15"/>
-      <c r="V50" s="15"/>
-      <c r="W50" s="15"/>
-      <c r="X50" s="15"/>
-      <c r="Y50" s="15"/>
+      <c r="A50" s="16"/>
+      <c r="B50" s="16"/>
+      <c r="C50" s="16"/>
+      <c r="D50" s="16"/>
+      <c r="E50" s="16"/>
+      <c r="F50" s="16"/>
+      <c r="G50" s="16"/>
+      <c r="H50" s="16"/>
+      <c r="I50" s="16"/>
+      <c r="J50" s="16"/>
+      <c r="K50" s="16"/>
+      <c r="L50" s="16"/>
+      <c r="M50" s="16"/>
+      <c r="N50" s="16"/>
+      <c r="O50" s="16"/>
+      <c r="P50" s="16"/>
+      <c r="Q50" s="16"/>
+      <c r="R50" s="16"/>
+      <c r="S50" s="16"/>
+      <c r="T50" s="16"/>
+      <c r="U50" s="16"/>
+      <c r="V50" s="16"/>
+      <c r="W50" s="16"/>
+      <c r="X50" s="16"/>
+      <c r="Y50" s="16"/>
     </row>
     <row r="51">
       <c r="A51" s="12" t="s">
         <v>61</v>
       </c>
       <c r="B51" s="12">
-        <f>Z3 +Z1 +Z3 + Z3 + Z2 +Z3 +Z6</f>
-        <v>119</v>
+        <f>Z3 +Z1 +Z3 + Z3 + Z2 +Z3 +Z6 +Z5 +Z12</f>
+        <v>134</v>
       </c>
       <c r="C51" s="12" t="s">
         <v>60</v>
@@ -3210,7 +3321,7 @@
       <c r="E51" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="F51" s="17">
+      <c r="F51" s="15">
         <v>3.0</v>
       </c>
       <c r="G51" s="11">
@@ -3231,7 +3342,7 @@
       <c r="L51" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="M51" s="17">
+      <c r="M51" s="15">
         <v>3.0</v>
       </c>
       <c r="N51" s="18">
@@ -3240,47 +3351,51 @@
       <c r="O51" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="P51" s="17">
+      <c r="P51" s="15">
         <v>3.0</v>
       </c>
       <c r="Q51" s="13">
         <v>6.0</v>
       </c>
-      <c r="R51" s="15"/>
-      <c r="S51" s="15"/>
-      <c r="T51" s="15"/>
-      <c r="U51" s="15"/>
-      <c r="V51" s="15"/>
-      <c r="W51" s="15"/>
-      <c r="X51" s="15"/>
-      <c r="Y51" s="15"/>
+      <c r="R51" s="13">
+        <v>5.0</v>
+      </c>
+      <c r="S51" s="13">
+        <v>12.0</v>
+      </c>
+      <c r="T51" s="16"/>
+      <c r="U51" s="16"/>
+      <c r="V51" s="16"/>
+      <c r="W51" s="16"/>
+      <c r="X51" s="16"/>
+      <c r="Y51" s="16"/>
     </row>
     <row r="52">
-      <c r="A52" s="15"/>
-      <c r="B52" s="15"/>
-      <c r="C52" s="15"/>
-      <c r="D52" s="15"/>
-      <c r="E52" s="15"/>
-      <c r="F52" s="15"/>
-      <c r="G52" s="15"/>
-      <c r="H52" s="15"/>
-      <c r="I52" s="15"/>
-      <c r="J52" s="15"/>
-      <c r="K52" s="15"/>
-      <c r="L52" s="15"/>
-      <c r="M52" s="15"/>
-      <c r="N52" s="15"/>
-      <c r="O52" s="15"/>
-      <c r="P52" s="15"/>
-      <c r="Q52" s="15"/>
-      <c r="R52" s="15"/>
-      <c r="S52" s="15"/>
-      <c r="T52" s="15"/>
-      <c r="U52" s="15"/>
-      <c r="V52" s="15"/>
-      <c r="W52" s="15"/>
-      <c r="X52" s="15"/>
-      <c r="Y52" s="15"/>
+      <c r="A52" s="16"/>
+      <c r="B52" s="16"/>
+      <c r="C52" s="16"/>
+      <c r="D52" s="16"/>
+      <c r="E52" s="16"/>
+      <c r="F52" s="16"/>
+      <c r="G52" s="16"/>
+      <c r="H52" s="16"/>
+      <c r="I52" s="16"/>
+      <c r="J52" s="16"/>
+      <c r="K52" s="16"/>
+      <c r="L52" s="16"/>
+      <c r="M52" s="16"/>
+      <c r="N52" s="16"/>
+      <c r="O52" s="16"/>
+      <c r="P52" s="16"/>
+      <c r="Q52" s="16"/>
+      <c r="R52" s="16"/>
+      <c r="S52" s="16"/>
+      <c r="T52" s="16"/>
+      <c r="U52" s="16"/>
+      <c r="V52" s="16"/>
+      <c r="W52" s="16"/>
+      <c r="X52" s="16"/>
+      <c r="Y52" s="16"/>
     </row>
     <row r="53">
       <c r="A53" s="12" t="s">
@@ -3334,49 +3449,53 @@
       <c r="Q53" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="R53" s="15"/>
-      <c r="S53" s="15"/>
-      <c r="T53" s="15"/>
-      <c r="U53" s="15"/>
-      <c r="V53" s="15"/>
-      <c r="W53" s="15"/>
-      <c r="X53" s="15"/>
-      <c r="Y53" s="15"/>
+      <c r="R53" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="S53" s="12">
+        <v>19.0</v>
+      </c>
+      <c r="T53" s="16"/>
+      <c r="U53" s="16"/>
+      <c r="V53" s="16"/>
+      <c r="W53" s="16"/>
+      <c r="X53" s="16"/>
+      <c r="Y53" s="16"/>
     </row>
     <row r="54">
-      <c r="A54" s="15"/>
-      <c r="B54" s="15"/>
-      <c r="C54" s="15"/>
-      <c r="D54" s="15"/>
-      <c r="E54" s="15"/>
-      <c r="F54" s="15"/>
-      <c r="G54" s="15"/>
-      <c r="H54" s="15"/>
-      <c r="I54" s="15"/>
-      <c r="J54" s="15"/>
-      <c r="K54" s="15"/>
-      <c r="L54" s="15"/>
-      <c r="M54" s="15"/>
-      <c r="N54" s="15"/>
-      <c r="O54" s="15"/>
-      <c r="P54" s="15"/>
-      <c r="Q54" s="15"/>
-      <c r="R54" s="15"/>
-      <c r="S54" s="15"/>
-      <c r="T54" s="15"/>
-      <c r="U54" s="15"/>
-      <c r="V54" s="15"/>
-      <c r="W54" s="15"/>
-      <c r="X54" s="15"/>
-      <c r="Y54" s="15"/>
+      <c r="A54" s="16"/>
+      <c r="B54" s="16"/>
+      <c r="C54" s="16"/>
+      <c r="D54" s="16"/>
+      <c r="E54" s="16"/>
+      <c r="F54" s="16"/>
+      <c r="G54" s="16"/>
+      <c r="H54" s="16"/>
+      <c r="I54" s="16"/>
+      <c r="J54" s="16"/>
+      <c r="K54" s="16"/>
+      <c r="L54" s="16"/>
+      <c r="M54" s="16"/>
+      <c r="N54" s="16"/>
+      <c r="O54" s="16"/>
+      <c r="P54" s="16"/>
+      <c r="Q54" s="16"/>
+      <c r="R54" s="16"/>
+      <c r="S54" s="16"/>
+      <c r="T54" s="16"/>
+      <c r="U54" s="16"/>
+      <c r="V54" s="16"/>
+      <c r="W54" s="16"/>
+      <c r="X54" s="16"/>
+      <c r="Y54" s="16"/>
     </row>
     <row r="55">
       <c r="A55" s="12" t="s">
         <v>64</v>
       </c>
       <c r="B55" s="12">
-        <f>Z14 +Z14</f>
-        <v>4</v>
+        <f>Z14 +Z14 +Z13</f>
+        <v>7</v>
       </c>
       <c r="C55" s="12" t="s">
         <v>63</v>
@@ -3423,54 +3542,58 @@
       <c r="Q55" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="R55" s="15"/>
-      <c r="S55" s="15"/>
-      <c r="T55" s="15"/>
-      <c r="U55" s="15"/>
-      <c r="V55" s="15"/>
-      <c r="W55" s="15"/>
-      <c r="X55" s="15"/>
-      <c r="Y55" s="15"/>
+      <c r="R55" s="13">
+        <v>13.0</v>
+      </c>
+      <c r="S55" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="T55" s="16"/>
+      <c r="U55" s="16"/>
+      <c r="V55" s="16"/>
+      <c r="W55" s="16"/>
+      <c r="X55" s="16"/>
+      <c r="Y55" s="16"/>
     </row>
     <row r="56">
-      <c r="A56" s="15"/>
-      <c r="B56" s="15"/>
-      <c r="C56" s="15"/>
-      <c r="D56" s="15"/>
-      <c r="E56" s="15"/>
-      <c r="F56" s="15"/>
-      <c r="G56" s="15"/>
-      <c r="H56" s="15"/>
-      <c r="I56" s="15"/>
-      <c r="J56" s="15"/>
-      <c r="K56" s="15"/>
-      <c r="L56" s="15"/>
-      <c r="M56" s="15"/>
-      <c r="N56" s="15"/>
-      <c r="O56" s="15"/>
-      <c r="P56" s="15"/>
-      <c r="Q56" s="15"/>
-      <c r="R56" s="15"/>
-      <c r="S56" s="15"/>
-      <c r="T56" s="15"/>
-      <c r="U56" s="15"/>
-      <c r="V56" s="15"/>
-      <c r="W56" s="15"/>
-      <c r="X56" s="15"/>
-      <c r="Y56" s="15"/>
+      <c r="A56" s="16"/>
+      <c r="B56" s="16"/>
+      <c r="C56" s="16"/>
+      <c r="D56" s="16"/>
+      <c r="E56" s="16"/>
+      <c r="F56" s="16"/>
+      <c r="G56" s="16"/>
+      <c r="H56" s="16"/>
+      <c r="I56" s="16"/>
+      <c r="J56" s="16"/>
+      <c r="K56" s="16"/>
+      <c r="L56" s="16"/>
+      <c r="M56" s="16"/>
+      <c r="N56" s="16"/>
+      <c r="O56" s="16"/>
+      <c r="P56" s="16"/>
+      <c r="Q56" s="16"/>
+      <c r="R56" s="16"/>
+      <c r="S56" s="16"/>
+      <c r="T56" s="16"/>
+      <c r="U56" s="16"/>
+      <c r="V56" s="16"/>
+      <c r="W56" s="16"/>
+      <c r="X56" s="16"/>
+      <c r="Y56" s="16"/>
     </row>
     <row r="57">
       <c r="A57" s="12" t="s">
         <v>65</v>
       </c>
       <c r="B57" s="12">
-        <f> Z3 +Z7 +Z6 +Z7 +Z8 +Z6 + Z7 + Z3 + Z3 +Z9</f>
-        <v>110</v>
+        <f> Z3 +Z7 +Z6 +Z7 +Z8 +Z6 + Z7 + Z3 + Z3 +Z9 +Z2</f>
+        <v>130</v>
       </c>
       <c r="C57" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="D57" s="17">
+      <c r="D57" s="15">
         <v>3.0</v>
       </c>
       <c r="E57" s="13">
@@ -3500,10 +3623,10 @@
       <c r="M57" s="13">
         <v>7.0</v>
       </c>
-      <c r="N57" s="17">
+      <c r="N57" s="15">
         <v>3.0</v>
       </c>
-      <c r="O57" s="17">
+      <c r="O57" s="15">
         <v>3.0</v>
       </c>
       <c r="P57" s="13">
@@ -3512,49 +3635,53 @@
       <c r="Q57" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="R57" s="15"/>
-      <c r="S57" s="15"/>
-      <c r="T57" s="15"/>
-      <c r="U57" s="15"/>
-      <c r="V57" s="15"/>
-      <c r="W57" s="15"/>
-      <c r="X57" s="15"/>
-      <c r="Y57" s="15"/>
+      <c r="R57" s="12">
+        <v>23.0</v>
+      </c>
+      <c r="S57" s="18">
+        <v>2.0</v>
+      </c>
+      <c r="T57" s="16"/>
+      <c r="U57" s="16"/>
+      <c r="V57" s="16"/>
+      <c r="W57" s="16"/>
+      <c r="X57" s="16"/>
+      <c r="Y57" s="16"/>
     </row>
     <row r="58">
-      <c r="A58" s="15"/>
-      <c r="B58" s="15"/>
-      <c r="C58" s="15"/>
-      <c r="D58" s="15"/>
-      <c r="E58" s="15"/>
-      <c r="F58" s="15"/>
-      <c r="G58" s="15"/>
-      <c r="H58" s="15"/>
-      <c r="I58" s="15"/>
-      <c r="J58" s="15"/>
-      <c r="K58" s="15"/>
-      <c r="L58" s="15"/>
-      <c r="M58" s="15"/>
-      <c r="N58" s="15"/>
-      <c r="O58" s="15"/>
-      <c r="P58" s="15"/>
-      <c r="Q58" s="15"/>
-      <c r="R58" s="15"/>
-      <c r="S58" s="15"/>
-      <c r="T58" s="15"/>
-      <c r="U58" s="15"/>
-      <c r="V58" s="15"/>
-      <c r="W58" s="15"/>
-      <c r="X58" s="15"/>
-      <c r="Y58" s="15"/>
+      <c r="A58" s="16"/>
+      <c r="B58" s="16"/>
+      <c r="C58" s="16"/>
+      <c r="D58" s="16"/>
+      <c r="E58" s="16"/>
+      <c r="F58" s="16"/>
+      <c r="G58" s="16"/>
+      <c r="H58" s="16"/>
+      <c r="I58" s="16"/>
+      <c r="J58" s="16"/>
+      <c r="K58" s="16"/>
+      <c r="L58" s="16"/>
+      <c r="M58" s="16"/>
+      <c r="N58" s="16"/>
+      <c r="O58" s="16"/>
+      <c r="P58" s="16"/>
+      <c r="Q58" s="16"/>
+      <c r="R58" s="16"/>
+      <c r="S58" s="16"/>
+      <c r="T58" s="16"/>
+      <c r="U58" s="16"/>
+      <c r="V58" s="16"/>
+      <c r="W58" s="16"/>
+      <c r="X58" s="16"/>
+      <c r="Y58" s="16"/>
     </row>
     <row r="59">
       <c r="A59" s="12" t="s">
         <v>67</v>
       </c>
       <c r="B59" s="12">
-        <f> Z5 +Z11 +Z6 +Z14 +Z10 +Z10 + Z13 + Z6 + Z9 +Z2 +Z10</f>
-        <v>86</v>
+        <f> Z5 +Z11 +Z6 +Z14 +Z10 +Z10 + Z13 + Z6 + Z9 +Z2 +Z10 +Z12 +Z3</f>
+        <v>106</v>
       </c>
       <c r="C59" s="12" t="s">
         <v>66</v>
@@ -3601,41 +3728,45 @@
       <c r="Q59" s="13">
         <v>10.0</v>
       </c>
-      <c r="R59" s="15"/>
-      <c r="S59" s="15"/>
-      <c r="T59" s="15"/>
-      <c r="U59" s="15"/>
-      <c r="V59" s="15"/>
-      <c r="W59" s="15"/>
-      <c r="X59" s="15"/>
-      <c r="Y59" s="15"/>
+      <c r="R59" s="13">
+        <v>12.0</v>
+      </c>
+      <c r="S59" s="15">
+        <v>3.0</v>
+      </c>
+      <c r="T59" s="16"/>
+      <c r="U59" s="16"/>
+      <c r="V59" s="16"/>
+      <c r="W59" s="16"/>
+      <c r="X59" s="16"/>
+      <c r="Y59" s="16"/>
     </row>
     <row r="60">
-      <c r="A60" s="15"/>
-      <c r="B60" s="15"/>
-      <c r="C60" s="15"/>
-      <c r="D60" s="15"/>
-      <c r="E60" s="15"/>
-      <c r="F60" s="15"/>
-      <c r="G60" s="15"/>
-      <c r="H60" s="15"/>
-      <c r="I60" s="15"/>
-      <c r="J60" s="15"/>
-      <c r="K60" s="15"/>
-      <c r="L60" s="15"/>
-      <c r="M60" s="15"/>
-      <c r="N60" s="15"/>
-      <c r="O60" s="15"/>
-      <c r="P60" s="15"/>
-      <c r="Q60" s="15"/>
-      <c r="R60" s="15"/>
-      <c r="S60" s="15"/>
-      <c r="T60" s="15"/>
-      <c r="U60" s="15"/>
-      <c r="V60" s="15"/>
-      <c r="W60" s="15"/>
-      <c r="X60" s="15"/>
-      <c r="Y60" s="15"/>
+      <c r="A60" s="16"/>
+      <c r="B60" s="16"/>
+      <c r="C60" s="16"/>
+      <c r="D60" s="16"/>
+      <c r="E60" s="16"/>
+      <c r="F60" s="16"/>
+      <c r="G60" s="16"/>
+      <c r="H60" s="16"/>
+      <c r="I60" s="16"/>
+      <c r="J60" s="16"/>
+      <c r="K60" s="16"/>
+      <c r="L60" s="16"/>
+      <c r="M60" s="16"/>
+      <c r="N60" s="16"/>
+      <c r="O60" s="16"/>
+      <c r="P60" s="16"/>
+      <c r="Q60" s="16"/>
+      <c r="R60" s="16"/>
+      <c r="S60" s="16"/>
+      <c r="T60" s="16"/>
+      <c r="U60" s="16"/>
+      <c r="V60" s="16"/>
+      <c r="W60" s="16"/>
+      <c r="X60" s="16"/>
+      <c r="Y60" s="16"/>
     </row>
     <row r="61">
       <c r="A61" s="12" t="s">
@@ -3690,49 +3821,53 @@
       <c r="Q61" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="R61" s="15"/>
-      <c r="S61" s="15"/>
-      <c r="T61" s="15"/>
-      <c r="U61" s="15"/>
-      <c r="V61" s="15"/>
-      <c r="W61" s="15"/>
-      <c r="X61" s="15"/>
-      <c r="Y61" s="15"/>
+      <c r="R61" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="S61" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="T61" s="16"/>
+      <c r="U61" s="16"/>
+      <c r="V61" s="16"/>
+      <c r="W61" s="16"/>
+      <c r="X61" s="16"/>
+      <c r="Y61" s="16"/>
     </row>
     <row r="62">
-      <c r="A62" s="15"/>
-      <c r="B62" s="15"/>
-      <c r="C62" s="15"/>
-      <c r="D62" s="15"/>
-      <c r="E62" s="15"/>
-      <c r="F62" s="15"/>
-      <c r="G62" s="15"/>
-      <c r="H62" s="15"/>
-      <c r="I62" s="15"/>
-      <c r="J62" s="15"/>
-      <c r="K62" s="15"/>
-      <c r="L62" s="15"/>
-      <c r="M62" s="15"/>
-      <c r="N62" s="15"/>
-      <c r="O62" s="15"/>
-      <c r="P62" s="15"/>
-      <c r="Q62" s="15"/>
-      <c r="R62" s="15"/>
-      <c r="S62" s="15"/>
-      <c r="T62" s="15"/>
-      <c r="U62" s="15"/>
-      <c r="V62" s="15"/>
-      <c r="W62" s="15"/>
-      <c r="X62" s="15"/>
-      <c r="Y62" s="15"/>
+      <c r="A62" s="16"/>
+      <c r="B62" s="16"/>
+      <c r="C62" s="16"/>
+      <c r="D62" s="16"/>
+      <c r="E62" s="16"/>
+      <c r="F62" s="16"/>
+      <c r="G62" s="16"/>
+      <c r="H62" s="16"/>
+      <c r="I62" s="16"/>
+      <c r="J62" s="16"/>
+      <c r="K62" s="16"/>
+      <c r="L62" s="16"/>
+      <c r="M62" s="16"/>
+      <c r="N62" s="16"/>
+      <c r="O62" s="16"/>
+      <c r="P62" s="16"/>
+      <c r="Q62" s="16"/>
+      <c r="R62" s="16"/>
+      <c r="S62" s="16"/>
+      <c r="T62" s="16"/>
+      <c r="U62" s="16"/>
+      <c r="V62" s="16"/>
+      <c r="W62" s="16"/>
+      <c r="X62" s="16"/>
+      <c r="Y62" s="16"/>
     </row>
     <row r="63">
       <c r="A63" s="12" t="s">
         <v>70</v>
       </c>
       <c r="B63" s="12">
-        <f>Z12 +Z10 +Z8 +Z12 +Z9 + Z14 + Z15 +Z11</f>
-        <v>37</v>
+        <f>Z12 +Z10 +Z8 +Z12 +Z9 + Z14 + Z15 +Z11 +Z14 +Z13</f>
+        <v>42</v>
       </c>
       <c r="C63" s="12" t="s">
         <v>69</v>
@@ -3779,14 +3914,18 @@
       <c r="Q63" s="13">
         <v>11.0</v>
       </c>
-      <c r="R63" s="15"/>
-      <c r="S63" s="15"/>
-      <c r="T63" s="15"/>
-      <c r="U63" s="15"/>
-      <c r="V63" s="15"/>
-      <c r="W63" s="15"/>
-      <c r="X63" s="15"/>
-      <c r="Y63" s="15"/>
+      <c r="R63" s="13">
+        <v>14.0</v>
+      </c>
+      <c r="S63" s="13">
+        <v>13.0</v>
+      </c>
+      <c r="T63" s="16"/>
+      <c r="U63" s="16"/>
+      <c r="V63" s="16"/>
+      <c r="W63" s="16"/>
+      <c r="X63" s="16"/>
+      <c r="Y63" s="16"/>
     </row>
     <row r="65">
       <c r="A65" s="12" t="s">
@@ -3808,14 +3947,14 @@
       </c>
       <c r="B66" s="12">
         <f> B5+B7</f>
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="D66" s="12" t="s">
         <v>74</v>
       </c>
       <c r="E66" s="12">
         <f> B66+B67+B68+B69+B72+B73+B80+B79+B77+B76+B75</f>
-        <v>1486</v>
+        <v>1691</v>
       </c>
       <c r="W66" s="21">
         <v>1.0</v>
@@ -3830,14 +3969,14 @@
       </c>
       <c r="B67" s="12">
         <f> B9+B11</f>
-        <v>176</v>
+        <v>199</v>
       </c>
       <c r="D67" s="12" t="s">
         <v>75</v>
       </c>
       <c r="E67" s="12">
         <f> B71+B70</f>
-        <v>463</v>
+        <v>535</v>
       </c>
       <c r="W67" s="23">
         <v>2.0</v>
@@ -3852,14 +3991,14 @@
       </c>
       <c r="B68" s="12">
         <f> B13+B15</f>
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="D68" s="12" t="s">
         <v>76</v>
       </c>
       <c r="E68" s="12">
         <f> B78+B74</f>
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="W68" s="24">
         <v>3.0</v>
@@ -3874,7 +4013,7 @@
       </c>
       <c r="B69" s="12">
         <f>B17+B19</f>
-        <v>202</v>
+        <v>227</v>
       </c>
       <c r="W69" s="25">
         <v>4.0</v>
@@ -3889,7 +4028,7 @@
       </c>
       <c r="B70" s="12">
         <f> B21+B23</f>
-        <v>245</v>
+        <v>290</v>
       </c>
       <c r="W70" s="25">
         <v>5.0</v>
@@ -3904,7 +4043,7 @@
       </c>
       <c r="B71" s="12">
         <f> B25+B27</f>
-        <v>218</v>
+        <v>245</v>
       </c>
       <c r="W71" s="25">
         <v>6.0</v>
@@ -3919,7 +4058,7 @@
       </c>
       <c r="B72" s="12">
         <f> B29+B31</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="W72" s="25">
         <v>7.0</v>
@@ -3934,7 +4073,7 @@
       </c>
       <c r="B73" s="12">
         <f>B33+B35</f>
-        <v>338</v>
+        <v>363</v>
       </c>
       <c r="W73" s="25">
         <v>8.0</v>
@@ -3960,7 +4099,7 @@
       </c>
       <c r="B75" s="12">
         <f> B37+B39</f>
-        <v>106</v>
+        <v>131</v>
       </c>
       <c r="W75" s="25">
         <v>9.0</v>
@@ -3990,7 +4129,7 @@
       </c>
       <c r="B77" s="12">
         <f> B49+B51</f>
-        <v>199</v>
+        <v>232</v>
       </c>
       <c r="W77" s="25">
         <v>12.0</v>
@@ -4005,7 +4144,7 @@
       </c>
       <c r="B78" s="12">
         <f> B53+B55</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="W78" s="25">
         <v>13.0</v>
@@ -4020,7 +4159,7 @@
       </c>
       <c r="B79" s="12">
         <f> B57+B59</f>
-        <v>196</v>
+        <v>236</v>
       </c>
       <c r="W79" s="25">
         <v>14.0</v>
@@ -4035,7 +4174,7 @@
       </c>
       <c r="B80" s="12">
         <f> B61+B63</f>
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="W80" s="25">
         <v>15.0</v>
@@ -4166,6 +4305,12 @@
       </c>
       <c r="O83" s="33" t="s">
         <v>92</v>
+      </c>
+      <c r="P83" s="33" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q83" s="33" t="s">
+        <v>94</v>
       </c>
       <c r="W83" s="34"/>
     </row>
@@ -4186,46 +4331,52 @@
         <v>47</v>
       </c>
       <c r="B85" s="30" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C85" s="31" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D85" s="32" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E85" s="32" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F85" s="30" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="G85" s="30" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H85" s="30" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I85" s="30" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="J85" s="33" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="K85" s="33" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="L85" s="33" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="M85" s="33" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="N85" s="33" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="O85" s="33" t="s">
-        <v>106</v>
+        <v>108</v>
+      </c>
+      <c r="P85" s="33" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q85" s="33" t="s">
+        <v>110</v>
       </c>
       <c r="W85" s="34"/>
     </row>
@@ -4246,49 +4397,53 @@
         <v>29</v>
       </c>
       <c r="B87" s="37" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C87" s="38" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D87" s="39" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="E87" s="39" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="F87" s="37" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="G87" s="37" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="H87" s="37" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="I87" s="37" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="J87" s="40" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="K87" s="40" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="L87" s="40" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="M87" s="40" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="N87" s="40" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="O87" s="40" t="s">
-        <v>120</v>
-      </c>
-      <c r="P87" s="41"/>
-      <c r="Q87" s="41"/>
+        <v>124</v>
+      </c>
+      <c r="P87" s="40" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q87" s="40" t="s">
+        <v>126</v>
+      </c>
       <c r="R87" s="41"/>
       <c r="S87" s="41"/>
       <c r="T87" s="41"/>

--- a/docs/classifiche/classifica2025.xlsx
+++ b/docs/classifiche/classifica2025.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Foglio1" sheetId="1" r:id="rId4"/>
+    <sheet state="visible" name="Foglio1" sheetId="1" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="145">
   <si>
     <t>STAGIONE 2025: MOTO 2</t>
   </si>
@@ -298,6 +298,24 @@
     <t>1:35.314</t>
   </si>
   <si>
+    <t>1:49.363</t>
+  </si>
+  <si>
+    <t>1:40.304</t>
+  </si>
+  <si>
+    <t>1:30.530</t>
+  </si>
+  <si>
+    <t>2:03.249</t>
+  </si>
+  <si>
+    <t>1:42.291</t>
+  </si>
+  <si>
+    <t>1:32.683, Arbolino</t>
+  </si>
+  <si>
     <t>1:33.839, pole</t>
   </si>
   <si>
@@ -346,6 +364,24 @@
     <t>1:35.314, pole</t>
   </si>
   <si>
+    <t>1:49.363, pole, FL</t>
+  </si>
+  <si>
+    <t>1:40.483, 2, FL</t>
+  </si>
+  <si>
+    <t>1:30.530, pole</t>
+  </si>
+  <si>
+    <t>2:03.249, pole, FL</t>
+  </si>
+  <si>
+    <t>1:42.291, pole</t>
+  </si>
+  <si>
+    <t>1:32.982, 4</t>
+  </si>
+  <si>
     <t>1:34.373, 2</t>
   </si>
   <si>
@@ -392,6 +428,24 @@
   </si>
   <si>
     <t>1:36.115, 7</t>
+  </si>
+  <si>
+    <t>1:49.760, 3</t>
+  </si>
+  <si>
+    <t>1:40.304, pole</t>
+  </si>
+  <si>
+    <t>1:30.962, 2</t>
+  </si>
+  <si>
+    <t>2:03.714, 2</t>
+  </si>
+  <si>
+    <t>1:43.665, 14</t>
+  </si>
+  <si>
+    <t>1:33.754, 16</t>
   </si>
 </sst>
 </file>
@@ -575,7 +629,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="41">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -616,11 +670,11 @@
     <xf borderId="0" fillId="6" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
+    <xf borderId="0" fillId="7" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
     <xf borderId="6" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="0" fillId="7" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="7" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
@@ -685,8 +739,6 @@
     <xf borderId="5" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="5" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="9" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -697,6 +749,10 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -912,6 +968,10 @@
     <col customWidth="1" min="13" max="13" width="14.25"/>
     <col customWidth="1" min="15" max="15" width="14.75"/>
     <col customWidth="1" min="16" max="16" width="13.5"/>
+    <col customWidth="1" min="18" max="18" width="14.5"/>
+    <col customWidth="1" min="20" max="20" width="14.13"/>
+    <col customWidth="1" min="21" max="21" width="14.88"/>
+    <col customWidth="1" min="23" max="23" width="14.88"/>
     <col customWidth="1" min="26" max="27" width="14.63"/>
   </cols>
   <sheetData>
@@ -1074,8 +1134,8 @@
         <v>25</v>
       </c>
       <c r="B5" s="12">
-        <f>Z13 +Z11 +Z7 +Z10 +Z5 +Z9 +Z6 + Z8 + Z7 +Z4 +Z3</f>
-        <v>97</v>
+        <f>Z13 +Z11 +Z7 +Z10 +Z5 +Z9 +Z6 + Z8 + Z7 +Z4 +Z3 +Z11 +Z4 +Z12 + Z6 + Z6</f>
+        <v>139</v>
       </c>
       <c r="C5" s="12" t="s">
         <v>26</v>
@@ -1128,45 +1188,57 @@
       <c r="S5" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="T5" s="16"/>
-      <c r="U5" s="16"/>
-      <c r="V5" s="16"/>
-      <c r="W5" s="16"/>
-      <c r="X5" s="16"/>
-      <c r="Y5" s="16"/>
+      <c r="T5" s="13">
+        <v>11.0</v>
+      </c>
+      <c r="U5" s="13">
+        <v>4.0</v>
+      </c>
+      <c r="V5" s="13">
+        <v>12.0</v>
+      </c>
+      <c r="W5" s="13">
+        <v>6.0</v>
+      </c>
+      <c r="X5" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y5" s="13">
+        <v>6.0</v>
+      </c>
       <c r="Z5" s="3">
         <v>11.0</v>
       </c>
-      <c r="AA5" s="17">
+      <c r="AA5" s="16">
         <v>2.0</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="16"/>
-      <c r="B6" s="16"/>
-      <c r="C6" s="16"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="16"/>
-      <c r="F6" s="16"/>
-      <c r="G6" s="16"/>
-      <c r="H6" s="16"/>
-      <c r="I6" s="16"/>
-      <c r="J6" s="16"/>
-      <c r="K6" s="16"/>
-      <c r="L6" s="16"/>
-      <c r="M6" s="16"/>
-      <c r="N6" s="16"/>
-      <c r="O6" s="16"/>
-      <c r="P6" s="16"/>
-      <c r="Q6" s="16"/>
-      <c r="R6" s="16"/>
-      <c r="S6" s="16"/>
-      <c r="T6" s="16"/>
-      <c r="U6" s="16"/>
-      <c r="V6" s="16"/>
-      <c r="W6" s="16"/>
-      <c r="X6" s="16"/>
-      <c r="Y6" s="16"/>
+      <c r="A6" s="17"/>
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="17"/>
+      <c r="H6" s="17"/>
+      <c r="I6" s="17"/>
+      <c r="J6" s="17"/>
+      <c r="K6" s="17"/>
+      <c r="L6" s="17"/>
+      <c r="M6" s="17"/>
+      <c r="N6" s="17"/>
+      <c r="O6" s="17"/>
+      <c r="P6" s="17"/>
+      <c r="Q6" s="17"/>
+      <c r="R6" s="17"/>
+      <c r="S6" s="17"/>
+      <c r="T6" s="17"/>
+      <c r="U6" s="17"/>
+      <c r="V6" s="17"/>
+      <c r="W6" s="17"/>
+      <c r="X6" s="17"/>
+      <c r="Y6" s="17"/>
       <c r="Z6" s="3">
         <v>10.0</v>
       </c>
@@ -1179,8 +1251,8 @@
         <v>28</v>
       </c>
       <c r="B7" s="12">
-        <f>Z15 +Z12</f>
-        <v>5</v>
+        <f>Z15 +Z12 +Z14 + Z15 + Z11</f>
+        <v>13</v>
       </c>
       <c r="C7" s="12" t="s">
         <v>26</v>
@@ -1233,12 +1305,24 @@
       <c r="S7" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="T7" s="16"/>
-      <c r="U7" s="16"/>
-      <c r="V7" s="16"/>
-      <c r="W7" s="16"/>
-      <c r="X7" s="16"/>
-      <c r="Y7" s="16"/>
+      <c r="T7" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="U7" s="13">
+        <v>14.0</v>
+      </c>
+      <c r="V7" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="W7" s="13">
+        <v>15.0</v>
+      </c>
+      <c r="X7" s="13">
+        <v>11.0</v>
+      </c>
+      <c r="Y7" s="14" t="s">
+        <v>27</v>
+      </c>
       <c r="Z7" s="3">
         <v>9.0</v>
       </c>
@@ -1247,31 +1331,31 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="16"/>
-      <c r="B8" s="16"/>
-      <c r="C8" s="16"/>
-      <c r="D8" s="16"/>
-      <c r="E8" s="16"/>
-      <c r="F8" s="16"/>
-      <c r="G8" s="16"/>
-      <c r="H8" s="16"/>
-      <c r="I8" s="16"/>
-      <c r="J8" s="16"/>
-      <c r="K8" s="16"/>
-      <c r="L8" s="16"/>
-      <c r="M8" s="16"/>
-      <c r="N8" s="16"/>
-      <c r="O8" s="16"/>
-      <c r="P8" s="16"/>
-      <c r="Q8" s="16"/>
-      <c r="R8" s="16"/>
-      <c r="S8" s="16"/>
-      <c r="T8" s="16"/>
-      <c r="U8" s="16"/>
-      <c r="V8" s="16"/>
-      <c r="W8" s="16"/>
-      <c r="X8" s="16"/>
-      <c r="Y8" s="16"/>
+      <c r="A8" s="17"/>
+      <c r="B8" s="17"/>
+      <c r="C8" s="17"/>
+      <c r="D8" s="17"/>
+      <c r="E8" s="17"/>
+      <c r="F8" s="17"/>
+      <c r="G8" s="17"/>
+      <c r="H8" s="17"/>
+      <c r="I8" s="17"/>
+      <c r="J8" s="17"/>
+      <c r="K8" s="17"/>
+      <c r="L8" s="17"/>
+      <c r="M8" s="17"/>
+      <c r="N8" s="17"/>
+      <c r="O8" s="17"/>
+      <c r="P8" s="17"/>
+      <c r="Q8" s="17"/>
+      <c r="R8" s="17"/>
+      <c r="S8" s="17"/>
+      <c r="T8" s="17"/>
+      <c r="U8" s="17"/>
+      <c r="V8" s="17"/>
+      <c r="W8" s="17"/>
+      <c r="X8" s="17"/>
+      <c r="Y8" s="17"/>
       <c r="Z8" s="3">
         <v>8.0</v>
       </c>
@@ -1284,8 +1368,8 @@
         <v>29</v>
       </c>
       <c r="B9" s="12">
-        <f> Z4 +Z10 +Z14 +Z2 +Z4 +Z11 +Z13 +Z3 + Z2 + Z2 +Z10 +Z6</f>
-        <v>134</v>
+        <f> Z4 +Z10 +Z14 +Z2 +Z4 +Z11 +Z13 +Z3 + Z2 + Z2 +Z10 +Z6 +Z2 +Z2 +Z8 + Z11 + Z8</f>
+        <v>195</v>
       </c>
       <c r="C9" s="12" t="s">
         <v>30</v>
@@ -1302,7 +1386,7 @@
       <c r="G9" s="13">
         <v>14.0</v>
       </c>
-      <c r="H9" s="17">
+      <c r="H9" s="16">
         <v>2.0</v>
       </c>
       <c r="I9" s="13">
@@ -1338,12 +1422,24 @@
       <c r="S9" s="13">
         <v>6.0</v>
       </c>
-      <c r="T9" s="16"/>
-      <c r="U9" s="16"/>
-      <c r="V9" s="16"/>
-      <c r="W9" s="16"/>
-      <c r="X9" s="16"/>
-      <c r="Y9" s="16"/>
+      <c r="T9" s="18">
+        <v>2.0</v>
+      </c>
+      <c r="U9" s="18">
+        <v>2.0</v>
+      </c>
+      <c r="V9" s="13">
+        <v>8.0</v>
+      </c>
+      <c r="W9" s="13">
+        <v>11.0</v>
+      </c>
+      <c r="X9" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y9" s="13">
+        <v>8.0</v>
+      </c>
       <c r="Z9" s="3">
         <v>7.0</v>
       </c>
@@ -1352,31 +1448,31 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="16"/>
-      <c r="B10" s="16"/>
-      <c r="C10" s="16"/>
-      <c r="D10" s="16"/>
-      <c r="E10" s="16"/>
-      <c r="F10" s="16"/>
-      <c r="G10" s="16"/>
-      <c r="H10" s="16"/>
-      <c r="I10" s="16"/>
-      <c r="J10" s="16"/>
-      <c r="K10" s="16"/>
-      <c r="L10" s="16"/>
-      <c r="M10" s="16"/>
-      <c r="N10" s="16"/>
-      <c r="O10" s="16"/>
-      <c r="P10" s="16"/>
-      <c r="Q10" s="16"/>
-      <c r="R10" s="16"/>
-      <c r="S10" s="16"/>
-      <c r="T10" s="16"/>
-      <c r="U10" s="16"/>
-      <c r="V10" s="16"/>
-      <c r="W10" s="16"/>
-      <c r="X10" s="16"/>
-      <c r="Y10" s="16"/>
+      <c r="A10" s="17"/>
+      <c r="B10" s="17"/>
+      <c r="C10" s="17"/>
+      <c r="D10" s="17"/>
+      <c r="E10" s="17"/>
+      <c r="F10" s="17"/>
+      <c r="G10" s="17"/>
+      <c r="H10" s="17"/>
+      <c r="I10" s="17"/>
+      <c r="J10" s="17"/>
+      <c r="K10" s="17"/>
+      <c r="L10" s="17"/>
+      <c r="M10" s="17"/>
+      <c r="N10" s="17"/>
+      <c r="O10" s="17"/>
+      <c r="P10" s="17"/>
+      <c r="Q10" s="17"/>
+      <c r="R10" s="17"/>
+      <c r="S10" s="17"/>
+      <c r="T10" s="17"/>
+      <c r="U10" s="17"/>
+      <c r="V10" s="17"/>
+      <c r="W10" s="17"/>
+      <c r="X10" s="17"/>
+      <c r="Y10" s="17"/>
       <c r="Z10" s="3">
         <v>6.0</v>
       </c>
@@ -1389,8 +1485,8 @@
         <v>31</v>
       </c>
       <c r="B11" s="12">
-        <f>Z13 +Z9 +Z13 +Z11 +Z11 +Z14 +Z10 +Z12 + Z15 + Z11 + Z12 +Z10 +Z9 +Z9</f>
-        <v>65</v>
+        <f>Z13 +Z9 +Z13 +Z11 +Z11 +Z14 +Z10 +Z12 + Z15 + Z11 + Z12 +Z10 +Z9 +Z9 +Z9 +Z13 + Z14 + Z7 + Z14</f>
+        <v>88</v>
       </c>
       <c r="C11" s="12" t="s">
         <v>30</v>
@@ -1443,12 +1539,24 @@
       <c r="S11" s="13">
         <v>9.0</v>
       </c>
-      <c r="T11" s="16"/>
-      <c r="U11" s="16"/>
-      <c r="V11" s="16"/>
-      <c r="W11" s="16"/>
-      <c r="X11" s="16"/>
-      <c r="Y11" s="16"/>
+      <c r="T11" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="U11" s="13">
+        <v>9.0</v>
+      </c>
+      <c r="V11" s="13">
+        <v>13.0</v>
+      </c>
+      <c r="W11" s="13">
+        <v>14.0</v>
+      </c>
+      <c r="X11" s="13">
+        <v>7.0</v>
+      </c>
+      <c r="Y11" s="13">
+        <v>14.0</v>
+      </c>
       <c r="Z11" s="3">
         <v>5.0</v>
       </c>
@@ -1457,31 +1565,31 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="16"/>
-      <c r="B12" s="16"/>
-      <c r="C12" s="16"/>
-      <c r="D12" s="16"/>
-      <c r="E12" s="16"/>
-      <c r="F12" s="16"/>
-      <c r="G12" s="16"/>
-      <c r="H12" s="16"/>
-      <c r="I12" s="16"/>
-      <c r="J12" s="16"/>
-      <c r="K12" s="16"/>
-      <c r="L12" s="16"/>
-      <c r="M12" s="16"/>
-      <c r="N12" s="16"/>
-      <c r="O12" s="16"/>
-      <c r="P12" s="16"/>
-      <c r="Q12" s="16"/>
-      <c r="R12" s="16"/>
-      <c r="S12" s="16"/>
-      <c r="T12" s="16"/>
-      <c r="U12" s="16"/>
-      <c r="V12" s="16"/>
-      <c r="W12" s="16"/>
-      <c r="X12" s="16"/>
-      <c r="Y12" s="16"/>
+      <c r="A12" s="17"/>
+      <c r="B12" s="17"/>
+      <c r="C12" s="17"/>
+      <c r="D12" s="17"/>
+      <c r="E12" s="17"/>
+      <c r="F12" s="17"/>
+      <c r="G12" s="17"/>
+      <c r="H12" s="17"/>
+      <c r="I12" s="17"/>
+      <c r="J12" s="17"/>
+      <c r="K12" s="17"/>
+      <c r="L12" s="17"/>
+      <c r="M12" s="17"/>
+      <c r="N12" s="17"/>
+      <c r="O12" s="17"/>
+      <c r="P12" s="17"/>
+      <c r="Q12" s="17"/>
+      <c r="R12" s="17"/>
+      <c r="S12" s="17"/>
+      <c r="T12" s="17"/>
+      <c r="U12" s="17"/>
+      <c r="V12" s="17"/>
+      <c r="W12" s="17"/>
+      <c r="X12" s="17"/>
+      <c r="Y12" s="17"/>
       <c r="Z12" s="3">
         <v>4.0</v>
       </c>
@@ -1494,8 +1602,8 @@
         <v>32</v>
       </c>
       <c r="B13" s="12">
-        <f>Z14 +Z8 +Z11 +Z9 +Z15 +Z13 + Z11 +Z11 +Z8 +Z15 +Z15</f>
-        <v>46</v>
+        <f>Z14 +Z8 +Z11 +Z9 +Z15 +Z13 + Z11 +Z11 +Z8 +Z15 +Z15 +Z15 + Z8 + Z15</f>
+        <v>56</v>
       </c>
       <c r="C13" s="12" t="s">
         <v>33</v>
@@ -1548,12 +1656,24 @@
       <c r="S13" s="13">
         <v>15.0</v>
       </c>
-      <c r="T13" s="16"/>
-      <c r="U13" s="16"/>
-      <c r="V13" s="16"/>
-      <c r="W13" s="16"/>
-      <c r="X13" s="16"/>
-      <c r="Y13" s="16"/>
+      <c r="T13" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="U13" s="13">
+        <v>15.0</v>
+      </c>
+      <c r="V13" s="12">
+        <v>19.0</v>
+      </c>
+      <c r="W13" s="12">
+        <v>16.0</v>
+      </c>
+      <c r="X13" s="13">
+        <v>8.0</v>
+      </c>
+      <c r="Y13" s="13">
+        <v>15.0</v>
+      </c>
       <c r="Z13" s="3">
         <v>3.0</v>
       </c>
@@ -1562,31 +1682,31 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="16"/>
-      <c r="B14" s="16"/>
-      <c r="C14" s="16"/>
-      <c r="D14" s="16"/>
-      <c r="E14" s="16"/>
-      <c r="F14" s="16"/>
-      <c r="G14" s="16"/>
-      <c r="H14" s="16"/>
-      <c r="I14" s="16"/>
-      <c r="J14" s="16"/>
-      <c r="K14" s="16"/>
-      <c r="L14" s="16"/>
-      <c r="M14" s="16"/>
-      <c r="N14" s="16"/>
-      <c r="O14" s="16"/>
-      <c r="P14" s="16"/>
-      <c r="Q14" s="16"/>
-      <c r="R14" s="16"/>
-      <c r="S14" s="16"/>
-      <c r="T14" s="16"/>
-      <c r="U14" s="16"/>
-      <c r="V14" s="16"/>
-      <c r="W14" s="16"/>
-      <c r="X14" s="16"/>
-      <c r="Y14" s="16"/>
+      <c r="A14" s="17"/>
+      <c r="B14" s="17"/>
+      <c r="C14" s="17"/>
+      <c r="D14" s="17"/>
+      <c r="E14" s="17"/>
+      <c r="F14" s="17"/>
+      <c r="G14" s="17"/>
+      <c r="H14" s="17"/>
+      <c r="I14" s="17"/>
+      <c r="J14" s="17"/>
+      <c r="K14" s="17"/>
+      <c r="L14" s="17"/>
+      <c r="M14" s="17"/>
+      <c r="N14" s="17"/>
+      <c r="O14" s="17"/>
+      <c r="P14" s="17"/>
+      <c r="Q14" s="17"/>
+      <c r="R14" s="17"/>
+      <c r="S14" s="17"/>
+      <c r="T14" s="17"/>
+      <c r="U14" s="17"/>
+      <c r="V14" s="17"/>
+      <c r="W14" s="17"/>
+      <c r="X14" s="17"/>
+      <c r="Y14" s="17"/>
       <c r="Z14" s="3">
         <v>2.0</v>
       </c>
@@ -1599,8 +1719,8 @@
         <v>34</v>
       </c>
       <c r="B15" s="12">
-        <f> Z6 +Z5 +Z8 +Z7 +Z4 +Z11 + Z6 +Z6 +Z7 +Z7</f>
-        <v>94</v>
+        <f> Z6 +Z5 +Z8 +Z7 +Z4 +Z11 + Z6 +Z6 +Z7 +Z7 +Z3 +Z11 +Z1 + Z3 + Z12</f>
+        <v>160</v>
       </c>
       <c r="C15" s="12" t="s">
         <v>33</v>
@@ -1653,12 +1773,24 @@
       <c r="S15" s="13">
         <v>7.0</v>
       </c>
-      <c r="T15" s="16"/>
-      <c r="U15" s="16"/>
-      <c r="V15" s="16"/>
-      <c r="W15" s="16"/>
-      <c r="X15" s="16"/>
-      <c r="Y15" s="16"/>
+      <c r="T15" s="15">
+        <v>3.0</v>
+      </c>
+      <c r="U15" s="13">
+        <v>11.0</v>
+      </c>
+      <c r="V15" s="11">
+        <v>1.0</v>
+      </c>
+      <c r="W15" s="15">
+        <v>3.0</v>
+      </c>
+      <c r="X15" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y15" s="13">
+        <v>12.0</v>
+      </c>
       <c r="Z15" s="3">
         <v>1.0</v>
       </c>
@@ -1667,31 +1799,31 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="16"/>
-      <c r="B16" s="16"/>
-      <c r="C16" s="16"/>
-      <c r="D16" s="16"/>
-      <c r="E16" s="16"/>
-      <c r="F16" s="16"/>
-      <c r="G16" s="16"/>
-      <c r="H16" s="16"/>
-      <c r="I16" s="16"/>
-      <c r="J16" s="16"/>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16"/>
-      <c r="N16" s="16"/>
-      <c r="O16" s="16"/>
-      <c r="P16" s="16"/>
-      <c r="Q16" s="16"/>
-      <c r="R16" s="16"/>
-      <c r="S16" s="16"/>
-      <c r="T16" s="16"/>
-      <c r="U16" s="16"/>
-      <c r="V16" s="16"/>
-      <c r="W16" s="16"/>
-      <c r="X16" s="16"/>
-      <c r="Y16" s="16"/>
+      <c r="A16" s="17"/>
+      <c r="B16" s="17"/>
+      <c r="C16" s="17"/>
+      <c r="D16" s="17"/>
+      <c r="E16" s="17"/>
+      <c r="F16" s="17"/>
+      <c r="G16" s="17"/>
+      <c r="H16" s="17"/>
+      <c r="I16" s="17"/>
+      <c r="J16" s="17"/>
+      <c r="K16" s="17"/>
+      <c r="L16" s="17"/>
+      <c r="M16" s="17"/>
+      <c r="N16" s="17"/>
+      <c r="O16" s="17"/>
+      <c r="P16" s="17"/>
+      <c r="Q16" s="17"/>
+      <c r="R16" s="17"/>
+      <c r="S16" s="17"/>
+      <c r="T16" s="17"/>
+      <c r="U16" s="17"/>
+      <c r="V16" s="17"/>
+      <c r="W16" s="17"/>
+      <c r="X16" s="17"/>
+      <c r="Y16" s="17"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="13">
         <v>13.0</v>
@@ -1702,8 +1834,8 @@
         <v>35</v>
       </c>
       <c r="B17" s="12">
-        <f>Z12 +Z4 +Z3 +Z6 +Z12 +Z8 + Z7 + Z5 +Z7 +Z9 +Z4</f>
-        <v>104</v>
+        <f>Z12 +Z4 +Z3 +Z6 +Z12 +Z8 + Z7 + Z5 +Z7 +Z9 +Z4 +Z7 +Z6 + Z7 + Z1 + Z5</f>
+        <v>168</v>
       </c>
       <c r="C17" s="12" t="s">
         <v>36</v>
@@ -1756,43 +1888,55 @@
       <c r="S17" s="13">
         <v>4.0</v>
       </c>
-      <c r="T17" s="16"/>
-      <c r="U17" s="16"/>
-      <c r="V17" s="16"/>
-      <c r="W17" s="16"/>
-      <c r="X17" s="16"/>
-      <c r="Y17" s="16"/>
+      <c r="T17" s="13">
+        <v>7.0</v>
+      </c>
+      <c r="U17" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="V17" s="13">
+        <v>6.0</v>
+      </c>
+      <c r="W17" s="13">
+        <v>7.0</v>
+      </c>
+      <c r="X17" s="11">
+        <v>1.0</v>
+      </c>
+      <c r="Y17" s="13">
+        <v>5.0</v>
+      </c>
       <c r="Z17" s="3"/>
       <c r="AA17" s="13">
         <v>14.0</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="16"/>
-      <c r="B18" s="16"/>
-      <c r="C18" s="16"/>
-      <c r="D18" s="16"/>
-      <c r="E18" s="16"/>
-      <c r="F18" s="16"/>
-      <c r="G18" s="16"/>
-      <c r="H18" s="16"/>
-      <c r="I18" s="16"/>
-      <c r="J18" s="16"/>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
-      <c r="N18" s="16"/>
-      <c r="O18" s="16"/>
-      <c r="P18" s="16"/>
-      <c r="Q18" s="16"/>
-      <c r="R18" s="16"/>
-      <c r="S18" s="16"/>
-      <c r="T18" s="16"/>
-      <c r="U18" s="16"/>
-      <c r="V18" s="16"/>
-      <c r="W18" s="16"/>
-      <c r="X18" s="16"/>
-      <c r="Y18" s="16"/>
+      <c r="A18" s="17"/>
+      <c r="B18" s="17"/>
+      <c r="C18" s="17"/>
+      <c r="D18" s="17"/>
+      <c r="E18" s="17"/>
+      <c r="F18" s="17"/>
+      <c r="G18" s="17"/>
+      <c r="H18" s="17"/>
+      <c r="I18" s="17"/>
+      <c r="J18" s="17"/>
+      <c r="K18" s="17"/>
+      <c r="L18" s="17"/>
+      <c r="M18" s="17"/>
+      <c r="N18" s="17"/>
+      <c r="O18" s="17"/>
+      <c r="P18" s="17"/>
+      <c r="Q18" s="17"/>
+      <c r="R18" s="17"/>
+      <c r="S18" s="17"/>
+      <c r="T18" s="17"/>
+      <c r="U18" s="17"/>
+      <c r="V18" s="17"/>
+      <c r="W18" s="17"/>
+      <c r="X18" s="17"/>
+      <c r="Y18" s="17"/>
       <c r="Z18" s="3"/>
       <c r="AA18" s="13">
         <v>15.0</v>
@@ -1803,8 +1947,8 @@
         <v>37</v>
       </c>
       <c r="B19" s="12">
-        <f> Z8 + Z2 +Z5 +Z4 +Z4 +Z4 +Z2 +Z7 + Z12 + Z13 +Z12 +Z11</f>
-        <v>123</v>
+        <f> Z8 + Z2 +Z5 +Z4 +Z4 +Z4 +Z2 +Z7 + Z12 + Z13 +Z12 +Z11 +Z12 +Z3 + Z8 + Z12 + Z1</f>
+        <v>180</v>
       </c>
       <c r="C19" s="12" t="s">
         <v>36</v>
@@ -1812,7 +1956,7 @@
       <c r="D19" s="13">
         <v>8.0</v>
       </c>
-      <c r="E19" s="17">
+      <c r="E19" s="16">
         <v>2.0</v>
       </c>
       <c r="F19" s="13">
@@ -1857,50 +2001,62 @@
       <c r="S19" s="12">
         <v>16.0</v>
       </c>
-      <c r="T19" s="16"/>
-      <c r="U19" s="16"/>
-      <c r="V19" s="16"/>
-      <c r="W19" s="16"/>
-      <c r="X19" s="16"/>
-      <c r="Y19" s="16"/>
+      <c r="T19" s="13">
+        <v>12.0</v>
+      </c>
+      <c r="U19" s="12">
+        <v>16.0</v>
+      </c>
+      <c r="V19" s="15">
+        <v>3.0</v>
+      </c>
+      <c r="W19" s="13">
+        <v>8.0</v>
+      </c>
+      <c r="X19" s="13">
+        <v>12.0</v>
+      </c>
+      <c r="Y19" s="11">
+        <v>1.0</v>
+      </c>
       <c r="AA19" s="14" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="16"/>
-      <c r="B20" s="16"/>
-      <c r="C20" s="16"/>
-      <c r="D20" s="16"/>
-      <c r="E20" s="16"/>
-      <c r="F20" s="16"/>
-      <c r="G20" s="16"/>
-      <c r="H20" s="16"/>
-      <c r="I20" s="16"/>
-      <c r="J20" s="16"/>
-      <c r="K20" s="16"/>
-      <c r="L20" s="16"/>
-      <c r="M20" s="16"/>
-      <c r="N20" s="16"/>
-      <c r="O20" s="16"/>
-      <c r="P20" s="16"/>
-      <c r="Q20" s="16"/>
-      <c r="R20" s="16"/>
-      <c r="S20" s="16"/>
-      <c r="T20" s="16"/>
-      <c r="U20" s="16"/>
-      <c r="V20" s="16"/>
-      <c r="W20" s="16"/>
-      <c r="X20" s="16"/>
-      <c r="Y20" s="16"/>
+      <c r="A20" s="17"/>
+      <c r="B20" s="17"/>
+      <c r="C20" s="17"/>
+      <c r="D20" s="17"/>
+      <c r="E20" s="17"/>
+      <c r="F20" s="17"/>
+      <c r="G20" s="17"/>
+      <c r="H20" s="17"/>
+      <c r="I20" s="17"/>
+      <c r="J20" s="17"/>
+      <c r="K20" s="17"/>
+      <c r="L20" s="17"/>
+      <c r="M20" s="17"/>
+      <c r="N20" s="17"/>
+      <c r="O20" s="17"/>
+      <c r="P20" s="17"/>
+      <c r="Q20" s="17"/>
+      <c r="R20" s="17"/>
+      <c r="S20" s="17"/>
+      <c r="T20" s="17"/>
+      <c r="U20" s="17"/>
+      <c r="V20" s="17"/>
+      <c r="W20" s="17"/>
+      <c r="X20" s="17"/>
+      <c r="Y20" s="17"/>
     </row>
     <row r="21">
       <c r="A21" s="12" t="s">
         <v>38</v>
       </c>
       <c r="B21" s="12">
-        <f>Z2 +Z2 +Z1 +Z1 +Z5+Z2 + Z14 + Z15 +Z4 +Z8 +Z5</f>
-        <v>156</v>
+        <f>Z2 +Z2 +Z1 +Z1 +Z5+Z2 + Z14 + Z15 +Z4 +Z8 +Z5 +Z10 + Z10</f>
+        <v>168</v>
       </c>
       <c r="C21" s="12" t="s">
         <v>39</v>
@@ -1911,10 +2067,10 @@
       <c r="E21" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="F21" s="17">
+      <c r="F21" s="16">
         <v>2.0</v>
       </c>
-      <c r="G21" s="17">
+      <c r="G21" s="16">
         <v>2.0</v>
       </c>
       <c r="H21" s="14" t="s">
@@ -1953,39 +2109,51 @@
       <c r="S21" s="13">
         <v>5.0</v>
       </c>
-      <c r="T21" s="16"/>
-      <c r="U21" s="16"/>
-      <c r="V21" s="16"/>
-      <c r="W21" s="16"/>
-      <c r="X21" s="16"/>
-      <c r="Y21" s="16"/>
+      <c r="T21" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="U21" s="12">
+        <v>20.0</v>
+      </c>
+      <c r="V21" s="13">
+        <v>10.0</v>
+      </c>
+      <c r="W21" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="X21" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y21" s="13">
+        <v>10.0</v>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="16"/>
-      <c r="B22" s="16"/>
-      <c r="C22" s="16"/>
-      <c r="D22" s="16"/>
-      <c r="E22" s="16"/>
-      <c r="F22" s="16"/>
-      <c r="G22" s="16"/>
-      <c r="H22" s="16"/>
-      <c r="I22" s="16"/>
-      <c r="J22" s="16"/>
-      <c r="K22" s="16"/>
-      <c r="L22" s="16"/>
-      <c r="M22" s="16"/>
-      <c r="N22" s="16"/>
-      <c r="O22" s="16"/>
-      <c r="P22" s="16"/>
-      <c r="Q22" s="16"/>
-      <c r="R22" s="16"/>
-      <c r="S22" s="16"/>
-      <c r="T22" s="16"/>
-      <c r="U22" s="16"/>
-      <c r="V22" s="16"/>
-      <c r="W22" s="16"/>
-      <c r="X22" s="16"/>
-      <c r="Y22" s="16"/>
+      <c r="A22" s="17"/>
+      <c r="B22" s="17"/>
+      <c r="C22" s="17"/>
+      <c r="D22" s="17"/>
+      <c r="E22" s="17"/>
+      <c r="F22" s="17"/>
+      <c r="G22" s="17"/>
+      <c r="H22" s="17"/>
+      <c r="I22" s="17"/>
+      <c r="J22" s="17"/>
+      <c r="K22" s="17"/>
+      <c r="L22" s="17"/>
+      <c r="M22" s="17"/>
+      <c r="N22" s="17"/>
+      <c r="O22" s="17"/>
+      <c r="P22" s="17"/>
+      <c r="Q22" s="17"/>
+      <c r="R22" s="17"/>
+      <c r="S22" s="17"/>
+      <c r="T22" s="17"/>
+      <c r="U22" s="17"/>
+      <c r="V22" s="17"/>
+      <c r="W22" s="17"/>
+      <c r="X22" s="17"/>
+      <c r="Y22" s="17"/>
       <c r="Z22" s="19"/>
     </row>
     <row r="23">
@@ -1993,8 +2161,8 @@
         <v>40</v>
       </c>
       <c r="B23" s="12">
-        <f>Z9 +Z1 +Z10 +Z1 + Z4 + Z4 +Z8 +Z5 +Z2 +Z10</f>
-        <v>134</v>
+        <f>Z9 +Z1 +Z10 +Z1 + Z4 + Z4 +Z8 +Z5 +Z2 +Z10 +Z5 +Z5 + Z4</f>
+        <v>169</v>
       </c>
       <c r="C23" s="12" t="s">
         <v>39</v>
@@ -2047,40 +2215,52 @@
       <c r="S23" s="13">
         <v>10.0</v>
       </c>
-      <c r="T23" s="16"/>
-      <c r="U23" s="16"/>
-      <c r="V23" s="16"/>
-      <c r="W23" s="16"/>
-      <c r="X23" s="16"/>
-      <c r="Y23" s="16"/>
+      <c r="T23" s="13">
+        <v>5.0</v>
+      </c>
+      <c r="U23" s="13">
+        <v>5.0</v>
+      </c>
+      <c r="V23" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="W23" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="X23" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y23" s="13">
+        <v>4.0</v>
+      </c>
       <c r="Z23" s="19"/>
     </row>
     <row r="24">
-      <c r="A24" s="16"/>
-      <c r="B24" s="16"/>
-      <c r="C24" s="16"/>
-      <c r="D24" s="16"/>
-      <c r="E24" s="16"/>
-      <c r="F24" s="16"/>
-      <c r="G24" s="16"/>
-      <c r="H24" s="16"/>
-      <c r="I24" s="16"/>
-      <c r="J24" s="16"/>
-      <c r="K24" s="16"/>
-      <c r="L24" s="16"/>
-      <c r="M24" s="16"/>
-      <c r="N24" s="16"/>
-      <c r="O24" s="16"/>
-      <c r="P24" s="16"/>
-      <c r="Q24" s="16"/>
-      <c r="R24" s="16"/>
-      <c r="S24" s="16"/>
-      <c r="T24" s="16"/>
-      <c r="U24" s="16"/>
-      <c r="V24" s="16"/>
-      <c r="W24" s="16"/>
-      <c r="X24" s="16"/>
-      <c r="Y24" s="16"/>
+      <c r="A24" s="17"/>
+      <c r="B24" s="17"/>
+      <c r="C24" s="17"/>
+      <c r="D24" s="17"/>
+      <c r="E24" s="17"/>
+      <c r="F24" s="17"/>
+      <c r="G24" s="17"/>
+      <c r="H24" s="17"/>
+      <c r="I24" s="17"/>
+      <c r="J24" s="17"/>
+      <c r="K24" s="17"/>
+      <c r="L24" s="17"/>
+      <c r="M24" s="17"/>
+      <c r="N24" s="17"/>
+      <c r="O24" s="17"/>
+      <c r="P24" s="17"/>
+      <c r="Q24" s="17"/>
+      <c r="R24" s="17"/>
+      <c r="S24" s="17"/>
+      <c r="T24" s="17"/>
+      <c r="U24" s="17"/>
+      <c r="V24" s="17"/>
+      <c r="W24" s="17"/>
+      <c r="X24" s="17"/>
+      <c r="Y24" s="17"/>
       <c r="Z24" s="19"/>
     </row>
     <row r="25">
@@ -2088,8 +2268,8 @@
         <v>41</v>
       </c>
       <c r="B25" s="12">
-        <f> Z9 + Z1 +Z8 +Z3 +Z3 +Z8 +Z5 + Z11 + Z1 + Z13 +Z7</f>
-        <v>133</v>
+        <f> Z9 + Z1 +Z8 +Z3 +Z3 +Z8 +Z5 + Z11 + Z1 + Z13 +Z7 +Z6 +Z7 + Z9</f>
+        <v>159</v>
       </c>
       <c r="C25" s="12" t="s">
         <v>42</v>
@@ -2142,40 +2322,52 @@
       <c r="S25" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="T25" s="16"/>
-      <c r="U25" s="16"/>
-      <c r="V25" s="16"/>
-      <c r="W25" s="16"/>
-      <c r="X25" s="16"/>
-      <c r="Y25" s="16"/>
+      <c r="T25" s="13">
+        <v>6.0</v>
+      </c>
+      <c r="U25" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="V25" s="13">
+        <v>7.0</v>
+      </c>
+      <c r="W25" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="X25" s="12">
+        <v>18.0</v>
+      </c>
+      <c r="Y25" s="13">
+        <v>9.0</v>
+      </c>
       <c r="Z25" s="19"/>
     </row>
     <row r="26">
-      <c r="A26" s="16"/>
-      <c r="B26" s="16"/>
-      <c r="C26" s="16"/>
-      <c r="D26" s="16"/>
-      <c r="E26" s="16"/>
-      <c r="F26" s="16"/>
-      <c r="G26" s="16"/>
-      <c r="H26" s="16"/>
-      <c r="I26" s="16"/>
-      <c r="J26" s="16"/>
-      <c r="K26" s="16"/>
-      <c r="L26" s="16"/>
-      <c r="M26" s="16"/>
-      <c r="N26" s="16"/>
-      <c r="O26" s="16"/>
-      <c r="P26" s="16"/>
-      <c r="Q26" s="16"/>
-      <c r="R26" s="16"/>
-      <c r="S26" s="16"/>
-      <c r="T26" s="16"/>
-      <c r="U26" s="16"/>
-      <c r="V26" s="16"/>
-      <c r="W26" s="16"/>
-      <c r="X26" s="16"/>
-      <c r="Y26" s="16"/>
+      <c r="A26" s="17"/>
+      <c r="B26" s="17"/>
+      <c r="C26" s="17"/>
+      <c r="D26" s="17"/>
+      <c r="E26" s="17"/>
+      <c r="F26" s="17"/>
+      <c r="G26" s="17"/>
+      <c r="H26" s="17"/>
+      <c r="I26" s="17"/>
+      <c r="J26" s="17"/>
+      <c r="K26" s="17"/>
+      <c r="L26" s="17"/>
+      <c r="M26" s="17"/>
+      <c r="N26" s="17"/>
+      <c r="O26" s="17"/>
+      <c r="P26" s="17"/>
+      <c r="Q26" s="17"/>
+      <c r="R26" s="17"/>
+      <c r="S26" s="17"/>
+      <c r="T26" s="17"/>
+      <c r="U26" s="17"/>
+      <c r="V26" s="17"/>
+      <c r="W26" s="17"/>
+      <c r="X26" s="17"/>
+      <c r="Y26" s="17"/>
       <c r="Z26" s="19"/>
     </row>
     <row r="27">
@@ -2183,8 +2375,8 @@
         <v>43</v>
       </c>
       <c r="B27" s="12">
-        <f>Z11 +Z6 +Z6 +Z5 +Z9 +Z2 +Z3 + Z10 + Z10 +Z13 +Z6 +Z8</f>
-        <v>112</v>
+        <f>Z11 +Z6 +Z6 +Z5 +Z9 +Z2 +Z3 + Z10 + Z10 +Z13 +Z6 +Z8 +Z8 +Z12 +Z11 + Z4 + Z3</f>
+        <v>158</v>
       </c>
       <c r="C27" s="12" t="s">
         <v>42</v>
@@ -2237,40 +2429,52 @@
       <c r="S27" s="13">
         <v>8.0</v>
       </c>
-      <c r="T27" s="16"/>
-      <c r="U27" s="16"/>
-      <c r="V27" s="16"/>
-      <c r="W27" s="16"/>
-      <c r="X27" s="16"/>
-      <c r="Y27" s="16"/>
+      <c r="T27" s="13">
+        <v>8.0</v>
+      </c>
+      <c r="U27" s="13">
+        <v>12.0</v>
+      </c>
+      <c r="V27" s="13">
+        <v>11.0</v>
+      </c>
+      <c r="W27" s="13">
+        <v>4.0</v>
+      </c>
+      <c r="X27" s="15">
+        <v>3.0</v>
+      </c>
+      <c r="Y27" s="12">
+        <v>16.0</v>
+      </c>
       <c r="Z27" s="19"/>
     </row>
     <row r="28">
-      <c r="A28" s="16"/>
-      <c r="B28" s="16"/>
-      <c r="C28" s="16"/>
-      <c r="D28" s="16"/>
-      <c r="E28" s="16"/>
-      <c r="F28" s="16"/>
-      <c r="G28" s="16"/>
-      <c r="H28" s="16"/>
-      <c r="I28" s="16"/>
-      <c r="J28" s="16"/>
-      <c r="K28" s="16"/>
-      <c r="L28" s="16"/>
-      <c r="M28" s="16"/>
-      <c r="N28" s="16"/>
-      <c r="O28" s="16"/>
-      <c r="P28" s="16"/>
-      <c r="Q28" s="16"/>
-      <c r="R28" s="16"/>
-      <c r="S28" s="16"/>
-      <c r="T28" s="16"/>
-      <c r="U28" s="16"/>
-      <c r="V28" s="16"/>
-      <c r="W28" s="16"/>
-      <c r="X28" s="16"/>
-      <c r="Y28" s="16"/>
+      <c r="A28" s="17"/>
+      <c r="B28" s="17"/>
+      <c r="C28" s="17"/>
+      <c r="D28" s="17"/>
+      <c r="E28" s="17"/>
+      <c r="F28" s="17"/>
+      <c r="G28" s="17"/>
+      <c r="H28" s="17"/>
+      <c r="I28" s="17"/>
+      <c r="J28" s="17"/>
+      <c r="K28" s="17"/>
+      <c r="L28" s="17"/>
+      <c r="M28" s="17"/>
+      <c r="N28" s="17"/>
+      <c r="O28" s="17"/>
+      <c r="P28" s="17"/>
+      <c r="Q28" s="17"/>
+      <c r="R28" s="17"/>
+      <c r="S28" s="17"/>
+      <c r="T28" s="17"/>
+      <c r="U28" s="17"/>
+      <c r="V28" s="17"/>
+      <c r="W28" s="17"/>
+      <c r="X28" s="17"/>
+      <c r="Y28" s="17"/>
       <c r="Z28" s="19"/>
     </row>
     <row r="29">
@@ -2278,8 +2482,8 @@
         <v>44</v>
       </c>
       <c r="B29" s="12">
-        <f>Z15 +Z13 +Z14</f>
-        <v>6</v>
+        <f>Z15 +Z13 +Z14 + Z13</f>
+        <v>9</v>
       </c>
       <c r="C29" s="12" t="s">
         <v>45</v>
@@ -2332,40 +2536,52 @@
       <c r="S29" s="13">
         <v>14.0</v>
       </c>
-      <c r="T29" s="16"/>
-      <c r="U29" s="16"/>
-      <c r="V29" s="16"/>
-      <c r="W29" s="16"/>
-      <c r="X29" s="16"/>
-      <c r="Y29" s="16"/>
+      <c r="T29" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="U29" s="12">
+        <v>17.0</v>
+      </c>
+      <c r="V29" s="12">
+        <v>18.0</v>
+      </c>
+      <c r="W29" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="X29" s="13">
+        <v>13.0</v>
+      </c>
+      <c r="Y29" s="14" t="s">
+        <v>27</v>
+      </c>
       <c r="Z29" s="19"/>
     </row>
     <row r="30">
-      <c r="A30" s="16"/>
-      <c r="B30" s="16"/>
-      <c r="C30" s="16"/>
-      <c r="D30" s="16"/>
-      <c r="E30" s="16"/>
-      <c r="F30" s="16"/>
-      <c r="G30" s="16"/>
-      <c r="H30" s="16"/>
-      <c r="I30" s="16"/>
-      <c r="J30" s="16"/>
-      <c r="K30" s="16"/>
-      <c r="L30" s="16"/>
-      <c r="M30" s="16"/>
-      <c r="N30" s="16"/>
-      <c r="O30" s="16"/>
-      <c r="P30" s="16"/>
-      <c r="Q30" s="16"/>
-      <c r="R30" s="16"/>
-      <c r="S30" s="16"/>
-      <c r="T30" s="16"/>
-      <c r="U30" s="16"/>
-      <c r="V30" s="16"/>
-      <c r="W30" s="16"/>
-      <c r="X30" s="16"/>
-      <c r="Y30" s="16"/>
+      <c r="A30" s="17"/>
+      <c r="B30" s="17"/>
+      <c r="C30" s="17"/>
+      <c r="D30" s="17"/>
+      <c r="E30" s="17"/>
+      <c r="F30" s="17"/>
+      <c r="G30" s="17"/>
+      <c r="H30" s="17"/>
+      <c r="I30" s="17"/>
+      <c r="J30" s="17"/>
+      <c r="K30" s="17"/>
+      <c r="L30" s="17"/>
+      <c r="M30" s="17"/>
+      <c r="N30" s="17"/>
+      <c r="O30" s="17"/>
+      <c r="P30" s="17"/>
+      <c r="Q30" s="17"/>
+      <c r="R30" s="17"/>
+      <c r="S30" s="17"/>
+      <c r="T30" s="17"/>
+      <c r="U30" s="17"/>
+      <c r="V30" s="17"/>
+      <c r="W30" s="17"/>
+      <c r="X30" s="17"/>
+      <c r="Y30" s="17"/>
       <c r="Z30" s="19"/>
     </row>
     <row r="31">
@@ -2373,8 +2589,8 @@
         <v>46</v>
       </c>
       <c r="B31" s="12">
-        <f>Z13</f>
-        <v>3</v>
+        <f>Z13 +Z14</f>
+        <v>5</v>
       </c>
       <c r="C31" s="12" t="s">
         <v>45</v>
@@ -2427,40 +2643,52 @@
       <c r="S31" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="T31" s="16"/>
-      <c r="U31" s="16"/>
-      <c r="V31" s="16"/>
-      <c r="W31" s="16"/>
-      <c r="X31" s="16"/>
-      <c r="Y31" s="16"/>
+      <c r="T31" s="12">
+        <v>19.0</v>
+      </c>
+      <c r="U31" s="12">
+        <v>19.0</v>
+      </c>
+      <c r="V31" s="13">
+        <v>14.0</v>
+      </c>
+      <c r="W31" s="12">
+        <v>17.0</v>
+      </c>
+      <c r="X31" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y31" s="14" t="s">
+        <v>27</v>
+      </c>
       <c r="Z31" s="19"/>
     </row>
     <row r="32">
-      <c r="A32" s="16"/>
-      <c r="B32" s="16"/>
-      <c r="C32" s="16"/>
-      <c r="D32" s="16"/>
-      <c r="E32" s="16"/>
-      <c r="F32" s="16"/>
-      <c r="G32" s="16"/>
-      <c r="H32" s="16"/>
-      <c r="I32" s="16"/>
-      <c r="J32" s="16"/>
-      <c r="K32" s="16"/>
-      <c r="L32" s="16"/>
-      <c r="M32" s="16"/>
-      <c r="N32" s="16"/>
-      <c r="O32" s="16"/>
-      <c r="P32" s="16"/>
-      <c r="Q32" s="16"/>
-      <c r="R32" s="16"/>
-      <c r="S32" s="16"/>
-      <c r="T32" s="16"/>
-      <c r="U32" s="16"/>
-      <c r="V32" s="16"/>
-      <c r="W32" s="16"/>
-      <c r="X32" s="16"/>
-      <c r="Y32" s="16"/>
+      <c r="A32" s="17"/>
+      <c r="B32" s="17"/>
+      <c r="C32" s="17"/>
+      <c r="D32" s="17"/>
+      <c r="E32" s="17"/>
+      <c r="F32" s="17"/>
+      <c r="G32" s="17"/>
+      <c r="H32" s="17"/>
+      <c r="I32" s="17"/>
+      <c r="J32" s="17"/>
+      <c r="K32" s="17"/>
+      <c r="L32" s="17"/>
+      <c r="M32" s="17"/>
+      <c r="N32" s="17"/>
+      <c r="O32" s="17"/>
+      <c r="P32" s="17"/>
+      <c r="Q32" s="17"/>
+      <c r="R32" s="17"/>
+      <c r="S32" s="17"/>
+      <c r="T32" s="17"/>
+      <c r="U32" s="17"/>
+      <c r="V32" s="17"/>
+      <c r="W32" s="17"/>
+      <c r="X32" s="17"/>
+      <c r="Y32" s="17"/>
       <c r="Z32" s="19"/>
     </row>
     <row r="33">
@@ -2468,8 +2696,8 @@
         <v>47</v>
       </c>
       <c r="B33" s="12">
-        <f> Z1 +Z4 +Z7 +Z12 +Z1 +Z2 +Z11 +Z1 +Z1 + Z5 + Z1 +Z1 +Z3 +Z1</f>
-        <v>253</v>
+        <f> Z1 +Z4 +Z7 +Z12 +Z1 +Z2 +Z11 +Z1 +Z1 + Z5 + Z1 +Z1 +Z3 +Z1 +Z1 +Z1 +Z9 + Z1 + Z13</f>
+        <v>338</v>
       </c>
       <c r="C33" s="12" t="s">
         <v>48</v>
@@ -2522,40 +2750,52 @@
       <c r="S33" s="11">
         <v>1.0</v>
       </c>
-      <c r="T33" s="16"/>
-      <c r="U33" s="16"/>
-      <c r="V33" s="16"/>
-      <c r="W33" s="16"/>
-      <c r="X33" s="16"/>
-      <c r="Y33" s="16"/>
+      <c r="T33" s="11">
+        <v>1.0</v>
+      </c>
+      <c r="U33" s="11">
+        <v>1.0</v>
+      </c>
+      <c r="V33" s="13">
+        <v>9.0</v>
+      </c>
+      <c r="W33" s="11">
+        <v>1.0</v>
+      </c>
+      <c r="X33" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y33" s="13">
+        <v>13.0</v>
+      </c>
       <c r="Z33" s="19"/>
     </row>
     <row r="34">
-      <c r="A34" s="16"/>
-      <c r="B34" s="16"/>
-      <c r="C34" s="16"/>
-      <c r="D34" s="16"/>
-      <c r="E34" s="16"/>
-      <c r="F34" s="16"/>
-      <c r="G34" s="16"/>
-      <c r="H34" s="16"/>
-      <c r="I34" s="16"/>
-      <c r="J34" s="16"/>
-      <c r="K34" s="16"/>
-      <c r="L34" s="16"/>
-      <c r="M34" s="16"/>
-      <c r="N34" s="16"/>
-      <c r="O34" s="16"/>
-      <c r="P34" s="16"/>
-      <c r="Q34" s="16"/>
-      <c r="R34" s="16"/>
-      <c r="S34" s="16"/>
-      <c r="T34" s="16"/>
-      <c r="U34" s="16"/>
-      <c r="V34" s="16"/>
-      <c r="W34" s="16"/>
-      <c r="X34" s="16"/>
-      <c r="Y34" s="16"/>
+      <c r="A34" s="17"/>
+      <c r="B34" s="17"/>
+      <c r="C34" s="17"/>
+      <c r="D34" s="17"/>
+      <c r="E34" s="17"/>
+      <c r="F34" s="17"/>
+      <c r="G34" s="17"/>
+      <c r="H34" s="17"/>
+      <c r="I34" s="17"/>
+      <c r="J34" s="17"/>
+      <c r="K34" s="17"/>
+      <c r="L34" s="17"/>
+      <c r="M34" s="17"/>
+      <c r="N34" s="17"/>
+      <c r="O34" s="17"/>
+      <c r="P34" s="17"/>
+      <c r="Q34" s="17"/>
+      <c r="R34" s="17"/>
+      <c r="S34" s="17"/>
+      <c r="T34" s="17"/>
+      <c r="U34" s="17"/>
+      <c r="V34" s="17"/>
+      <c r="W34" s="17"/>
+      <c r="X34" s="17"/>
+      <c r="Y34" s="17"/>
       <c r="Z34" s="19"/>
     </row>
     <row r="35">
@@ -2563,13 +2803,13 @@
         <v>49</v>
       </c>
       <c r="B35" s="12">
-        <f> Z2 +Z9 +Z5 +Z7 +Z4 + Z9 + Z12 + Z8 +Z5 +Z2</f>
-        <v>110</v>
+        <f> Z2 +Z9 +Z5 +Z7 +Z4 + Z9 + Z12 + Z8 +Z5 +Z2 +Z4 +Z3 +Z5 + Z5 + Z3</f>
+        <v>177</v>
       </c>
       <c r="C35" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="D35" s="17">
+      <c r="D35" s="16">
         <v>2.0</v>
       </c>
       <c r="E35" s="14" t="s">
@@ -2617,40 +2857,52 @@
       <c r="S35" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="T35" s="16"/>
-      <c r="U35" s="16"/>
-      <c r="V35" s="16"/>
-      <c r="W35" s="16"/>
-      <c r="X35" s="16"/>
-      <c r="Y35" s="16"/>
+      <c r="T35" s="13">
+        <v>4.0</v>
+      </c>
+      <c r="U35" s="15">
+        <v>3.0</v>
+      </c>
+      <c r="V35" s="13">
+        <v>5.0</v>
+      </c>
+      <c r="W35" s="13">
+        <v>5.0</v>
+      </c>
+      <c r="X35" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y35" s="15">
+        <v>3.0</v>
+      </c>
       <c r="Z35" s="19"/>
     </row>
     <row r="36">
-      <c r="A36" s="16"/>
-      <c r="B36" s="16"/>
-      <c r="C36" s="16"/>
-      <c r="D36" s="16"/>
-      <c r="E36" s="16"/>
-      <c r="F36" s="16"/>
-      <c r="G36" s="16"/>
-      <c r="H36" s="16"/>
-      <c r="I36" s="16"/>
-      <c r="J36" s="16"/>
-      <c r="K36" s="16"/>
-      <c r="L36" s="16"/>
-      <c r="M36" s="16"/>
-      <c r="N36" s="16"/>
-      <c r="O36" s="16"/>
-      <c r="P36" s="16"/>
-      <c r="Q36" s="16"/>
-      <c r="R36" s="16"/>
-      <c r="S36" s="16"/>
-      <c r="T36" s="16"/>
-      <c r="U36" s="16"/>
-      <c r="V36" s="16"/>
-      <c r="W36" s="16"/>
-      <c r="X36" s="16"/>
-      <c r="Y36" s="16"/>
+      <c r="A36" s="17"/>
+      <c r="B36" s="17"/>
+      <c r="C36" s="17"/>
+      <c r="D36" s="17"/>
+      <c r="E36" s="17"/>
+      <c r="F36" s="17"/>
+      <c r="G36" s="17"/>
+      <c r="H36" s="17"/>
+      <c r="I36" s="17"/>
+      <c r="J36" s="17"/>
+      <c r="K36" s="17"/>
+      <c r="L36" s="17"/>
+      <c r="M36" s="17"/>
+      <c r="N36" s="17"/>
+      <c r="O36" s="17"/>
+      <c r="P36" s="17"/>
+      <c r="Q36" s="17"/>
+      <c r="R36" s="17"/>
+      <c r="S36" s="17"/>
+      <c r="T36" s="17"/>
+      <c r="U36" s="17"/>
+      <c r="V36" s="17"/>
+      <c r="W36" s="17"/>
+      <c r="X36" s="17"/>
+      <c r="Y36" s="17"/>
       <c r="Z36" s="19"/>
     </row>
     <row r="37">
@@ -2658,8 +2910,8 @@
         <v>50</v>
       </c>
       <c r="B37" s="12">
-        <f>Z14 +Z15 +Z12 +Z13 +Z14 + Z8</f>
-        <v>20</v>
+        <f>Z14 +Z15 +Z12 +Z13 +Z14 + Z8 +Z13 +Z15</f>
+        <v>24</v>
       </c>
       <c r="C37" s="12" t="s">
         <v>51</v>
@@ -2712,48 +2964,60 @@
       <c r="S37" s="12">
         <v>17.0</v>
       </c>
-      <c r="T37" s="16"/>
-      <c r="U37" s="16"/>
-      <c r="V37" s="16"/>
-      <c r="W37" s="16"/>
-      <c r="X37" s="16"/>
-      <c r="Y37" s="16"/>
+      <c r="T37" s="13">
+        <v>13.0</v>
+      </c>
+      <c r="U37" s="12">
+        <v>18.0</v>
+      </c>
+      <c r="V37" s="13">
+        <v>15.0</v>
+      </c>
+      <c r="W37" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="X37" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y37" s="14" t="s">
+        <v>27</v>
+      </c>
       <c r="Z37" s="19"/>
     </row>
     <row r="38">
-      <c r="A38" s="16"/>
-      <c r="B38" s="16"/>
-      <c r="C38" s="16"/>
-      <c r="D38" s="16"/>
-      <c r="E38" s="16"/>
-      <c r="F38" s="16"/>
-      <c r="G38" s="16"/>
-      <c r="H38" s="16"/>
-      <c r="I38" s="16"/>
-      <c r="J38" s="16"/>
-      <c r="K38" s="16"/>
-      <c r="L38" s="16"/>
-      <c r="M38" s="16"/>
-      <c r="N38" s="16"/>
-      <c r="O38" s="16"/>
-      <c r="P38" s="16"/>
-      <c r="Q38" s="16"/>
-      <c r="R38" s="16"/>
-      <c r="S38" s="16"/>
-      <c r="T38" s="16"/>
-      <c r="U38" s="16"/>
-      <c r="V38" s="16"/>
-      <c r="W38" s="16"/>
-      <c r="X38" s="16"/>
-      <c r="Y38" s="16"/>
+      <c r="A38" s="17"/>
+      <c r="B38" s="17"/>
+      <c r="C38" s="17"/>
+      <c r="D38" s="17"/>
+      <c r="E38" s="17"/>
+      <c r="F38" s="17"/>
+      <c r="G38" s="17"/>
+      <c r="H38" s="17"/>
+      <c r="I38" s="17"/>
+      <c r="J38" s="17"/>
+      <c r="K38" s="17"/>
+      <c r="L38" s="17"/>
+      <c r="M38" s="17"/>
+      <c r="N38" s="17"/>
+      <c r="O38" s="17"/>
+      <c r="P38" s="17"/>
+      <c r="Q38" s="17"/>
+      <c r="R38" s="17"/>
+      <c r="S38" s="17"/>
+      <c r="T38" s="17"/>
+      <c r="U38" s="17"/>
+      <c r="V38" s="17"/>
+      <c r="W38" s="17"/>
+      <c r="X38" s="17"/>
+      <c r="Y38" s="17"/>
     </row>
     <row r="39">
       <c r="A39" s="12" t="s">
         <v>52</v>
       </c>
       <c r="B39" s="12">
-        <f> Z10 +Z5 +Z8 +Z10 + Z5 + Z4 + Z10 +Z1 +Z1</f>
-        <v>111</v>
+        <f> Z10 +Z5 +Z8 +Z10 + Z5 + Z4 + Z10 +Z1 +Z1 +Z7 + Z10 + Z5 + Z7</f>
+        <v>146</v>
       </c>
       <c r="C39" s="12" t="s">
         <v>51</v>
@@ -2806,39 +3070,51 @@
       <c r="S39" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="T39" s="16"/>
-      <c r="U39" s="16"/>
-      <c r="V39" s="16"/>
-      <c r="W39" s="16"/>
-      <c r="X39" s="16"/>
-      <c r="Y39" s="16"/>
+      <c r="T39" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="U39" s="13">
+        <v>7.0</v>
+      </c>
+      <c r="V39" s="12">
+        <v>16.0</v>
+      </c>
+      <c r="W39" s="13">
+        <v>10.0</v>
+      </c>
+      <c r="X39" s="13">
+        <v>5.0</v>
+      </c>
+      <c r="Y39" s="13">
+        <v>7.0</v>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" s="16"/>
-      <c r="B40" s="16"/>
-      <c r="C40" s="16"/>
-      <c r="D40" s="16"/>
-      <c r="E40" s="16"/>
-      <c r="F40" s="16"/>
-      <c r="G40" s="16"/>
-      <c r="H40" s="16"/>
-      <c r="I40" s="16"/>
-      <c r="J40" s="16"/>
-      <c r="K40" s="16"/>
-      <c r="L40" s="16"/>
-      <c r="M40" s="16"/>
-      <c r="N40" s="16"/>
-      <c r="O40" s="16"/>
-      <c r="P40" s="16"/>
-      <c r="Q40" s="16"/>
-      <c r="R40" s="16"/>
-      <c r="S40" s="16"/>
-      <c r="T40" s="16"/>
-      <c r="U40" s="16"/>
-      <c r="V40" s="16"/>
-      <c r="W40" s="16"/>
-      <c r="X40" s="16"/>
-      <c r="Y40" s="16"/>
+      <c r="A40" s="17"/>
+      <c r="B40" s="17"/>
+      <c r="C40" s="17"/>
+      <c r="D40" s="17"/>
+      <c r="E40" s="17"/>
+      <c r="F40" s="17"/>
+      <c r="G40" s="17"/>
+      <c r="H40" s="17"/>
+      <c r="I40" s="17"/>
+      <c r="J40" s="17"/>
+      <c r="K40" s="17"/>
+      <c r="L40" s="17"/>
+      <c r="M40" s="17"/>
+      <c r="N40" s="17"/>
+      <c r="O40" s="17"/>
+      <c r="P40" s="17"/>
+      <c r="Q40" s="17"/>
+      <c r="R40" s="17"/>
+      <c r="S40" s="17"/>
+      <c r="T40" s="17"/>
+      <c r="U40" s="17"/>
+      <c r="V40" s="17"/>
+      <c r="W40" s="17"/>
+      <c r="X40" s="17"/>
+      <c r="Y40" s="17"/>
     </row>
     <row r="41">
       <c r="A41" s="12" t="s">
@@ -2899,39 +3175,51 @@
       <c r="S41" s="12">
         <v>18.0</v>
       </c>
-      <c r="T41" s="16"/>
-      <c r="U41" s="16"/>
-      <c r="V41" s="16"/>
-      <c r="W41" s="16"/>
-      <c r="X41" s="16"/>
-      <c r="Y41" s="16"/>
+      <c r="T41" s="12">
+        <v>16.0</v>
+      </c>
+      <c r="U41" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="V41" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="W41" s="12">
+        <v>18.0</v>
+      </c>
+      <c r="X41" s="12">
+        <v>19.0</v>
+      </c>
+      <c r="Y41" s="12">
+        <v>17.0</v>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" s="16"/>
-      <c r="B42" s="16"/>
-      <c r="C42" s="16"/>
-      <c r="D42" s="16"/>
-      <c r="E42" s="16"/>
-      <c r="F42" s="16"/>
-      <c r="G42" s="16"/>
-      <c r="H42" s="16"/>
-      <c r="I42" s="16"/>
-      <c r="J42" s="16"/>
-      <c r="K42" s="16"/>
-      <c r="L42" s="16"/>
-      <c r="M42" s="16"/>
-      <c r="N42" s="16"/>
-      <c r="O42" s="16"/>
-      <c r="P42" s="16"/>
-      <c r="Q42" s="16"/>
-      <c r="R42" s="16"/>
-      <c r="S42" s="16"/>
-      <c r="T42" s="16"/>
-      <c r="U42" s="16"/>
-      <c r="V42" s="16"/>
-      <c r="W42" s="16"/>
-      <c r="X42" s="16"/>
-      <c r="Y42" s="16"/>
+      <c r="A42" s="17"/>
+      <c r="B42" s="17"/>
+      <c r="C42" s="17"/>
+      <c r="D42" s="17"/>
+      <c r="E42" s="17"/>
+      <c r="F42" s="17"/>
+      <c r="G42" s="17"/>
+      <c r="H42" s="17"/>
+      <c r="I42" s="17"/>
+      <c r="J42" s="17"/>
+      <c r="K42" s="17"/>
+      <c r="L42" s="17"/>
+      <c r="M42" s="17"/>
+      <c r="N42" s="17"/>
+      <c r="O42" s="17"/>
+      <c r="P42" s="17"/>
+      <c r="Q42" s="17"/>
+      <c r="R42" s="17"/>
+      <c r="S42" s="17"/>
+      <c r="T42" s="17"/>
+      <c r="U42" s="17"/>
+      <c r="V42" s="17"/>
+      <c r="W42" s="17"/>
+      <c r="X42" s="17"/>
+      <c r="Y42" s="17"/>
     </row>
     <row r="43">
       <c r="A43" s="12" t="s">
@@ -2991,47 +3279,59 @@
       <c r="S43" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="T43" s="16"/>
-      <c r="U43" s="16"/>
-      <c r="V43" s="16"/>
-      <c r="W43" s="16"/>
-      <c r="X43" s="16"/>
-      <c r="Y43" s="16"/>
+      <c r="T43" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="U43" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="V43" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="W43" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="X43" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y43" s="14" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="44">
-      <c r="A44" s="16"/>
-      <c r="B44" s="16"/>
-      <c r="C44" s="16"/>
-      <c r="D44" s="16"/>
-      <c r="E44" s="16"/>
-      <c r="F44" s="16"/>
-      <c r="G44" s="16"/>
-      <c r="H44" s="16"/>
-      <c r="I44" s="16"/>
-      <c r="J44" s="16"/>
-      <c r="K44" s="16"/>
-      <c r="L44" s="16"/>
-      <c r="M44" s="16"/>
-      <c r="N44" s="16"/>
-      <c r="O44" s="16"/>
-      <c r="P44" s="16"/>
-      <c r="Q44" s="16"/>
-      <c r="R44" s="16"/>
-      <c r="S44" s="16"/>
-      <c r="T44" s="16"/>
-      <c r="U44" s="16"/>
-      <c r="V44" s="16"/>
-      <c r="W44" s="16"/>
-      <c r="X44" s="16"/>
-      <c r="Y44" s="16"/>
+      <c r="A44" s="17"/>
+      <c r="B44" s="17"/>
+      <c r="C44" s="17"/>
+      <c r="D44" s="17"/>
+      <c r="E44" s="17"/>
+      <c r="F44" s="17"/>
+      <c r="G44" s="17"/>
+      <c r="H44" s="17"/>
+      <c r="I44" s="17"/>
+      <c r="J44" s="17"/>
+      <c r="K44" s="17"/>
+      <c r="L44" s="17"/>
+      <c r="M44" s="17"/>
+      <c r="N44" s="17"/>
+      <c r="O44" s="17"/>
+      <c r="P44" s="17"/>
+      <c r="Q44" s="17"/>
+      <c r="R44" s="17"/>
+      <c r="S44" s="17"/>
+      <c r="T44" s="17"/>
+      <c r="U44" s="17"/>
+      <c r="V44" s="17"/>
+      <c r="W44" s="17"/>
+      <c r="X44" s="17"/>
+      <c r="Y44" s="17"/>
     </row>
     <row r="45">
       <c r="A45" s="12" t="s">
         <v>56</v>
       </c>
       <c r="B45" s="12">
-        <f>Z14 +Z14</f>
-        <v>4</v>
+        <f>Z14 +Z14 +Z14 +Z13 + Z14</f>
+        <v>11</v>
       </c>
       <c r="C45" s="12" t="s">
         <v>57</v>
@@ -3084,39 +3384,51 @@
       <c r="S45" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="T45" s="16"/>
-      <c r="U45" s="16"/>
-      <c r="V45" s="16"/>
-      <c r="W45" s="16"/>
-      <c r="X45" s="16"/>
-      <c r="Y45" s="16"/>
+      <c r="T45" s="13">
+        <v>14.0</v>
+      </c>
+      <c r="U45" s="13">
+        <v>13.0</v>
+      </c>
+      <c r="V45" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="W45" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="X45" s="13">
+        <v>14.0</v>
+      </c>
+      <c r="Y45" s="12">
+        <v>22.0</v>
+      </c>
     </row>
     <row r="46">
-      <c r="A46" s="16"/>
-      <c r="B46" s="16"/>
-      <c r="C46" s="16"/>
-      <c r="D46" s="16"/>
-      <c r="E46" s="16"/>
-      <c r="F46" s="16"/>
-      <c r="G46" s="16"/>
-      <c r="H46" s="16"/>
-      <c r="I46" s="16"/>
-      <c r="J46" s="16"/>
-      <c r="K46" s="16"/>
-      <c r="L46" s="16"/>
-      <c r="M46" s="16"/>
-      <c r="N46" s="16"/>
-      <c r="O46" s="16"/>
-      <c r="P46" s="16"/>
-      <c r="Q46" s="16"/>
-      <c r="R46" s="16"/>
-      <c r="S46" s="16"/>
-      <c r="T46" s="16"/>
-      <c r="U46" s="16"/>
-      <c r="V46" s="16"/>
-      <c r="W46" s="16"/>
-      <c r="X46" s="16"/>
-      <c r="Y46" s="16"/>
+      <c r="A46" s="17"/>
+      <c r="B46" s="17"/>
+      <c r="C46" s="17"/>
+      <c r="D46" s="17"/>
+      <c r="E46" s="17"/>
+      <c r="F46" s="17"/>
+      <c r="G46" s="17"/>
+      <c r="H46" s="17"/>
+      <c r="I46" s="17"/>
+      <c r="J46" s="17"/>
+      <c r="K46" s="17"/>
+      <c r="L46" s="17"/>
+      <c r="M46" s="17"/>
+      <c r="N46" s="17"/>
+      <c r="O46" s="17"/>
+      <c r="P46" s="17"/>
+      <c r="Q46" s="17"/>
+      <c r="R46" s="17"/>
+      <c r="S46" s="17"/>
+      <c r="T46" s="17"/>
+      <c r="U46" s="17"/>
+      <c r="V46" s="17"/>
+      <c r="W46" s="17"/>
+      <c r="X46" s="17"/>
+      <c r="Y46" s="17"/>
     </row>
     <row r="47">
       <c r="A47" s="12" t="s">
@@ -3177,47 +3489,59 @@
       <c r="S47" s="12">
         <v>20.0</v>
       </c>
-      <c r="T47" s="16"/>
-      <c r="U47" s="16"/>
-      <c r="V47" s="16"/>
-      <c r="W47" s="16"/>
-      <c r="X47" s="16"/>
-      <c r="Y47" s="16"/>
+      <c r="T47" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="U47" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="V47" s="12">
+        <v>22.0</v>
+      </c>
+      <c r="W47" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="X47" s="12">
+        <v>17.0</v>
+      </c>
+      <c r="Y47" s="14" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="48">
-      <c r="A48" s="16"/>
-      <c r="B48" s="16"/>
-      <c r="C48" s="16"/>
-      <c r="D48" s="16"/>
-      <c r="E48" s="16"/>
-      <c r="F48" s="16"/>
-      <c r="G48" s="16"/>
-      <c r="H48" s="16"/>
-      <c r="I48" s="16"/>
-      <c r="J48" s="16"/>
-      <c r="K48" s="16"/>
-      <c r="L48" s="16"/>
-      <c r="M48" s="16"/>
-      <c r="N48" s="16"/>
-      <c r="O48" s="16"/>
-      <c r="P48" s="16"/>
-      <c r="Q48" s="16"/>
-      <c r="R48" s="16"/>
-      <c r="S48" s="16"/>
-      <c r="T48" s="16"/>
-      <c r="U48" s="16"/>
-      <c r="V48" s="16"/>
-      <c r="W48" s="16"/>
-      <c r="X48" s="16"/>
-      <c r="Y48" s="16"/>
+      <c r="A48" s="17"/>
+      <c r="B48" s="17"/>
+      <c r="C48" s="17"/>
+      <c r="D48" s="17"/>
+      <c r="E48" s="17"/>
+      <c r="F48" s="17"/>
+      <c r="G48" s="17"/>
+      <c r="H48" s="17"/>
+      <c r="I48" s="17"/>
+      <c r="J48" s="17"/>
+      <c r="K48" s="17"/>
+      <c r="L48" s="17"/>
+      <c r="M48" s="17"/>
+      <c r="N48" s="17"/>
+      <c r="O48" s="17"/>
+      <c r="P48" s="17"/>
+      <c r="Q48" s="17"/>
+      <c r="R48" s="17"/>
+      <c r="S48" s="17"/>
+      <c r="T48" s="17"/>
+      <c r="U48" s="17"/>
+      <c r="V48" s="17"/>
+      <c r="W48" s="17"/>
+      <c r="X48" s="17"/>
+      <c r="Y48" s="17"/>
     </row>
     <row r="49">
       <c r="A49" s="12" t="s">
         <v>59</v>
       </c>
       <c r="B49" s="12">
-        <f> Z7 +Z3 +Z12 +Z14 +Z7 +Z6 +Z12 +Z9 + Z6 + Z9 + Z14 +Z4 +Z11</f>
-        <v>98</v>
+        <f> Z7 +Z3 +Z12 +Z14 +Z7 +Z6 +Z12 +Z9 + Z6 + Z9 + Z14 +Z4 +Z11 +Z10 +Z6 + Z2 + Z11</f>
+        <v>139</v>
       </c>
       <c r="C49" s="12" t="s">
         <v>60</v>
@@ -3270,47 +3594,59 @@
       <c r="S49" s="13">
         <v>11.0</v>
       </c>
-      <c r="T49" s="16"/>
-      <c r="U49" s="16"/>
-      <c r="V49" s="16"/>
-      <c r="W49" s="16"/>
-      <c r="X49" s="16"/>
-      <c r="Y49" s="16"/>
+      <c r="T49" s="13">
+        <v>10.0</v>
+      </c>
+      <c r="U49" s="13">
+        <v>6.0</v>
+      </c>
+      <c r="V49" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="W49" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="X49" s="18">
+        <v>2.0</v>
+      </c>
+      <c r="Y49" s="13">
+        <v>11.0</v>
+      </c>
     </row>
     <row r="50">
-      <c r="A50" s="16"/>
-      <c r="B50" s="16"/>
-      <c r="C50" s="16"/>
-      <c r="D50" s="16"/>
-      <c r="E50" s="16"/>
-      <c r="F50" s="16"/>
-      <c r="G50" s="16"/>
-      <c r="H50" s="16"/>
-      <c r="I50" s="16"/>
-      <c r="J50" s="16"/>
-      <c r="K50" s="16"/>
-      <c r="L50" s="16"/>
-      <c r="M50" s="16"/>
-      <c r="N50" s="16"/>
-      <c r="O50" s="16"/>
-      <c r="P50" s="16"/>
-      <c r="Q50" s="16"/>
-      <c r="R50" s="16"/>
-      <c r="S50" s="16"/>
-      <c r="T50" s="16"/>
-      <c r="U50" s="16"/>
-      <c r="V50" s="16"/>
-      <c r="W50" s="16"/>
-      <c r="X50" s="16"/>
-      <c r="Y50" s="16"/>
+      <c r="A50" s="17"/>
+      <c r="B50" s="17"/>
+      <c r="C50" s="17"/>
+      <c r="D50" s="17"/>
+      <c r="E50" s="17"/>
+      <c r="F50" s="17"/>
+      <c r="G50" s="17"/>
+      <c r="H50" s="17"/>
+      <c r="I50" s="17"/>
+      <c r="J50" s="17"/>
+      <c r="K50" s="17"/>
+      <c r="L50" s="17"/>
+      <c r="M50" s="17"/>
+      <c r="N50" s="17"/>
+      <c r="O50" s="17"/>
+      <c r="P50" s="17"/>
+      <c r="Q50" s="17"/>
+      <c r="R50" s="17"/>
+      <c r="S50" s="17"/>
+      <c r="T50" s="17"/>
+      <c r="U50" s="17"/>
+      <c r="V50" s="17"/>
+      <c r="W50" s="17"/>
+      <c r="X50" s="17"/>
+      <c r="Y50" s="17"/>
     </row>
     <row r="51">
       <c r="A51" s="12" t="s">
         <v>61</v>
       </c>
       <c r="B51" s="12">
-        <f>Z3 +Z1 +Z3 + Z3 + Z2 +Z3 +Z6 +Z5 +Z12</f>
-        <v>134</v>
+        <f>Z3 +Z1 +Z3 + Z3 + Z2 +Z3 +Z6 +Z5 +Z12 +Z8 +Z2 + Z2 + Z9 + Z2</f>
+        <v>209</v>
       </c>
       <c r="C51" s="12" t="s">
         <v>60</v>
@@ -3363,39 +3699,51 @@
       <c r="S51" s="13">
         <v>12.0</v>
       </c>
-      <c r="T51" s="16"/>
-      <c r="U51" s="16"/>
-      <c r="V51" s="16"/>
-      <c r="W51" s="16"/>
-      <c r="X51" s="16"/>
-      <c r="Y51" s="16"/>
+      <c r="T51" s="12">
+        <v>18.0</v>
+      </c>
+      <c r="U51" s="13">
+        <v>8.0</v>
+      </c>
+      <c r="V51" s="18">
+        <v>2.0</v>
+      </c>
+      <c r="W51" s="18">
+        <v>2.0</v>
+      </c>
+      <c r="X51" s="13">
+        <v>9.0</v>
+      </c>
+      <c r="Y51" s="18">
+        <v>2.0</v>
+      </c>
     </row>
     <row r="52">
-      <c r="A52" s="16"/>
-      <c r="B52" s="16"/>
-      <c r="C52" s="16"/>
-      <c r="D52" s="16"/>
-      <c r="E52" s="16"/>
-      <c r="F52" s="16"/>
-      <c r="G52" s="16"/>
-      <c r="H52" s="16"/>
-      <c r="I52" s="16"/>
-      <c r="J52" s="16"/>
-      <c r="K52" s="16"/>
-      <c r="L52" s="16"/>
-      <c r="M52" s="16"/>
-      <c r="N52" s="16"/>
-      <c r="O52" s="16"/>
-      <c r="P52" s="16"/>
-      <c r="Q52" s="16"/>
-      <c r="R52" s="16"/>
-      <c r="S52" s="16"/>
-      <c r="T52" s="16"/>
-      <c r="U52" s="16"/>
-      <c r="V52" s="16"/>
-      <c r="W52" s="16"/>
-      <c r="X52" s="16"/>
-      <c r="Y52" s="16"/>
+      <c r="A52" s="17"/>
+      <c r="B52" s="17"/>
+      <c r="C52" s="17"/>
+      <c r="D52" s="17"/>
+      <c r="E52" s="17"/>
+      <c r="F52" s="17"/>
+      <c r="G52" s="17"/>
+      <c r="H52" s="17"/>
+      <c r="I52" s="17"/>
+      <c r="J52" s="17"/>
+      <c r="K52" s="17"/>
+      <c r="L52" s="17"/>
+      <c r="M52" s="17"/>
+      <c r="N52" s="17"/>
+      <c r="O52" s="17"/>
+      <c r="P52" s="17"/>
+      <c r="Q52" s="17"/>
+      <c r="R52" s="17"/>
+      <c r="S52" s="17"/>
+      <c r="T52" s="17"/>
+      <c r="U52" s="17"/>
+      <c r="V52" s="17"/>
+      <c r="W52" s="17"/>
+      <c r="X52" s="17"/>
+      <c r="Y52" s="17"/>
     </row>
     <row r="53">
       <c r="A53" s="12" t="s">
@@ -3455,47 +3803,59 @@
       <c r="S53" s="12">
         <v>19.0</v>
       </c>
-      <c r="T53" s="16"/>
-      <c r="U53" s="16"/>
-      <c r="V53" s="16"/>
-      <c r="W53" s="16"/>
-      <c r="X53" s="16"/>
-      <c r="Y53" s="16"/>
+      <c r="T53" s="12">
+        <v>17.0</v>
+      </c>
+      <c r="U53" s="12">
+        <v>21.0</v>
+      </c>
+      <c r="V53" s="12">
+        <v>17.0</v>
+      </c>
+      <c r="W53" s="12">
+        <v>20.0</v>
+      </c>
+      <c r="X53" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y53" s="14" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="54">
-      <c r="A54" s="16"/>
-      <c r="B54" s="16"/>
-      <c r="C54" s="16"/>
-      <c r="D54" s="16"/>
-      <c r="E54" s="16"/>
-      <c r="F54" s="16"/>
-      <c r="G54" s="16"/>
-      <c r="H54" s="16"/>
-      <c r="I54" s="16"/>
-      <c r="J54" s="16"/>
-      <c r="K54" s="16"/>
-      <c r="L54" s="16"/>
-      <c r="M54" s="16"/>
-      <c r="N54" s="16"/>
-      <c r="O54" s="16"/>
-      <c r="P54" s="16"/>
-      <c r="Q54" s="16"/>
-      <c r="R54" s="16"/>
-      <c r="S54" s="16"/>
-      <c r="T54" s="16"/>
-      <c r="U54" s="16"/>
-      <c r="V54" s="16"/>
-      <c r="W54" s="16"/>
-      <c r="X54" s="16"/>
-      <c r="Y54" s="16"/>
+      <c r="A54" s="17"/>
+      <c r="B54" s="17"/>
+      <c r="C54" s="17"/>
+      <c r="D54" s="17"/>
+      <c r="E54" s="17"/>
+      <c r="F54" s="17"/>
+      <c r="G54" s="17"/>
+      <c r="H54" s="17"/>
+      <c r="I54" s="17"/>
+      <c r="J54" s="17"/>
+      <c r="K54" s="17"/>
+      <c r="L54" s="17"/>
+      <c r="M54" s="17"/>
+      <c r="N54" s="17"/>
+      <c r="O54" s="17"/>
+      <c r="P54" s="17"/>
+      <c r="Q54" s="17"/>
+      <c r="R54" s="17"/>
+      <c r="S54" s="17"/>
+      <c r="T54" s="17"/>
+      <c r="U54" s="17"/>
+      <c r="V54" s="17"/>
+      <c r="W54" s="17"/>
+      <c r="X54" s="17"/>
+      <c r="Y54" s="17"/>
     </row>
     <row r="55">
       <c r="A55" s="12" t="s">
         <v>64</v>
       </c>
       <c r="B55" s="12">
-        <f>Z14 +Z14 +Z13</f>
-        <v>7</v>
+        <f>Z14 +Z14 +Z13 + Z10</f>
+        <v>13</v>
       </c>
       <c r="C55" s="12" t="s">
         <v>63</v>
@@ -3548,47 +3908,59 @@
       <c r="S55" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="T55" s="16"/>
-      <c r="U55" s="16"/>
-      <c r="V55" s="16"/>
-      <c r="W55" s="16"/>
-      <c r="X55" s="16"/>
-      <c r="Y55" s="16"/>
+      <c r="T55" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="U55" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="V55" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="W55" s="12">
+        <v>19.0</v>
+      </c>
+      <c r="X55" s="13">
+        <v>10.0</v>
+      </c>
+      <c r="Y55" s="12">
+        <v>18.0</v>
+      </c>
     </row>
     <row r="56">
-      <c r="A56" s="16"/>
-      <c r="B56" s="16"/>
-      <c r="C56" s="16"/>
-      <c r="D56" s="16"/>
-      <c r="E56" s="16"/>
-      <c r="F56" s="16"/>
-      <c r="G56" s="16"/>
-      <c r="H56" s="16"/>
-      <c r="I56" s="16"/>
-      <c r="J56" s="16"/>
-      <c r="K56" s="16"/>
-      <c r="L56" s="16"/>
-      <c r="M56" s="16"/>
-      <c r="N56" s="16"/>
-      <c r="O56" s="16"/>
-      <c r="P56" s="16"/>
-      <c r="Q56" s="16"/>
-      <c r="R56" s="16"/>
-      <c r="S56" s="16"/>
-      <c r="T56" s="16"/>
-      <c r="U56" s="16"/>
-      <c r="V56" s="16"/>
-      <c r="W56" s="16"/>
-      <c r="X56" s="16"/>
-      <c r="Y56" s="16"/>
+      <c r="A56" s="17"/>
+      <c r="B56" s="17"/>
+      <c r="C56" s="17"/>
+      <c r="D56" s="17"/>
+      <c r="E56" s="17"/>
+      <c r="F56" s="17"/>
+      <c r="G56" s="17"/>
+      <c r="H56" s="17"/>
+      <c r="I56" s="17"/>
+      <c r="J56" s="17"/>
+      <c r="K56" s="17"/>
+      <c r="L56" s="17"/>
+      <c r="M56" s="17"/>
+      <c r="N56" s="17"/>
+      <c r="O56" s="17"/>
+      <c r="P56" s="17"/>
+      <c r="Q56" s="17"/>
+      <c r="R56" s="17"/>
+      <c r="S56" s="17"/>
+      <c r="T56" s="17"/>
+      <c r="U56" s="17"/>
+      <c r="V56" s="17"/>
+      <c r="W56" s="17"/>
+      <c r="X56" s="17"/>
+      <c r="Y56" s="17"/>
     </row>
     <row r="57">
       <c r="A57" s="12" t="s">
         <v>65</v>
       </c>
       <c r="B57" s="12">
-        <f> Z3 +Z7 +Z6 +Z7 +Z8 +Z6 + Z7 + Z3 + Z3 +Z9 +Z2</f>
-        <v>130</v>
+        <f> Z3 +Z7 +Z6 +Z7 +Z8 +Z6 + Z7 + Z3 + Z3 +Z9 +Z2 +Z4 + Z9 + Z4</f>
+        <v>163</v>
       </c>
       <c r="C57" s="12" t="s">
         <v>66</v>
@@ -3641,47 +4013,59 @@
       <c r="S57" s="18">
         <v>2.0</v>
       </c>
-      <c r="T57" s="16"/>
-      <c r="U57" s="16"/>
-      <c r="V57" s="16"/>
-      <c r="W57" s="16"/>
-      <c r="X57" s="16"/>
-      <c r="Y57" s="16"/>
+      <c r="T57" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="U57" s="12">
+        <v>23.0</v>
+      </c>
+      <c r="V57" s="13">
+        <v>4.0</v>
+      </c>
+      <c r="W57" s="13">
+        <v>9.0</v>
+      </c>
+      <c r="X57" s="13">
+        <v>4.0</v>
+      </c>
+      <c r="Y57" s="14" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="58">
-      <c r="A58" s="16"/>
-      <c r="B58" s="16"/>
-      <c r="C58" s="16"/>
-      <c r="D58" s="16"/>
-      <c r="E58" s="16"/>
-      <c r="F58" s="16"/>
-      <c r="G58" s="16"/>
-      <c r="H58" s="16"/>
-      <c r="I58" s="16"/>
-      <c r="J58" s="16"/>
-      <c r="K58" s="16"/>
-      <c r="L58" s="16"/>
-      <c r="M58" s="16"/>
-      <c r="N58" s="16"/>
-      <c r="O58" s="16"/>
-      <c r="P58" s="16"/>
-      <c r="Q58" s="16"/>
-      <c r="R58" s="16"/>
-      <c r="S58" s="16"/>
-      <c r="T58" s="16"/>
-      <c r="U58" s="16"/>
-      <c r="V58" s="16"/>
-      <c r="W58" s="16"/>
-      <c r="X58" s="16"/>
-      <c r="Y58" s="16"/>
+      <c r="A58" s="17"/>
+      <c r="B58" s="17"/>
+      <c r="C58" s="17"/>
+      <c r="D58" s="17"/>
+      <c r="E58" s="17"/>
+      <c r="F58" s="17"/>
+      <c r="G58" s="17"/>
+      <c r="H58" s="17"/>
+      <c r="I58" s="17"/>
+      <c r="J58" s="17"/>
+      <c r="K58" s="17"/>
+      <c r="L58" s="17"/>
+      <c r="M58" s="17"/>
+      <c r="N58" s="17"/>
+      <c r="O58" s="17"/>
+      <c r="P58" s="17"/>
+      <c r="Q58" s="17"/>
+      <c r="R58" s="17"/>
+      <c r="S58" s="17"/>
+      <c r="T58" s="17"/>
+      <c r="U58" s="17"/>
+      <c r="V58" s="17"/>
+      <c r="W58" s="17"/>
+      <c r="X58" s="17"/>
+      <c r="Y58" s="17"/>
     </row>
     <row r="59">
       <c r="A59" s="12" t="s">
         <v>67</v>
       </c>
       <c r="B59" s="12">
-        <f> Z5 +Z11 +Z6 +Z14 +Z10 +Z10 + Z13 + Z6 + Z9 +Z2 +Z10 +Z12 +Z3</f>
-        <v>106</v>
+        <f> Z5 +Z11 +Z6 +Z14 +Z10 +Z10 + Z13 + Z6 + Z9 +Z2 +Z10 +Z12 +Z3 +Z9 +Z10 + Z12 + Z15</f>
+        <v>124</v>
       </c>
       <c r="C59" s="12" t="s">
         <v>66</v>
@@ -3734,39 +4118,51 @@
       <c r="S59" s="15">
         <v>3.0</v>
       </c>
-      <c r="T59" s="16"/>
-      <c r="U59" s="16"/>
-      <c r="V59" s="16"/>
-      <c r="W59" s="16"/>
-      <c r="X59" s="16"/>
-      <c r="Y59" s="16"/>
+      <c r="T59" s="13">
+        <v>9.0</v>
+      </c>
+      <c r="U59" s="13">
+        <v>10.0</v>
+      </c>
+      <c r="V59" s="12">
+        <v>20.0</v>
+      </c>
+      <c r="W59" s="13">
+        <v>12.0</v>
+      </c>
+      <c r="X59" s="13">
+        <v>15.0</v>
+      </c>
+      <c r="Y59" s="12">
+        <v>21.0</v>
+      </c>
     </row>
     <row r="60">
-      <c r="A60" s="16"/>
-      <c r="B60" s="16"/>
-      <c r="C60" s="16"/>
-      <c r="D60" s="16"/>
-      <c r="E60" s="16"/>
-      <c r="F60" s="16"/>
-      <c r="G60" s="16"/>
-      <c r="H60" s="16"/>
-      <c r="I60" s="16"/>
-      <c r="J60" s="16"/>
-      <c r="K60" s="16"/>
-      <c r="L60" s="16"/>
-      <c r="M60" s="16"/>
-      <c r="N60" s="16"/>
-      <c r="O60" s="16"/>
-      <c r="P60" s="16"/>
-      <c r="Q60" s="16"/>
-      <c r="R60" s="16"/>
-      <c r="S60" s="16"/>
-      <c r="T60" s="16"/>
-      <c r="U60" s="16"/>
-      <c r="V60" s="16"/>
-      <c r="W60" s="16"/>
-      <c r="X60" s="16"/>
-      <c r="Y60" s="16"/>
+      <c r="A60" s="17"/>
+      <c r="B60" s="17"/>
+      <c r="C60" s="17"/>
+      <c r="D60" s="17"/>
+      <c r="E60" s="17"/>
+      <c r="F60" s="17"/>
+      <c r="G60" s="17"/>
+      <c r="H60" s="17"/>
+      <c r="I60" s="17"/>
+      <c r="J60" s="17"/>
+      <c r="K60" s="17"/>
+      <c r="L60" s="17"/>
+      <c r="M60" s="17"/>
+      <c r="N60" s="17"/>
+      <c r="O60" s="17"/>
+      <c r="P60" s="17"/>
+      <c r="Q60" s="17"/>
+      <c r="R60" s="17"/>
+      <c r="S60" s="17"/>
+      <c r="T60" s="17"/>
+      <c r="U60" s="17"/>
+      <c r="V60" s="17"/>
+      <c r="W60" s="17"/>
+      <c r="X60" s="17"/>
+      <c r="Y60" s="17"/>
     </row>
     <row r="61">
       <c r="A61" s="12" t="s">
@@ -3827,47 +4223,59 @@
       <c r="S61" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="T61" s="16"/>
-      <c r="U61" s="16"/>
-      <c r="V61" s="16"/>
-      <c r="W61" s="16"/>
-      <c r="X61" s="16"/>
-      <c r="Y61" s="16"/>
+      <c r="T61" s="12">
+        <v>20.0</v>
+      </c>
+      <c r="U61" s="12">
+        <v>22.0</v>
+      </c>
+      <c r="V61" s="12">
+        <v>21.0</v>
+      </c>
+      <c r="W61" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="X61" s="12">
+        <v>16.0</v>
+      </c>
+      <c r="Y61" s="12">
+        <v>19.0</v>
+      </c>
     </row>
     <row r="62">
-      <c r="A62" s="16"/>
-      <c r="B62" s="16"/>
-      <c r="C62" s="16"/>
-      <c r="D62" s="16"/>
-      <c r="E62" s="16"/>
-      <c r="F62" s="16"/>
-      <c r="G62" s="16"/>
-      <c r="H62" s="16"/>
-      <c r="I62" s="16"/>
-      <c r="J62" s="16"/>
-      <c r="K62" s="16"/>
-      <c r="L62" s="16"/>
-      <c r="M62" s="16"/>
-      <c r="N62" s="16"/>
-      <c r="O62" s="16"/>
-      <c r="P62" s="16"/>
-      <c r="Q62" s="16"/>
-      <c r="R62" s="16"/>
-      <c r="S62" s="16"/>
-      <c r="T62" s="16"/>
-      <c r="U62" s="16"/>
-      <c r="V62" s="16"/>
-      <c r="W62" s="16"/>
-      <c r="X62" s="16"/>
-      <c r="Y62" s="16"/>
+      <c r="A62" s="17"/>
+      <c r="B62" s="17"/>
+      <c r="C62" s="17"/>
+      <c r="D62" s="17"/>
+      <c r="E62" s="17"/>
+      <c r="F62" s="17"/>
+      <c r="G62" s="17"/>
+      <c r="H62" s="17"/>
+      <c r="I62" s="17"/>
+      <c r="J62" s="17"/>
+      <c r="K62" s="17"/>
+      <c r="L62" s="17"/>
+      <c r="M62" s="17"/>
+      <c r="N62" s="17"/>
+      <c r="O62" s="17"/>
+      <c r="P62" s="17"/>
+      <c r="Q62" s="17"/>
+      <c r="R62" s="17"/>
+      <c r="S62" s="17"/>
+      <c r="T62" s="17"/>
+      <c r="U62" s="17"/>
+      <c r="V62" s="17"/>
+      <c r="W62" s="17"/>
+      <c r="X62" s="17"/>
+      <c r="Y62" s="17"/>
     </row>
     <row r="63">
       <c r="A63" s="12" t="s">
         <v>70</v>
       </c>
       <c r="B63" s="12">
-        <f>Z12 +Z10 +Z8 +Z12 +Z9 + Z14 + Z15 +Z11 +Z14 +Z13</f>
-        <v>42</v>
+        <f>Z12 +Z10 +Z8 +Z12 +Z9 + Z14 + Z15 +Z11 +Z14 +Z13 +Z15 + Z13 + Z6</f>
+        <v>56</v>
       </c>
       <c r="C63" s="12" t="s">
         <v>69</v>
@@ -3920,12 +4328,24 @@
       <c r="S63" s="13">
         <v>13.0</v>
       </c>
-      <c r="T63" s="16"/>
-      <c r="U63" s="16"/>
-      <c r="V63" s="16"/>
-      <c r="W63" s="16"/>
-      <c r="X63" s="16"/>
-      <c r="Y63" s="16"/>
+      <c r="T63" s="13">
+        <v>15.0</v>
+      </c>
+      <c r="U63" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="V63" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="W63" s="13">
+        <v>13.0</v>
+      </c>
+      <c r="X63" s="13">
+        <v>6.0</v>
+      </c>
+      <c r="Y63" s="12">
+        <v>20.0</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="12" t="s">
@@ -3947,14 +4367,14 @@
       </c>
       <c r="B66" s="12">
         <f> B5+B7</f>
-        <v>102</v>
+        <v>152</v>
       </c>
       <c r="D66" s="12" t="s">
         <v>74</v>
       </c>
       <c r="E66" s="12">
         <f> B66+B67+B68+B69+B72+B73+B80+B79+B77+B76+B75</f>
-        <v>1691</v>
+        <v>2399</v>
       </c>
       <c r="W66" s="21">
         <v>1.0</v>
@@ -3969,14 +4389,14 @@
       </c>
       <c r="B67" s="12">
         <f> B9+B11</f>
-        <v>199</v>
+        <v>283</v>
       </c>
       <c r="D67" s="12" t="s">
         <v>75</v>
       </c>
       <c r="E67" s="12">
         <f> B71+B70</f>
-        <v>535</v>
+        <v>654</v>
       </c>
       <c r="W67" s="23">
         <v>2.0</v>
@@ -3991,14 +4411,14 @@
       </c>
       <c r="B68" s="12">
         <f> B13+B15</f>
-        <v>140</v>
+        <v>216</v>
       </c>
       <c r="D68" s="12" t="s">
         <v>76</v>
       </c>
       <c r="E68" s="12">
         <f> B78+B74</f>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="W68" s="24">
         <v>3.0</v>
@@ -4013,7 +4433,7 @@
       </c>
       <c r="B69" s="12">
         <f>B17+B19</f>
-        <v>227</v>
+        <v>348</v>
       </c>
       <c r="W69" s="25">
         <v>4.0</v>
@@ -4028,7 +4448,7 @@
       </c>
       <c r="B70" s="12">
         <f> B21+B23</f>
-        <v>290</v>
+        <v>337</v>
       </c>
       <c r="W70" s="25">
         <v>5.0</v>
@@ -4043,7 +4463,7 @@
       </c>
       <c r="B71" s="12">
         <f> B25+B27</f>
-        <v>245</v>
+        <v>317</v>
       </c>
       <c r="W71" s="25">
         <v>6.0</v>
@@ -4058,7 +4478,7 @@
       </c>
       <c r="B72" s="12">
         <f> B29+B31</f>
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="W72" s="25">
         <v>7.0</v>
@@ -4073,7 +4493,7 @@
       </c>
       <c r="B73" s="12">
         <f>B33+B35</f>
-        <v>363</v>
+        <v>515</v>
       </c>
       <c r="W73" s="25">
         <v>8.0</v>
@@ -4088,7 +4508,7 @@
       </c>
       <c r="B74" s="12">
         <f> B45+B47</f>
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="W74" s="25"/>
       <c r="X74" s="22"/>
@@ -4099,7 +4519,7 @@
       </c>
       <c r="B75" s="12">
         <f> B37+B39</f>
-        <v>131</v>
+        <v>170</v>
       </c>
       <c r="W75" s="25">
         <v>9.0</v>
@@ -4129,7 +4549,7 @@
       </c>
       <c r="B77" s="12">
         <f> B49+B51</f>
-        <v>232</v>
+        <v>348</v>
       </c>
       <c r="W77" s="25">
         <v>12.0</v>
@@ -4144,7 +4564,7 @@
       </c>
       <c r="B78" s="12">
         <f> B53+B55</f>
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="W78" s="25">
         <v>13.0</v>
@@ -4159,7 +4579,7 @@
       </c>
       <c r="B79" s="12">
         <f> B57+B59</f>
-        <v>236</v>
+        <v>287</v>
       </c>
       <c r="W79" s="25">
         <v>14.0</v>
@@ -4174,7 +4594,7 @@
       </c>
       <c r="B80" s="12">
         <f> B61+B63</f>
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="W80" s="25">
         <v>15.0</v>
@@ -4312,7 +4732,24 @@
       <c r="Q83" s="33" t="s">
         <v>94</v>
       </c>
-      <c r="W83" s="34"/>
+      <c r="R83" s="33" t="s">
+        <v>95</v>
+      </c>
+      <c r="S83" s="33" t="s">
+        <v>96</v>
+      </c>
+      <c r="T83" s="33" t="s">
+        <v>97</v>
+      </c>
+      <c r="U83" s="33" t="s">
+        <v>98</v>
+      </c>
+      <c r="V83" s="33" t="s">
+        <v>99</v>
+      </c>
+      <c r="W83" s="30" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="34"/>
@@ -4331,54 +4768,71 @@
         <v>47</v>
       </c>
       <c r="B85" s="30" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="C85" s="31" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="D85" s="32" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="E85" s="32" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="F85" s="30" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="G85" s="30" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="H85" s="30" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="I85" s="30" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="J85" s="33" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="K85" s="33" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="L85" s="33" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="M85" s="33" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="N85" s="33" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="O85" s="33" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="P85" s="33" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="Q85" s="33" t="s">
-        <v>110</v>
-      </c>
-      <c r="W85" s="34"/>
+        <v>116</v>
+      </c>
+      <c r="R85" s="33" t="s">
+        <v>117</v>
+      </c>
+      <c r="S85" s="33" t="s">
+        <v>118</v>
+      </c>
+      <c r="T85" s="33" t="s">
+        <v>119</v>
+      </c>
+      <c r="U85" s="33" t="s">
+        <v>120</v>
+      </c>
+      <c r="V85" s="33" t="s">
+        <v>121</v>
+      </c>
+      <c r="W85" s="30" t="s">
+        <v>122</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="34"/>
@@ -4397,59 +4851,71 @@
         <v>29</v>
       </c>
       <c r="B87" s="37" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="C87" s="38" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="D87" s="39" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="E87" s="39" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="F87" s="37" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="G87" s="37" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="H87" s="37" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="I87" s="37" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="J87" s="40" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="K87" s="40" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="L87" s="40" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="M87" s="40" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="N87" s="40" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="O87" s="40" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="P87" s="40" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="Q87" s="40" t="s">
-        <v>126</v>
-      </c>
-      <c r="R87" s="41"/>
-      <c r="S87" s="41"/>
-      <c r="T87" s="41"/>
-      <c r="U87" s="41"/>
-      <c r="V87" s="41"/>
-      <c r="W87" s="42"/>
+        <v>138</v>
+      </c>
+      <c r="R87" s="40" t="s">
+        <v>139</v>
+      </c>
+      <c r="S87" s="40" t="s">
+        <v>140</v>
+      </c>
+      <c r="T87" s="40" t="s">
+        <v>141</v>
+      </c>
+      <c r="U87" s="40" t="s">
+        <v>142</v>
+      </c>
+      <c r="V87" s="40" t="s">
+        <v>143</v>
+      </c>
+      <c r="W87" s="37" t="s">
+        <v>144</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/docs/classifiche/classifica2025.xlsx
+++ b/docs/classifiche/classifica2025.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="183">
   <si>
     <t>STAGIONE 2025: MOTO 2</t>
   </si>
@@ -235,13 +235,127 @@
     <t>Costruttori</t>
   </si>
   <si>
+    <t>CLASSIFICA PILOTI</t>
+  </si>
+  <si>
     <t>Kalex</t>
   </si>
   <si>
+    <t>Bonelli</t>
+  </si>
+  <si>
+    <t>Lopez</t>
+  </si>
+  <si>
+    <t>Cardalus</t>
+  </si>
+  <si>
     <t>Boscoscuro</t>
   </si>
   <si>
+    <t>Roberts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OF American Racing Team </t>
+  </si>
+  <si>
+    <t>Aldeguer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Muñoz </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preicanos </t>
+  </si>
+  <si>
     <t>Forward</t>
+  </si>
+  <si>
+    <t>Gabrielli</t>
+  </si>
+  <si>
+    <t>Chantra</t>
+  </si>
+  <si>
+    <t>Idemitsu Honda</t>
+  </si>
+  <si>
+    <t>Binder</t>
+  </si>
+  <si>
+    <t>Husquarna</t>
+  </si>
+  <si>
+    <t>Dixon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramirez </t>
+  </si>
+  <si>
+    <t>Artigas</t>
+  </si>
+  <si>
+    <t>Klint Forward</t>
+  </si>
+  <si>
+    <t>Arbolino</t>
+  </si>
+  <si>
+    <t>Canet</t>
+  </si>
+  <si>
+    <t>Foggia</t>
+  </si>
+  <si>
+    <t>Italtrans</t>
+  </si>
+  <si>
+    <t>Garcia</t>
+  </si>
+  <si>
+    <t>Arenas</t>
+  </si>
+  <si>
+    <t>Gresini Moto 2</t>
+  </si>
+  <si>
+    <t>Escrig</t>
+  </si>
+  <si>
+    <t>Ogura</t>
+  </si>
+  <si>
+    <t>van den Goorbergh</t>
+  </si>
+  <si>
+    <t>Agius</t>
+  </si>
+  <si>
+    <t>Guevara</t>
+  </si>
+  <si>
+    <t>Oncu</t>
+  </si>
+  <si>
+    <t>Sasaki</t>
+  </si>
+  <si>
+    <t>Gonzales</t>
+  </si>
+  <si>
+    <t>Alcoba</t>
+  </si>
+  <si>
+    <t>Moreira</t>
+  </si>
+  <si>
+    <t>Vietti</t>
+  </si>
+  <si>
+    <t>Aji</t>
+  </si>
+  <si>
+    <t>Masia</t>
   </si>
   <si>
     <t>TEMPI IN QUALIFICA</t>
@@ -546,7 +660,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="15">
     <border/>
     <border>
       <left style="thin">
@@ -594,6 +708,47 @@
       </bottom>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+    </border>
+    <border>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
@@ -629,7 +784,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="46">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -685,6 +840,11 @@
     <xf borderId="0" fillId="6" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
     </xf>
+    <xf borderId="7" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="8" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="9" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="0" fillId="3" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -700,6 +860,12 @@
     <xf borderId="0" fillId="4" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
+    <xf borderId="10" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="2" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf borderId="0" fillId="5" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -712,28 +878,28 @@
     <xf borderId="6" fillId="2" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="7" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="11" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="3" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="8" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="12" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="7" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="11" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="3" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="8" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="9" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="12" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="13" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="10" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="14" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="5" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -962,12 +1128,14 @@
     <col customWidth="1" min="5" max="5" width="15.13"/>
     <col customWidth="1" min="6" max="6" width="14.38"/>
     <col customWidth="1" min="7" max="7" width="15.0"/>
-    <col customWidth="1" min="8" max="8" width="16.38"/>
+    <col customWidth="1" min="8" max="8" width="20.75"/>
     <col customWidth="1" min="9" max="9" width="14.75"/>
     <col customWidth="1" min="10" max="10" width="15.75"/>
+    <col customWidth="1" min="11" max="11" width="15.63"/>
+    <col customWidth="1" min="12" max="12" width="21.75"/>
     <col customWidth="1" min="13" max="13" width="14.25"/>
     <col customWidth="1" min="15" max="15" width="14.75"/>
-    <col customWidth="1" min="16" max="16" width="13.5"/>
+    <col customWidth="1" min="16" max="16" width="15.38"/>
     <col customWidth="1" min="18" max="18" width="14.5"/>
     <col customWidth="1" min="20" max="20" width="14.13"/>
     <col customWidth="1" min="21" max="21" width="14.88"/>
@@ -4360,6 +4528,20 @@
       <c r="E65" s="12" t="s">
         <v>72</v>
       </c>
+      <c r="G65" s="21" t="s">
+        <v>74</v>
+      </c>
+      <c r="H65" s="22"/>
+      <c r="I65" s="22"/>
+      <c r="J65" s="22"/>
+      <c r="K65" s="22"/>
+      <c r="L65" s="22"/>
+      <c r="M65" s="22"/>
+      <c r="N65" s="22"/>
+      <c r="O65" s="22"/>
+      <c r="P65" s="22"/>
+      <c r="Q65" s="22"/>
+      <c r="R65" s="23"/>
     </row>
     <row r="66">
       <c r="A66" s="12" t="s">
@@ -4370,16 +4552,52 @@
         <v>152</v>
       </c>
       <c r="D66" s="12" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E66" s="12">
         <f> B66+B67+B68+B69+B72+B73+B80+B79+B77+B76+B75</f>
         <v>2399</v>
       </c>
-      <c r="W66" s="21">
+      <c r="G66" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="H66" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="I66" s="12">
+        <v>338.0</v>
+      </c>
+      <c r="J66" s="11">
         <v>1.0</v>
       </c>
-      <c r="X66" s="22">
+      <c r="K66" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="L66" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="M66" s="12">
+        <v>159.0</v>
+      </c>
+      <c r="N66" s="12">
+        <v>11.0</v>
+      </c>
+      <c r="O66" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="P66" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q66" s="12">
+        <v>13.0</v>
+      </c>
+      <c r="R66" s="12">
+        <v>21.0</v>
+      </c>
+      <c r="W66" s="24">
+        <v>1.0</v>
+      </c>
+      <c r="X66" s="25">
         <v>25.0</v>
       </c>
     </row>
@@ -4392,16 +4610,52 @@
         <v>283</v>
       </c>
       <c r="D67" s="12" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="E67" s="12">
         <f> B71+B70</f>
         <v>654</v>
       </c>
-      <c r="W67" s="23">
+      <c r="G67" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="H67" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="I67" s="12">
+        <v>209.0</v>
+      </c>
+      <c r="J67" s="18">
         <v>2.0</v>
       </c>
-      <c r="X67" s="22">
+      <c r="K67" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="L67" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="M67" s="12">
+        <v>158.0</v>
+      </c>
+      <c r="N67" s="12">
+        <v>12.0</v>
+      </c>
+      <c r="O67" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="P67" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q67" s="12">
+        <v>13.0</v>
+      </c>
+      <c r="R67" s="12">
+        <v>22.0</v>
+      </c>
+      <c r="W67" s="26">
+        <v>2.0</v>
+      </c>
+      <c r="X67" s="25">
         <v>20.0</v>
       </c>
     </row>
@@ -4414,16 +4668,52 @@
         <v>216</v>
       </c>
       <c r="D68" s="12" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="E68" s="12">
         <f> B78+B74</f>
         <v>26</v>
       </c>
-      <c r="W68" s="24">
+      <c r="G68" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="H68" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="I68" s="12">
+        <v>195.0</v>
+      </c>
+      <c r="J68" s="15">
         <v>3.0</v>
       </c>
-      <c r="X68" s="22">
+      <c r="K68" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="L68" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="M68" s="12">
+        <v>146.0</v>
+      </c>
+      <c r="N68" s="12">
+        <v>13.0</v>
+      </c>
+      <c r="O68" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="P68" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q68" s="12">
+        <v>11.0</v>
+      </c>
+      <c r="R68" s="12">
+        <v>23.0</v>
+      </c>
+      <c r="W68" s="27">
+        <v>3.0</v>
+      </c>
+      <c r="X68" s="25">
         <v>16.0</v>
       </c>
     </row>
@@ -4435,10 +4725,46 @@
         <f>B17+B19</f>
         <v>348</v>
       </c>
-      <c r="W69" s="25">
+      <c r="G69" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="H69" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="I69" s="12">
+        <v>180.0</v>
+      </c>
+      <c r="J69" s="12">
         <v>4.0</v>
       </c>
-      <c r="X69" s="22">
+      <c r="K69" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="L69" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="M69" s="12">
+        <v>139.0</v>
+      </c>
+      <c r="N69" s="12">
+        <v>14.0</v>
+      </c>
+      <c r="O69" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="P69" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q69" s="12">
+        <v>9.0</v>
+      </c>
+      <c r="R69" s="12">
+        <v>24.0</v>
+      </c>
+      <c r="W69" s="28">
+        <v>4.0</v>
+      </c>
+      <c r="X69" s="25">
         <v>13.0</v>
       </c>
     </row>
@@ -4450,10 +4776,46 @@
         <f> B21+B23</f>
         <v>337</v>
       </c>
-      <c r="W70" s="25">
+      <c r="G70" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="H70" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="I70" s="12">
+        <v>177.0</v>
+      </c>
+      <c r="J70" s="12">
         <v>5.0</v>
       </c>
-      <c r="X70" s="22">
+      <c r="K70" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="L70" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="M70" s="12">
+        <v>139.0</v>
+      </c>
+      <c r="N70" s="12">
+        <v>15.0</v>
+      </c>
+      <c r="O70" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="P70" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q70" s="12">
+        <v>8.0</v>
+      </c>
+      <c r="R70" s="12">
+        <v>25.0</v>
+      </c>
+      <c r="W70" s="28">
+        <v>5.0</v>
+      </c>
+      <c r="X70" s="25">
         <v>11.0</v>
       </c>
     </row>
@@ -4465,10 +4827,46 @@
         <f> B25+B27</f>
         <v>317</v>
       </c>
-      <c r="W71" s="25">
+      <c r="G71" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="H71" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="I71" s="12">
+        <v>169.0</v>
+      </c>
+      <c r="J71" s="12">
         <v>6.0</v>
       </c>
-      <c r="X71" s="22">
+      <c r="K71" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="L71" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="M71" s="12">
+        <v>124.0</v>
+      </c>
+      <c r="N71" s="12">
+        <v>16.0</v>
+      </c>
+      <c r="O71" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="P71" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q71" s="12">
+        <v>5.0</v>
+      </c>
+      <c r="R71" s="12">
+        <v>26.0</v>
+      </c>
+      <c r="W71" s="28">
+        <v>6.0</v>
+      </c>
+      <c r="X71" s="25">
         <v>10.0</v>
       </c>
     </row>
@@ -4480,10 +4878,46 @@
         <f> B29+B31</f>
         <v>14</v>
       </c>
-      <c r="W72" s="25">
+      <c r="G72" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="H72" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="I72" s="12">
+        <v>168.0</v>
+      </c>
+      <c r="J72" s="12">
         <v>7.0</v>
       </c>
-      <c r="X72" s="22">
+      <c r="K72" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="L72" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="M72" s="12">
+        <v>88.0</v>
+      </c>
+      <c r="N72" s="12">
+        <v>17.0</v>
+      </c>
+      <c r="O72" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="P72" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q72" s="12">
+        <v>2.0</v>
+      </c>
+      <c r="R72" s="12">
+        <v>27.0</v>
+      </c>
+      <c r="W72" s="28">
+        <v>7.0</v>
+      </c>
+      <c r="X72" s="25">
         <v>9.0</v>
       </c>
     </row>
@@ -4495,10 +4929,46 @@
         <f>B33+B35</f>
         <v>515</v>
       </c>
-      <c r="W73" s="25">
+      <c r="G73" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="H73" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="I73" s="12">
+        <v>168.0</v>
+      </c>
+      <c r="J73" s="12">
         <v>8.0</v>
       </c>
-      <c r="X73" s="22">
+      <c r="K73" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="L73" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="M73" s="12">
+        <v>56.0</v>
+      </c>
+      <c r="N73" s="12">
+        <v>18.0</v>
+      </c>
+      <c r="O73" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="P73" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q73" s="12">
+        <v>2.0</v>
+      </c>
+      <c r="R73" s="12">
+        <v>28.0</v>
+      </c>
+      <c r="W73" s="28">
+        <v>8.0</v>
+      </c>
+      <c r="X73" s="25">
         <v>8.0</v>
       </c>
     </row>
@@ -4510,8 +4980,44 @@
         <f> B45+B47</f>
         <v>13</v>
       </c>
-      <c r="W74" s="25"/>
-      <c r="X74" s="22"/>
+      <c r="G74" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="H74" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="I74" s="12">
+        <v>163.0</v>
+      </c>
+      <c r="J74" s="12">
+        <v>9.0</v>
+      </c>
+      <c r="K74" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="L74" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="M74" s="12">
+        <v>56.0</v>
+      </c>
+      <c r="N74" s="12">
+        <v>19.0</v>
+      </c>
+      <c r="O74" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="P74" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q74" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="R74" s="12">
+        <v>29.0</v>
+      </c>
+      <c r="W74" s="28"/>
+      <c r="X74" s="25"/>
     </row>
     <row r="75">
       <c r="A75" s="12" t="s">
@@ -4521,10 +5027,46 @@
         <f> B37+B39</f>
         <v>170</v>
       </c>
-      <c r="W75" s="25">
+      <c r="G75" s="29" t="s">
+        <v>112</v>
+      </c>
+      <c r="H75" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="I75" s="29">
+        <v>160.0</v>
+      </c>
+      <c r="J75" s="29">
+        <v>10.0</v>
+      </c>
+      <c r="K75" s="29" t="s">
+        <v>113</v>
+      </c>
+      <c r="L75" s="29" t="s">
+        <v>88</v>
+      </c>
+      <c r="M75" s="29">
+        <v>24.0</v>
+      </c>
+      <c r="N75" s="29">
+        <v>20.0</v>
+      </c>
+      <c r="O75" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="P75" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q75" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="R75" s="12">
+        <v>30.0</v>
+      </c>
+      <c r="W75" s="28">
         <v>9.0</v>
       </c>
-      <c r="X75" s="22">
+      <c r="X75" s="25">
         <v>7.0</v>
       </c>
     </row>
@@ -4536,10 +5078,18 @@
         <f>B41+B43</f>
         <v>8</v>
       </c>
-      <c r="W76" s="25">
+      <c r="G76" s="30"/>
+      <c r="H76" s="30"/>
+      <c r="I76" s="30"/>
+      <c r="J76" s="30"/>
+      <c r="K76" s="30"/>
+      <c r="L76" s="30"/>
+      <c r="M76" s="30"/>
+      <c r="N76" s="30"/>
+      <c r="W76" s="28">
         <v>10.0</v>
       </c>
-      <c r="X76" s="22">
+      <c r="X76" s="25">
         <v>6.0</v>
       </c>
     </row>
@@ -4551,10 +5101,10 @@
         <f> B49+B51</f>
         <v>348</v>
       </c>
-      <c r="W77" s="25">
+      <c r="W77" s="28">
         <v>12.0</v>
       </c>
-      <c r="X77" s="22">
+      <c r="X77" s="25">
         <v>4.0</v>
       </c>
     </row>
@@ -4566,10 +5116,10 @@
         <f> B53+B55</f>
         <v>13</v>
       </c>
-      <c r="W78" s="25">
+      <c r="W78" s="28">
         <v>13.0</v>
       </c>
-      <c r="X78" s="22">
+      <c r="X78" s="25">
         <v>3.0</v>
       </c>
     </row>
@@ -4581,10 +5131,10 @@
         <f> B57+B59</f>
         <v>287</v>
       </c>
-      <c r="W79" s="25">
+      <c r="W79" s="28">
         <v>14.0</v>
       </c>
-      <c r="X79" s="22">
+      <c r="X79" s="25">
         <v>2.0</v>
       </c>
     </row>
@@ -4596,27 +5146,27 @@
         <f> B61+B63</f>
         <v>58</v>
       </c>
-      <c r="W80" s="25">
+      <c r="W80" s="28">
         <v>15.0</v>
       </c>
-      <c r="X80" s="22">
+      <c r="X80" s="25">
         <v>1.0</v>
       </c>
     </row>
     <row r="81">
-      <c r="W81" s="26" t="s">
-        <v>27</v>
-      </c>
-      <c r="X81" s="27"/>
+      <c r="W81" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="X81" s="32"/>
     </row>
     <row r="82">
-      <c r="A82" s="28" t="s">
-        <v>77</v>
+      <c r="A82" s="33" t="s">
+        <v>115</v>
       </c>
       <c r="B82" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="C82" s="29" t="s">
+      <c r="C82" s="34" t="s">
         <v>5</v>
       </c>
       <c r="D82" s="9" t="s">
@@ -4681,245 +5231,246 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="30" t="s">
-        <v>78</v>
-      </c>
-      <c r="B83" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="C83" s="31" t="s">
-        <v>80</v>
-      </c>
-      <c r="D83" s="32" t="s">
-        <v>81</v>
-      </c>
-      <c r="E83" s="32" t="s">
-        <v>82</v>
-      </c>
-      <c r="F83" s="30" t="s">
-        <v>83</v>
-      </c>
-      <c r="G83" s="30" t="s">
-        <v>84</v>
-      </c>
-      <c r="H83" s="30" t="s">
-        <v>85</v>
-      </c>
-      <c r="I83" s="30" t="s">
-        <v>86</v>
-      </c>
-      <c r="J83" s="33" t="s">
-        <v>87</v>
-      </c>
-      <c r="K83" s="33" t="s">
-        <v>88</v>
-      </c>
-      <c r="L83" s="33" t="s">
-        <v>89</v>
-      </c>
-      <c r="M83" s="33" t="s">
-        <v>90</v>
-      </c>
-      <c r="N83" s="33" t="s">
-        <v>91</v>
-      </c>
-      <c r="O83" s="33" t="s">
-        <v>92</v>
-      </c>
-      <c r="P83" s="33" t="s">
-        <v>93</v>
-      </c>
-      <c r="Q83" s="33" t="s">
-        <v>94</v>
-      </c>
-      <c r="R83" s="33" t="s">
-        <v>95</v>
-      </c>
-      <c r="S83" s="33" t="s">
-        <v>96</v>
-      </c>
-      <c r="T83" s="33" t="s">
-        <v>97</v>
-      </c>
-      <c r="U83" s="33" t="s">
-        <v>98</v>
-      </c>
-      <c r="V83" s="33" t="s">
-        <v>99</v>
-      </c>
-      <c r="W83" s="30" t="s">
-        <v>100</v>
+      <c r="A83" s="35" t="s">
+        <v>116</v>
+      </c>
+      <c r="B83" s="35" t="s">
+        <v>117</v>
+      </c>
+      <c r="C83" s="36" t="s">
+        <v>118</v>
+      </c>
+      <c r="D83" s="37" t="s">
+        <v>119</v>
+      </c>
+      <c r="E83" s="37" t="s">
+        <v>120</v>
+      </c>
+      <c r="F83" s="35" t="s">
+        <v>121</v>
+      </c>
+      <c r="G83" s="35" t="s">
+        <v>122</v>
+      </c>
+      <c r="H83" s="35" t="s">
+        <v>123</v>
+      </c>
+      <c r="I83" s="35" t="s">
+        <v>124</v>
+      </c>
+      <c r="J83" s="38" t="s">
+        <v>125</v>
+      </c>
+      <c r="K83" s="38" t="s">
+        <v>126</v>
+      </c>
+      <c r="L83" s="38" t="s">
+        <v>127</v>
+      </c>
+      <c r="M83" s="38" t="s">
+        <v>128</v>
+      </c>
+      <c r="N83" s="38" t="s">
+        <v>129</v>
+      </c>
+      <c r="O83" s="38" t="s">
+        <v>130</v>
+      </c>
+      <c r="P83" s="38" t="s">
+        <v>131</v>
+      </c>
+      <c r="Q83" s="38" t="s">
+        <v>132</v>
+      </c>
+      <c r="R83" s="38" t="s">
+        <v>133</v>
+      </c>
+      <c r="S83" s="38" t="s">
+        <v>134</v>
+      </c>
+      <c r="T83" s="38" t="s">
+        <v>135</v>
+      </c>
+      <c r="U83" s="38" t="s">
+        <v>136</v>
+      </c>
+      <c r="V83" s="38" t="s">
+        <v>137</v>
+      </c>
+      <c r="W83" s="35" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="34"/>
-      <c r="B84" s="34"/>
-      <c r="C84" s="35"/>
-      <c r="D84" s="36"/>
-      <c r="E84" s="36"/>
-      <c r="F84" s="34"/>
-      <c r="G84" s="34"/>
-      <c r="H84" s="34"/>
-      <c r="I84" s="34"/>
-      <c r="W84" s="34"/>
+      <c r="A84" s="39"/>
+      <c r="B84" s="39"/>
+      <c r="C84" s="40"/>
+      <c r="D84" s="41"/>
+      <c r="E84" s="41"/>
+      <c r="F84" s="39"/>
+      <c r="G84" s="39"/>
+      <c r="H84" s="39"/>
+      <c r="I84" s="39"/>
+      <c r="W84" s="39"/>
     </row>
     <row r="85">
-      <c r="A85" s="30" t="s">
+      <c r="A85" s="35" t="s">
         <v>47</v>
       </c>
-      <c r="B85" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="C85" s="31" t="s">
-        <v>102</v>
-      </c>
-      <c r="D85" s="32" t="s">
-        <v>103</v>
-      </c>
-      <c r="E85" s="32" t="s">
-        <v>104</v>
-      </c>
-      <c r="F85" s="30" t="s">
-        <v>105</v>
-      </c>
-      <c r="G85" s="30" t="s">
-        <v>106</v>
-      </c>
-      <c r="H85" s="30" t="s">
-        <v>107</v>
-      </c>
-      <c r="I85" s="30" t="s">
-        <v>108</v>
-      </c>
-      <c r="J85" s="33" t="s">
-        <v>109</v>
-      </c>
-      <c r="K85" s="33" t="s">
-        <v>110</v>
-      </c>
-      <c r="L85" s="33" t="s">
-        <v>111</v>
-      </c>
-      <c r="M85" s="33" t="s">
-        <v>112</v>
-      </c>
-      <c r="N85" s="33" t="s">
-        <v>113</v>
-      </c>
-      <c r="O85" s="33" t="s">
-        <v>114</v>
-      </c>
-      <c r="P85" s="33" t="s">
-        <v>115</v>
-      </c>
-      <c r="Q85" s="33" t="s">
-        <v>116</v>
-      </c>
-      <c r="R85" s="33" t="s">
-        <v>117</v>
-      </c>
-      <c r="S85" s="33" t="s">
-        <v>118</v>
-      </c>
-      <c r="T85" s="33" t="s">
-        <v>119</v>
-      </c>
-      <c r="U85" s="33" t="s">
-        <v>120</v>
-      </c>
-      <c r="V85" s="33" t="s">
-        <v>121</v>
-      </c>
-      <c r="W85" s="30" t="s">
-        <v>122</v>
+      <c r="B85" s="35" t="s">
+        <v>139</v>
+      </c>
+      <c r="C85" s="36" t="s">
+        <v>140</v>
+      </c>
+      <c r="D85" s="37" t="s">
+        <v>141</v>
+      </c>
+      <c r="E85" s="37" t="s">
+        <v>142</v>
+      </c>
+      <c r="F85" s="35" t="s">
+        <v>143</v>
+      </c>
+      <c r="G85" s="35" t="s">
+        <v>144</v>
+      </c>
+      <c r="H85" s="35" t="s">
+        <v>145</v>
+      </c>
+      <c r="I85" s="35" t="s">
+        <v>146</v>
+      </c>
+      <c r="J85" s="38" t="s">
+        <v>147</v>
+      </c>
+      <c r="K85" s="38" t="s">
+        <v>148</v>
+      </c>
+      <c r="L85" s="38" t="s">
+        <v>149</v>
+      </c>
+      <c r="M85" s="38" t="s">
+        <v>150</v>
+      </c>
+      <c r="N85" s="38" t="s">
+        <v>151</v>
+      </c>
+      <c r="O85" s="38" t="s">
+        <v>152</v>
+      </c>
+      <c r="P85" s="38" t="s">
+        <v>153</v>
+      </c>
+      <c r="Q85" s="38" t="s">
+        <v>154</v>
+      </c>
+      <c r="R85" s="38" t="s">
+        <v>155</v>
+      </c>
+      <c r="S85" s="38" t="s">
+        <v>156</v>
+      </c>
+      <c r="T85" s="38" t="s">
+        <v>157</v>
+      </c>
+      <c r="U85" s="38" t="s">
+        <v>158</v>
+      </c>
+      <c r="V85" s="38" t="s">
+        <v>159</v>
+      </c>
+      <c r="W85" s="35" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="34"/>
-      <c r="B86" s="34"/>
-      <c r="C86" s="35"/>
-      <c r="D86" s="36"/>
-      <c r="E86" s="36"/>
-      <c r="F86" s="34"/>
-      <c r="G86" s="34"/>
-      <c r="H86" s="34"/>
-      <c r="I86" s="34"/>
-      <c r="W86" s="34"/>
+      <c r="A86" s="39"/>
+      <c r="B86" s="39"/>
+      <c r="C86" s="40"/>
+      <c r="D86" s="41"/>
+      <c r="E86" s="41"/>
+      <c r="F86" s="39"/>
+      <c r="G86" s="39"/>
+      <c r="H86" s="39"/>
+      <c r="I86" s="39"/>
+      <c r="W86" s="39"/>
     </row>
     <row r="87">
-      <c r="A87" s="37" t="s">
+      <c r="A87" s="42" t="s">
         <v>29</v>
       </c>
-      <c r="B87" s="37" t="s">
-        <v>123</v>
-      </c>
-      <c r="C87" s="38" t="s">
-        <v>124</v>
-      </c>
-      <c r="D87" s="39" t="s">
-        <v>125</v>
-      </c>
-      <c r="E87" s="39" t="s">
-        <v>126</v>
-      </c>
-      <c r="F87" s="37" t="s">
-        <v>127</v>
-      </c>
-      <c r="G87" s="37" t="s">
-        <v>128</v>
-      </c>
-      <c r="H87" s="37" t="s">
-        <v>129</v>
-      </c>
-      <c r="I87" s="37" t="s">
-        <v>130</v>
-      </c>
-      <c r="J87" s="40" t="s">
-        <v>131</v>
-      </c>
-      <c r="K87" s="40" t="s">
-        <v>132</v>
-      </c>
-      <c r="L87" s="40" t="s">
-        <v>133</v>
-      </c>
-      <c r="M87" s="40" t="s">
-        <v>134</v>
-      </c>
-      <c r="N87" s="40" t="s">
-        <v>135</v>
-      </c>
-      <c r="O87" s="40" t="s">
-        <v>136</v>
-      </c>
-      <c r="P87" s="40" t="s">
-        <v>137</v>
-      </c>
-      <c r="Q87" s="40" t="s">
-        <v>138</v>
-      </c>
-      <c r="R87" s="40" t="s">
-        <v>139</v>
-      </c>
-      <c r="S87" s="40" t="s">
-        <v>140</v>
-      </c>
-      <c r="T87" s="40" t="s">
-        <v>141</v>
-      </c>
-      <c r="U87" s="40" t="s">
-        <v>142</v>
-      </c>
-      <c r="V87" s="40" t="s">
-        <v>143</v>
-      </c>
-      <c r="W87" s="37" t="s">
-        <v>144</v>
+      <c r="B87" s="42" t="s">
+        <v>161</v>
+      </c>
+      <c r="C87" s="43" t="s">
+        <v>162</v>
+      </c>
+      <c r="D87" s="44" t="s">
+        <v>163</v>
+      </c>
+      <c r="E87" s="44" t="s">
+        <v>164</v>
+      </c>
+      <c r="F87" s="42" t="s">
+        <v>165</v>
+      </c>
+      <c r="G87" s="42" t="s">
+        <v>166</v>
+      </c>
+      <c r="H87" s="42" t="s">
+        <v>167</v>
+      </c>
+      <c r="I87" s="42" t="s">
+        <v>168</v>
+      </c>
+      <c r="J87" s="45" t="s">
+        <v>169</v>
+      </c>
+      <c r="K87" s="45" t="s">
+        <v>170</v>
+      </c>
+      <c r="L87" s="45" t="s">
+        <v>171</v>
+      </c>
+      <c r="M87" s="45" t="s">
+        <v>172</v>
+      </c>
+      <c r="N87" s="45" t="s">
+        <v>173</v>
+      </c>
+      <c r="O87" s="45" t="s">
+        <v>174</v>
+      </c>
+      <c r="P87" s="45" t="s">
+        <v>175</v>
+      </c>
+      <c r="Q87" s="45" t="s">
+        <v>176</v>
+      </c>
+      <c r="R87" s="45" t="s">
+        <v>177</v>
+      </c>
+      <c r="S87" s="45" t="s">
+        <v>178</v>
+      </c>
+      <c r="T87" s="45" t="s">
+        <v>179</v>
+      </c>
+      <c r="U87" s="45" t="s">
+        <v>180</v>
+      </c>
+      <c r="V87" s="45" t="s">
+        <v>181</v>
+      </c>
+      <c r="W87" s="42" t="s">
+        <v>182</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="A1:Y3"/>
+    <mergeCell ref="G65:R65"/>
   </mergeCells>
   <drawing r:id="rId1"/>
 </worksheet>
